--- a/review-results/河北实时运行及市场出清数据-20260731.xlsx
+++ b/review-results/河北实时运行及市场出清数据-20260731.xlsx
@@ -1391,9 +1391,7 @@
       <s:c r="F2" s="14" t="n">
         <s:v>4222</s:v>
       </s:c>
-      <s:c r="G2" s="15" t="n">
-        <s:v>5966.02</s:v>
-      </s:c>
+      <s:c r="G2" s="15"/>
       <s:c r="J2"/>
       <s:c r="K2"/>
       <s:c r="L2"/>
@@ -1415,9 +1413,7 @@
       <s:c r="F3" s="14" t="n">
         <s:v>4278.5</s:v>
       </s:c>
-      <s:c r="G3" s="15" t="n">
-        <s:v>6290</s:v>
-      </s:c>
+      <s:c r="G3" s="15"/>
       <s:c r="J3"/>
       <s:c r="K3"/>
       <s:c r="L3"/>
@@ -1439,9 +1435,7 @@
       <s:c r="F4" s="14" t="n">
         <s:v>4277.1</s:v>
       </s:c>
-      <s:c r="G4" s="15" t="n">
-        <s:v>6327.64</s:v>
-      </s:c>
+      <s:c r="G4" s="15"/>
       <s:c r="J4"/>
       <s:c r="K4"/>
       <s:c r="L4"/>
@@ -1463,9 +1457,7 @@
       <s:c r="F5" s="14" t="n">
         <s:v>4167.7</s:v>
       </s:c>
-      <s:c r="G5" s="15" t="n">
-        <s:v>6274.15</s:v>
-      </s:c>
+      <s:c r="G5" s="15"/>
       <s:c r="J5"/>
       <s:c r="K5"/>
       <s:c r="L5"/>
@@ -1487,9 +1479,7 @@
       <s:c r="F6" s="14" t="n">
         <s:v>4140.3</s:v>
       </s:c>
-      <s:c r="G6" s="15" t="n">
-        <s:v>6943.91</s:v>
-      </s:c>
+      <s:c r="G6" s="15"/>
       <s:c r="J6"/>
       <s:c r="K6"/>
       <s:c r="L6"/>
@@ -1511,9 +1501,7 @@
       <s:c r="F7" s="14" t="n">
         <s:v>4073.7</s:v>
       </s:c>
-      <s:c r="G7" s="15" t="n">
-        <s:v>6853.01</s:v>
-      </s:c>
+      <s:c r="G7" s="15"/>
       <s:c r="J7"/>
       <s:c r="K7"/>
       <s:c r="L7"/>
@@ -1535,9 +1523,7 @@
       <s:c r="F8" s="14" t="n">
         <s:v>4022.1</s:v>
       </s:c>
-      <s:c r="G8" s="15" t="n">
-        <s:v>6152.18</s:v>
-      </s:c>
+      <s:c r="G8" s="15"/>
       <s:c r="J8"/>
       <s:c r="K8"/>
       <s:c r="L8"/>
@@ -1559,9 +1545,7 @@
       <s:c r="F9" s="14" t="n">
         <s:v>4005</s:v>
       </s:c>
-      <s:c r="G9" s="15" t="n">
-        <s:v>6430.28</s:v>
-      </s:c>
+      <s:c r="G9" s="15"/>
       <s:c r="J9"/>
       <s:c r="K9"/>
       <s:c r="L9"/>
@@ -1583,9 +1567,7 @@
       <s:c r="F10" s="14" t="n">
         <s:v>3947.3</s:v>
       </s:c>
-      <s:c r="G10" s="15" t="n">
-        <s:v>6195.17</s:v>
-      </s:c>
+      <s:c r="G10" s="15"/>
       <s:c r="J10"/>
       <s:c r="K10"/>
       <s:c r="L10"/>
@@ -1607,9 +1589,7 @@
       <s:c r="F11" s="14" t="n">
         <s:v>3919.9</s:v>
       </s:c>
-      <s:c r="G11" s="15" t="n">
-        <s:v>6067.49</s:v>
-      </s:c>
+      <s:c r="G11" s="15"/>
       <s:c r="J11"/>
       <s:c r="K11"/>
       <s:c r="L11"/>
@@ -1631,9 +1611,7 @@
       <s:c r="F12" s="14" t="n">
         <s:v>3911.1</s:v>
       </s:c>
-      <s:c r="G12" s="15" t="n">
-        <s:v>6388.89</s:v>
-      </s:c>
+      <s:c r="G12" s="15"/>
       <s:c r="J12"/>
       <s:c r="K12"/>
       <s:c r="L12"/>
@@ -1655,9 +1633,7 @@
       <s:c r="F13" s="14" t="n">
         <s:v>3874.8</s:v>
       </s:c>
-      <s:c r="G13" s="15" t="n">
-        <s:v>6131.2</s:v>
-      </s:c>
+      <s:c r="G13" s="15"/>
       <s:c r="J13"/>
       <s:c r="K13"/>
       <s:c r="L13"/>
@@ -1679,9 +1655,7 @@
       <s:c r="F14" s="14" t="n">
         <s:v>3692.9</s:v>
       </s:c>
-      <s:c r="G14" s="15" t="n">
-        <s:v>6223.6</s:v>
-      </s:c>
+      <s:c r="G14" s="15"/>
       <s:c r="J14"/>
       <s:c r="K14"/>
       <s:c r="L14"/>
@@ -1703,9 +1677,7 @@
       <s:c r="F15" s="14" t="n">
         <s:v>3628.4</s:v>
       </s:c>
-      <s:c r="G15" s="15" t="n">
-        <s:v>6169.01</s:v>
-      </s:c>
+      <s:c r="G15" s="15"/>
       <s:c r="J15"/>
       <s:c r="K15"/>
       <s:c r="L15"/>
@@ -1727,9 +1699,7 @@
       <s:c r="F16" s="14" t="n">
         <s:v>3548.1</s:v>
       </s:c>
-      <s:c r="G16" s="15" t="n">
-        <s:v>6152.05</s:v>
-      </s:c>
+      <s:c r="G16" s="15"/>
       <s:c r="J16"/>
       <s:c r="K16"/>
       <s:c r="L16"/>
@@ -1751,9 +1721,7 @@
       <s:c r="F17" s="14" t="n">
         <s:v>3413.8</s:v>
       </s:c>
-      <s:c r="G17" s="15" t="n">
-        <s:v>5894.12</s:v>
-      </s:c>
+      <s:c r="G17" s="15"/>
       <s:c r="J17"/>
       <s:c r="K17"/>
       <s:c r="L17"/>
@@ -1775,9 +1743,7 @@
       <s:c r="F18" s="14" t="n">
         <s:v>3248.8</s:v>
       </s:c>
-      <s:c r="G18" s="15" t="n">
-        <s:v>6076.5</s:v>
-      </s:c>
+      <s:c r="G18" s="15"/>
       <s:c r="J18"/>
       <s:c r="K18"/>
       <s:c r="L18"/>
@@ -1799,9 +1765,7 @@
       <s:c r="F19" s="14" t="n">
         <s:v>3064.6</s:v>
       </s:c>
-      <s:c r="G19" s="15" t="n">
-        <s:v>6250.65</s:v>
-      </s:c>
+      <s:c r="G19" s="15"/>
       <s:c r="J19"/>
       <s:c r="K19"/>
       <s:c r="L19"/>
@@ -1823,9 +1787,7 @@
       <s:c r="F20" s="14" t="n">
         <s:v>2932.6</s:v>
       </s:c>
-      <s:c r="G20" s="15" t="n">
-        <s:v>5963.3</s:v>
-      </s:c>
+      <s:c r="G20" s="15"/>
       <s:c r="J20"/>
       <s:c r="K20"/>
       <s:c r="L20"/>
@@ -1847,9 +1809,7 @@
       <s:c r="F21" s="14" t="n">
         <s:v>2910.1</s:v>
       </s:c>
-      <s:c r="G21" s="15" t="n">
-        <s:v>5911.71</s:v>
-      </s:c>
+      <s:c r="G21" s="15"/>
       <s:c r="J21"/>
       <s:c r="K21"/>
       <s:c r="L21"/>
@@ -1871,9 +1831,7 @@
       <s:c r="F22" s="14" t="n">
         <s:v>2846.6</s:v>
       </s:c>
-      <s:c r="G22" s="15" t="n">
-        <s:v>5967.08</s:v>
-      </s:c>
+      <s:c r="G22" s="15"/>
       <s:c r="J22"/>
       <s:c r="K22"/>
       <s:c r="L22"/>
@@ -1895,9 +1853,7 @@
       <s:c r="F23" s="14" t="n">
         <s:v>2836.7</s:v>
       </s:c>
-      <s:c r="G23" s="15" t="n">
-        <s:v>6192.63</s:v>
-      </s:c>
+      <s:c r="G23" s="15"/>
       <s:c r="J23"/>
       <s:c r="K23"/>
       <s:c r="L23"/>
@@ -1919,9 +1875,7 @@
       <s:c r="F24" s="14" t="n">
         <s:v>2930.2</s:v>
       </s:c>
-      <s:c r="G24" s="15" t="n">
-        <s:v>6024.89</s:v>
-      </s:c>
+      <s:c r="G24" s="15"/>
       <s:c r="J24"/>
       <s:c r="K24"/>
       <s:c r="L24"/>
@@ -1943,9 +1897,7 @@
       <s:c r="F25" s="14" t="n">
         <s:v>3186</s:v>
       </s:c>
-      <s:c r="G25" s="15" t="n">
-        <s:v>5891.91</s:v>
-      </s:c>
+      <s:c r="G25" s="15"/>
       <s:c r="J25"/>
       <s:c r="K25"/>
       <s:c r="L25"/>
@@ -1967,9 +1919,7 @@
       <s:c r="F26" s="14" t="n">
         <s:v>3416.1</s:v>
       </s:c>
-      <s:c r="G26" s="15" t="n">
-        <s:v>5542.05</s:v>
-      </s:c>
+      <s:c r="G26" s="15"/>
       <s:c r="J26"/>
       <s:c r="K26"/>
       <s:c r="L26"/>
@@ -1991,9 +1941,7 @@
       <s:c r="F27" s="14" t="n">
         <s:v>3680</s:v>
       </s:c>
-      <s:c r="G27" s="15" t="n">
-        <s:v>5155.54</s:v>
-      </s:c>
+      <s:c r="G27" s="15"/>
       <s:c r="J27"/>
       <s:c r="K27"/>
       <s:c r="L27"/>
@@ -2015,9 +1963,7 @@
       <s:c r="F28" s="14" t="n">
         <s:v>3866.8</s:v>
       </s:c>
-      <s:c r="G28" s="15" t="n">
-        <s:v>4910.43</s:v>
-      </s:c>
+      <s:c r="G28" s="15"/>
       <s:c r="J28"/>
       <s:c r="K28"/>
       <s:c r="L28"/>
@@ -2039,9 +1985,7 @@
       <s:c r="F29" s="14" t="n">
         <s:v>3780.5</s:v>
       </s:c>
-      <s:c r="G29" s="15" t="n">
-        <s:v>4358.68</s:v>
-      </s:c>
+      <s:c r="G29" s="15"/>
       <s:c r="J29"/>
       <s:c r="K29"/>
       <s:c r="L29"/>
@@ -2063,9 +2007,7 @@
       <s:c r="F30" s="14" t="n">
         <s:v>3877.6</s:v>
       </s:c>
-      <s:c r="G30" s="15" t="n">
-        <s:v>4630.1</s:v>
-      </s:c>
+      <s:c r="G30" s="15"/>
       <s:c r="J30"/>
       <s:c r="K30"/>
       <s:c r="L30"/>
@@ -2087,9 +2029,7 @@
       <s:c r="F31" s="14" t="n">
         <s:v>3842.6</s:v>
       </s:c>
-      <s:c r="G31" s="15" t="n">
-        <s:v>4909.53</s:v>
-      </s:c>
+      <s:c r="G31" s="15"/>
       <s:c r="J31"/>
       <s:c r="K31"/>
       <s:c r="L31"/>
@@ -2111,9 +2051,7 @@
       <s:c r="F32" s="14" t="n">
         <s:v>3983.6</s:v>
       </s:c>
-      <s:c r="G32" s="15" t="n">
-        <s:v>5621.49</s:v>
-      </s:c>
+      <s:c r="G32" s="15"/>
       <s:c r="J32"/>
       <s:c r="K32"/>
       <s:c r="L32"/>
@@ -2135,9 +2073,7 @@
       <s:c r="F33" s="14" t="n">
         <s:v>4427.6</s:v>
       </s:c>
-      <s:c r="G33" s="15" t="n">
-        <s:v>6719.95</s:v>
-      </s:c>
+      <s:c r="G33" s="15"/>
       <s:c r="J33"/>
       <s:c r="K33"/>
       <s:c r="L33"/>
@@ -2159,9 +2095,7 @@
       <s:c r="F34" s="14" t="n">
         <s:v>4814.5</s:v>
       </s:c>
-      <s:c r="G34" s="15" t="n">
-        <s:v>6955.79</s:v>
-      </s:c>
+      <s:c r="G34" s="15"/>
       <s:c r="J34"/>
       <s:c r="K34"/>
       <s:c r="L34"/>
@@ -2183,9 +2117,7 @@
       <s:c r="F35" s="14" t="n">
         <s:v>5160.6</s:v>
       </s:c>
-      <s:c r="G35" s="15" t="n">
-        <s:v>7489.12</s:v>
-      </s:c>
+      <s:c r="G35" s="15"/>
       <s:c r="J35"/>
       <s:c r="K35"/>
       <s:c r="L35"/>
@@ -2207,9 +2139,7 @@
       <s:c r="F36" s="14" t="n">
         <s:v>5274.2</s:v>
       </s:c>
-      <s:c r="G36" s="15" t="n">
-        <s:v>7833.91</s:v>
-      </s:c>
+      <s:c r="G36" s="15"/>
       <s:c r="J36"/>
       <s:c r="K36"/>
       <s:c r="L36"/>
@@ -2231,9 +2161,7 @@
       <s:c r="F37" s="14" t="n">
         <s:v>5208</s:v>
       </s:c>
-      <s:c r="G37" s="15" t="n">
-        <s:v>9152.81</s:v>
-      </s:c>
+      <s:c r="G37" s="15"/>
       <s:c r="J37"/>
       <s:c r="K37"/>
       <s:c r="L37"/>
@@ -2255,9 +2183,7 @@
       <s:c r="F38" s="14" t="n">
         <s:v>5621.7</s:v>
       </s:c>
-      <s:c r="G38" s="15" t="n">
-        <s:v>9225.33</s:v>
-      </s:c>
+      <s:c r="G38" s="15"/>
       <s:c r="J38"/>
       <s:c r="K38"/>
       <s:c r="L38"/>
@@ -2279,9 +2205,7 @@
       <s:c r="F39" s="14" t="n">
         <s:v>5961.4</s:v>
       </s:c>
-      <s:c r="G39" s="15" t="n">
-        <s:v>8831.05</s:v>
-      </s:c>
+      <s:c r="G39" s="15"/>
       <s:c r="J39"/>
       <s:c r="K39"/>
       <s:c r="L39"/>
@@ -2303,9 +2227,7 @@
       <s:c r="F40" s="14" t="n">
         <s:v>6409.4</s:v>
       </s:c>
-      <s:c r="G40" s="15" t="n">
-        <s:v>9165.93</s:v>
-      </s:c>
+      <s:c r="G40" s="15"/>
       <s:c r="J40"/>
       <s:c r="K40"/>
       <s:c r="L40"/>
@@ -2327,9 +2249,7 @@
       <s:c r="F41" s="14" t="n">
         <s:v>6975</s:v>
       </s:c>
-      <s:c r="G41" s="15" t="n">
-        <s:v>9181.17</s:v>
-      </s:c>
+      <s:c r="G41" s="15"/>
       <s:c r="J41"/>
       <s:c r="K41"/>
       <s:c r="L41"/>
@@ -2351,9 +2271,7 @@
       <s:c r="F42" s="14" t="n">
         <s:v>7256.9</s:v>
       </s:c>
-      <s:c r="G42" s="15" t="n">
-        <s:v>9313.31</s:v>
-      </s:c>
+      <s:c r="G42" s="15"/>
       <s:c r="J42"/>
       <s:c r="K42"/>
       <s:c r="L42"/>
@@ -2375,9 +2293,7 @@
       <s:c r="F43" s="14" t="n">
         <s:v>7572.6</s:v>
       </s:c>
-      <s:c r="G43" s="15" t="n">
-        <s:v>9165.76</s:v>
-      </s:c>
+      <s:c r="G43" s="15"/>
       <s:c r="J43"/>
       <s:c r="K43"/>
       <s:c r="L43"/>
@@ -2399,9 +2315,7 @@
       <s:c r="F44" s="14" t="n">
         <s:v>7840.6</s:v>
       </s:c>
-      <s:c r="G44" s="15" t="n">
-        <s:v>9237.29</s:v>
-      </s:c>
+      <s:c r="G44" s="15"/>
       <s:c r="J44"/>
       <s:c r="K44"/>
       <s:c r="L44"/>
@@ -2423,9 +2337,7 @@
       <s:c r="F45" s="14" t="n">
         <s:v>8284.3</s:v>
       </s:c>
-      <s:c r="G45" s="15" t="n">
-        <s:v>9091.86</s:v>
-      </s:c>
+      <s:c r="G45" s="15"/>
       <s:c r="J45"/>
       <s:c r="K45"/>
       <s:c r="L45"/>
@@ -2447,9 +2359,7 @@
       <s:c r="F46" s="14" t="n">
         <s:v>8294.4</s:v>
       </s:c>
-      <s:c r="G46" s="15" t="n">
-        <s:v>9231.24</s:v>
-      </s:c>
+      <s:c r="G46" s="15"/>
       <s:c r="J46"/>
       <s:c r="K46"/>
       <s:c r="L46"/>
@@ -2471,9 +2381,7 @@
       <s:c r="F47" s="14" t="n">
         <s:v>8614.2</s:v>
       </s:c>
-      <s:c r="G47" s="15" t="n">
-        <s:v>8387.81</s:v>
-      </s:c>
+      <s:c r="G47" s="15"/>
       <s:c r="J47"/>
       <s:c r="K47"/>
       <s:c r="L47"/>
@@ -2495,9 +2403,7 @@
       <s:c r="F48" s="14" t="n">
         <s:v>9096.1</s:v>
       </s:c>
-      <s:c r="G48" s="15" t="n">
-        <s:v>7908.52</s:v>
-      </s:c>
+      <s:c r="G48" s="15"/>
       <s:c r="J48"/>
       <s:c r="K48"/>
       <s:c r="L48"/>
@@ -2519,9 +2425,7 @@
       <s:c r="F49" s="14" t="n">
         <s:v>9394</s:v>
       </s:c>
-      <s:c r="G49" s="15" t="n">
-        <s:v>7374.35</s:v>
-      </s:c>
+      <s:c r="G49" s="15"/>
       <s:c r="J49"/>
       <s:c r="K49"/>
       <s:c r="L49"/>
@@ -2543,9 +2447,7 @@
       <s:c r="F50" s="14" t="n">
         <s:v>9552.8</s:v>
       </s:c>
-      <s:c r="G50" s="15" t="n">
-        <s:v>6907.48</s:v>
-      </s:c>
+      <s:c r="G50" s="15"/>
       <s:c r="J50"/>
       <s:c r="K50"/>
       <s:c r="L50"/>
@@ -2567,9 +2469,7 @@
       <s:c r="F51" s="14" t="n">
         <s:v>9600.4</s:v>
       </s:c>
-      <s:c r="G51" s="15" t="n">
-        <s:v>6983</s:v>
-      </s:c>
+      <s:c r="G51" s="15"/>
       <s:c r="J51"/>
       <s:c r="K51"/>
       <s:c r="L51"/>
@@ -2591,9 +2491,7 @@
       <s:c r="F52" s="14" t="n">
         <s:v>9459.4</s:v>
       </s:c>
-      <s:c r="G52" s="15" t="n">
-        <s:v>6647.74</s:v>
-      </s:c>
+      <s:c r="G52" s="15"/>
       <s:c r="J52"/>
       <s:c r="K52"/>
       <s:c r="L52"/>
@@ -2615,9 +2513,7 @@
       <s:c r="F53" s="14" t="n">
         <s:v>8916.6</s:v>
       </s:c>
-      <s:c r="G53" s="15" t="n">
-        <s:v>7027.79</s:v>
-      </s:c>
+      <s:c r="G53" s="15"/>
       <s:c r="J53"/>
       <s:c r="K53"/>
       <s:c r="L53"/>
@@ -2639,9 +2535,7 @@
       <s:c r="F54" s="14" t="n">
         <s:v>8617.9</s:v>
       </s:c>
-      <s:c r="G54" s="15" t="n">
-        <s:v>6900.79</s:v>
-      </s:c>
+      <s:c r="G54" s="15"/>
       <s:c r="J54"/>
       <s:c r="K54"/>
       <s:c r="L54"/>
@@ -2663,9 +2557,7 @@
       <s:c r="F55" s="14" t="n">
         <s:v>8524.2</s:v>
       </s:c>
-      <s:c r="G55" s="15" t="n">
-        <s:v>7337.19</s:v>
-      </s:c>
+      <s:c r="G55" s="15"/>
       <s:c r="J55"/>
       <s:c r="K55"/>
       <s:c r="L55"/>
@@ -2687,9 +2579,7 @@
       <s:c r="F56" s="14" t="n">
         <s:v>8352.2</s:v>
       </s:c>
-      <s:c r="G56" s="15" t="n">
-        <s:v>7239.22</s:v>
-      </s:c>
+      <s:c r="G56" s="15"/>
       <s:c r="J56"/>
       <s:c r="K56"/>
       <s:c r="L56"/>
@@ -2711,9 +2601,7 @@
       <s:c r="F57" s="14" t="n">
         <s:v>7959.3</s:v>
       </s:c>
-      <s:c r="G57" s="15" t="n">
-        <s:v>7908.82</s:v>
-      </s:c>
+      <s:c r="G57" s="15"/>
       <s:c r="J57"/>
       <s:c r="K57"/>
       <s:c r="L57"/>
@@ -2735,9 +2623,7 @@
       <s:c r="F58" s="14" t="n">
         <s:v>7565.2</s:v>
       </s:c>
-      <s:c r="G58" s="15" t="n">
-        <s:v>8151.77</s:v>
-      </s:c>
+      <s:c r="G58" s="15"/>
       <s:c r="J58"/>
       <s:c r="K58"/>
       <s:c r="L58"/>
@@ -2759,9 +2645,7 @@
       <s:c r="F59" s="14" t="n">
         <s:v>7378.9</s:v>
       </s:c>
-      <s:c r="G59" s="15" t="n">
-        <s:v>8850.45</s:v>
-      </s:c>
+      <s:c r="G59" s="15"/>
       <s:c r="J59"/>
       <s:c r="K59"/>
       <s:c r="L59"/>
@@ -2783,9 +2667,7 @@
       <s:c r="F60" s="14" t="n">
         <s:v>7311.1</s:v>
       </s:c>
-      <s:c r="G60" s="15" t="n">
-        <s:v>8586.32</s:v>
-      </s:c>
+      <s:c r="G60" s="15"/>
       <s:c r="J60"/>
       <s:c r="K60"/>
       <s:c r="L60"/>
@@ -2807,9 +2689,7 @@
       <s:c r="F61" s="14" t="n">
         <s:v>7199.3</s:v>
       </s:c>
-      <s:c r="G61" s="15" t="n">
-        <s:v>8308.32</s:v>
-      </s:c>
+      <s:c r="G61" s="15"/>
       <s:c r="J61"/>
       <s:c r="K61"/>
       <s:c r="L61"/>
@@ -2831,9 +2711,7 @@
       <s:c r="F62" s="14" t="n">
         <s:v>6772.6</s:v>
       </s:c>
-      <s:c r="G62" s="15" t="n">
-        <s:v>8264.8</s:v>
-      </s:c>
+      <s:c r="G62" s="15"/>
       <s:c r="J62"/>
       <s:c r="K62"/>
       <s:c r="L62"/>
@@ -2855,9 +2733,7 @@
       <s:c r="F63" s="14" t="n">
         <s:v>6437.2</s:v>
       </s:c>
-      <s:c r="G63" s="15" t="n">
-        <s:v>8649.28</s:v>
-      </s:c>
+      <s:c r="G63" s="15"/>
       <s:c r="J63"/>
       <s:c r="K63"/>
       <s:c r="L63"/>
@@ -2879,9 +2755,7 @@
       <s:c r="F64" s="14" t="n">
         <s:v>6406.7</s:v>
       </s:c>
-      <s:c r="G64" s="15" t="n">
-        <s:v>8439.18</s:v>
-      </s:c>
+      <s:c r="G64" s="15"/>
       <s:c r="J64"/>
       <s:c r="K64"/>
       <s:c r="L64"/>
@@ -2903,9 +2777,7 @@
       <s:c r="F65" s="14" t="n">
         <s:v>6322.9</s:v>
       </s:c>
-      <s:c r="G65" s="15" t="n">
-        <s:v>8556.46</s:v>
-      </s:c>
+      <s:c r="G65" s="15"/>
       <s:c r="J65"/>
       <s:c r="K65"/>
       <s:c r="L65"/>
@@ -2927,9 +2799,7 @@
       <s:c r="F66" s="14" t="n">
         <s:v>6288</s:v>
       </s:c>
-      <s:c r="G66" s="15" t="n">
-        <s:v>8368.94</s:v>
-      </s:c>
+      <s:c r="G66" s="15"/>
       <s:c r="J66"/>
       <s:c r="K66"/>
       <s:c r="L66"/>
@@ -2951,9 +2821,7 @@
       <s:c r="F67" s="14" t="n">
         <s:v>6068.7</s:v>
       </s:c>
-      <s:c r="G67" s="15" t="n">
-        <s:v>8401.96</s:v>
-      </s:c>
+      <s:c r="G67" s="15"/>
       <s:c r="J67"/>
       <s:c r="K67"/>
       <s:c r="L67"/>
@@ -2975,9 +2843,7 @@
       <s:c r="F68" s="14" t="n">
         <s:v>5722.7</s:v>
       </s:c>
-      <s:c r="G68" s="15" t="n">
-        <s:v>8330.35</s:v>
-      </s:c>
+      <s:c r="G68" s="15"/>
       <s:c r="J68"/>
       <s:c r="K68"/>
       <s:c r="L68"/>
@@ -2999,9 +2865,7 @@
       <s:c r="F69" s="14" t="n">
         <s:v>5248.6</s:v>
       </s:c>
-      <s:c r="G69" s="15" t="n">
-        <s:v>8327.28</s:v>
-      </s:c>
+      <s:c r="G69" s="15"/>
       <s:c r="J69"/>
       <s:c r="K69"/>
       <s:c r="L69"/>
@@ -3023,9 +2887,7 @@
       <s:c r="F70" s="14" t="n">
         <s:v>5238.6</s:v>
       </s:c>
-      <s:c r="G70" s="15" t="n">
-        <s:v>8646.31</s:v>
-      </s:c>
+      <s:c r="G70" s="15"/>
       <s:c r="J70"/>
       <s:c r="K70"/>
       <s:c r="L70"/>
@@ -3047,9 +2909,7 @@
       <s:c r="F71" s="14" t="n">
         <s:v>5246.1</s:v>
       </s:c>
-      <s:c r="G71" s="15" t="n">
-        <s:v>9176.74</s:v>
-      </s:c>
+      <s:c r="G71" s="15"/>
       <s:c r="J71"/>
       <s:c r="K71"/>
       <s:c r="L71"/>
@@ -3071,9 +2931,7 @@
       <s:c r="F72" s="14" t="n">
         <s:v>5403.3</s:v>
       </s:c>
-      <s:c r="G72" s="15" t="n">
-        <s:v>10054.34</s:v>
-      </s:c>
+      <s:c r="G72" s="15"/>
       <s:c r="J72"/>
       <s:c r="K72"/>
       <s:c r="L72"/>
@@ -3095,9 +2953,7 @@
       <s:c r="F73" s="14" t="n">
         <s:v>5416</s:v>
       </s:c>
-      <s:c r="G73" s="15" t="n">
-        <s:v>10756.3</s:v>
-      </s:c>
+      <s:c r="G73" s="15"/>
       <s:c r="J73"/>
       <s:c r="K73"/>
       <s:c r="L73"/>
@@ -3119,9 +2975,7 @@
       <s:c r="F74" s="14" t="n">
         <s:v>5092.4</s:v>
       </s:c>
-      <s:c r="G74" s="15" t="n">
-        <s:v>11284.59</s:v>
-      </s:c>
+      <s:c r="G74" s="15"/>
       <s:c r="J74"/>
       <s:c r="K74"/>
       <s:c r="L74"/>
@@ -3143,9 +2997,7 @@
       <s:c r="F75" s="14" t="n">
         <s:v>4773.4</s:v>
       </s:c>
-      <s:c r="G75" s="15" t="n">
-        <s:v>11228.44</s:v>
-      </s:c>
+      <s:c r="G75" s="15"/>
       <s:c r="J75"/>
       <s:c r="K75"/>
       <s:c r="L75"/>
@@ -3167,9 +3019,7 @@
       <s:c r="F76" s="14" t="n">
         <s:v>4585.2</s:v>
       </s:c>
-      <s:c r="G76" s="15" t="n">
-        <s:v>11336.77</s:v>
-      </s:c>
+      <s:c r="G76" s="15"/>
       <s:c r="J76"/>
       <s:c r="K76"/>
       <s:c r="L76"/>
@@ -3191,9 +3041,7 @@
       <s:c r="F77" s="14" t="n">
         <s:v>4609</s:v>
       </s:c>
-      <s:c r="G77" s="15" t="n">
-        <s:v>11283.36</s:v>
-      </s:c>
+      <s:c r="G77" s="15"/>
       <s:c r="J77"/>
       <s:c r="K77"/>
       <s:c r="L77"/>
@@ -3215,9 +3063,7 @@
       <s:c r="F78" s="14" t="n">
         <s:v>4534.3</s:v>
       </s:c>
-      <s:c r="G78" s="15" t="n">
-        <s:v>11514.27</s:v>
-      </s:c>
+      <s:c r="G78" s="15"/>
       <s:c r="J78"/>
       <s:c r="K78"/>
       <s:c r="L78"/>
@@ -3239,9 +3085,7 @@
       <s:c r="F79" s="14" t="n">
         <s:v>4198.5</s:v>
       </s:c>
-      <s:c r="G79" s="15" t="n">
-        <s:v>11904.52</s:v>
-      </s:c>
+      <s:c r="G79" s="15"/>
       <s:c r="J79"/>
       <s:c r="K79"/>
       <s:c r="L79"/>
@@ -3263,9 +3107,7 @@
       <s:c r="F80" s="14" t="n">
         <s:v>4484.9</s:v>
       </s:c>
-      <s:c r="G80" s="15" t="n">
-        <s:v>11704</s:v>
-      </s:c>
+      <s:c r="G80" s="15"/>
       <s:c r="J80"/>
       <s:c r="K80"/>
       <s:c r="L80"/>
@@ -3287,9 +3129,7 @@
       <s:c r="F81" s="14" t="n">
         <s:v>4366.5</s:v>
       </s:c>
-      <s:c r="G81" s="15" t="n">
-        <s:v>11613.39</s:v>
-      </s:c>
+      <s:c r="G81" s="15"/>
       <s:c r="J81"/>
       <s:c r="K81"/>
       <s:c r="L81"/>
@@ -3311,9 +3151,7 @@
       <s:c r="F82" s="14" t="n">
         <s:v>4039.4</s:v>
       </s:c>
-      <s:c r="G82" s="15" t="n">
-        <s:v>11726.49</s:v>
-      </s:c>
+      <s:c r="G82" s="15"/>
       <s:c r="J82"/>
       <s:c r="K82"/>
       <s:c r="L82"/>
@@ -3335,9 +3173,7 @@
       <s:c r="F83" s="14" t="n">
         <s:v>3763.7</s:v>
       </s:c>
-      <s:c r="G83" s="15" t="n">
-        <s:v>11561.38</s:v>
-      </s:c>
+      <s:c r="G83" s="15"/>
       <s:c r="J83"/>
       <s:c r="K83"/>
       <s:c r="L83"/>
@@ -3359,9 +3195,7 @@
       <s:c r="F84" s="14" t="n">
         <s:v>3713.4</s:v>
       </s:c>
-      <s:c r="G84" s="15" t="n">
-        <s:v>11544.92</s:v>
-      </s:c>
+      <s:c r="G84" s="15"/>
       <s:c r="J84"/>
       <s:c r="K84"/>
       <s:c r="L84"/>
@@ -3383,9 +3217,7 @@
       <s:c r="F85" s="14" t="n">
         <s:v>3857.4</s:v>
       </s:c>
-      <s:c r="G85" s="15" t="n">
-        <s:v>11501.36</s:v>
-      </s:c>
+      <s:c r="G85" s="15"/>
       <s:c r="J85"/>
       <s:c r="K85"/>
       <s:c r="L85"/>
@@ -3407,9 +3239,7 @@
       <s:c r="F86" s="14" t="n">
         <s:v>3753.8</s:v>
       </s:c>
-      <s:c r="G86" s="15" t="n">
-        <s:v>11276.5</s:v>
-      </s:c>
+      <s:c r="G86" s="15"/>
       <s:c r="J86"/>
       <s:c r="K86"/>
       <s:c r="L86"/>
@@ -3431,9 +3261,7 @@
       <s:c r="F87" s="14" t="n">
         <s:v>3763.1</s:v>
       </s:c>
-      <s:c r="G87" s="15" t="n">
-        <s:v>10741.23</s:v>
-      </s:c>
+      <s:c r="G87" s="15"/>
       <s:c r="J87"/>
       <s:c r="K87"/>
       <s:c r="L87"/>
@@ -3455,9 +3283,7 @@
       <s:c r="F88" s="14" t="n">
         <s:v>3915.7</s:v>
       </s:c>
-      <s:c r="G88" s="15" t="n">
-        <s:v>10118.53</s:v>
-      </s:c>
+      <s:c r="G88" s="15"/>
       <s:c r="J88"/>
       <s:c r="K88"/>
       <s:c r="L88"/>
@@ -3479,9 +3305,7 @@
       <s:c r="F89" s="14" t="n">
         <s:v>3871.5</s:v>
       </s:c>
-      <s:c r="G89" s="15" t="n">
-        <s:v>9838.66</s:v>
-      </s:c>
+      <s:c r="G89" s="15"/>
       <s:c r="J89"/>
       <s:c r="K89"/>
       <s:c r="L89"/>
@@ -3503,9 +3327,7 @@
       <s:c r="F90" s="14" t="n">
         <s:v>3602.4</s:v>
       </s:c>
-      <s:c r="G90" s="15" t="n">
-        <s:v>9013.66</s:v>
-      </s:c>
+      <s:c r="G90" s="15"/>
       <s:c r="J90"/>
       <s:c r="K90"/>
       <s:c r="L90"/>
@@ -3527,9 +3349,7 @@
       <s:c r="F91" s="14" t="n">
         <s:v>3371.6</s:v>
       </s:c>
-      <s:c r="G91" s="15" t="n">
-        <s:v>8329.48</s:v>
-      </s:c>
+      <s:c r="G91" s="15"/>
       <s:c r="J91"/>
       <s:c r="K91"/>
       <s:c r="L91"/>
@@ -3551,9 +3371,7 @@
       <s:c r="F92" s="14" t="n">
         <s:v>3112.6</s:v>
       </s:c>
-      <s:c r="G92" s="15" t="n">
-        <s:v>7364.94</s:v>
-      </s:c>
+      <s:c r="G92" s="15"/>
       <s:c r="J92"/>
       <s:c r="K92"/>
       <s:c r="L92"/>
@@ -3575,9 +3393,7 @@
       <s:c r="F93" s="14" t="n">
         <s:v>2951.2</s:v>
       </s:c>
-      <s:c r="G93" s="15" t="n">
-        <s:v>6831.04</s:v>
-      </s:c>
+      <s:c r="G93" s="15"/>
       <s:c r="J93"/>
       <s:c r="K93"/>
       <s:c r="L93"/>
@@ -3599,9 +3415,7 @@
       <s:c r="F94" s="14" t="n">
         <s:v>2976</s:v>
       </s:c>
-      <s:c r="G94" s="15" t="n">
-        <s:v>6223.79</s:v>
-      </s:c>
+      <s:c r="G94" s="15"/>
       <s:c r="J94"/>
       <s:c r="K94"/>
       <s:c r="L94"/>
@@ -3623,9 +3437,7 @@
       <s:c r="F95" s="14" t="n">
         <s:v>2942</s:v>
       </s:c>
-      <s:c r="G95" s="15" t="n">
-        <s:v>6222.08</s:v>
-      </s:c>
+      <s:c r="G95" s="15"/>
       <s:c r="J95"/>
       <s:c r="K95"/>
       <s:c r="L95"/>
@@ -3647,9 +3459,7 @@
       <s:c r="F96" s="14" t="n">
         <s:v>2910.3</s:v>
       </s:c>
-      <s:c r="G96" s="15" t="n">
-        <s:v>6097.34</s:v>
-      </s:c>
+      <s:c r="G96" s="15"/>
       <s:c r="J96"/>
       <s:c r="K96"/>
       <s:c r="L96"/>
@@ -3673,9 +3483,7 @@
       <s:c r="F97" s="14" t="n">
         <s:v>2872.9</s:v>
       </s:c>
-      <s:c r="G97" s="15" t="n">
-        <s:v>5928.24</s:v>
-      </s:c>
+      <s:c r="G97" s="15"/>
       <s:c r="J97"/>
       <s:c r="K97"/>
       <s:c r="L97"/>
@@ -3860,17 +3668,39 @@
       <s:c r="E2" s="1" t="n">
         <s:v>392.95</s:v>
       </s:c>
-      <s:c r="F2" s="1"/>
-      <s:c r="G2" s="1"/>
-      <s:c r="H2" s="1"/>
-      <s:c r="I2" s="1"/>
-      <s:c r="J2" s="1"/>
-      <s:c r="K2" s="1"/>
-      <s:c r="L2" s="1"/>
-      <s:c r="M2" s="1"/>
-      <s:c r="N2" s="1"/>
-      <s:c r="O2" s="1"/>
-      <s:c r="P2" s="1"/>
+      <s:c r="F2" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G2" s="1" t="n">
+        <s:v>2322.54</s:v>
+      </s:c>
+      <s:c r="H2" s="1" t="n">
+        <s:v>1.12</s:v>
+      </s:c>
+      <s:c r="I2" s="1" t="n">
+        <s:v>3.65</s:v>
+      </s:c>
+      <s:c r="J2" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K2" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L2" s="1" t="n">
+        <s:v>714.29</s:v>
+      </s:c>
+      <s:c r="M2" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N2" s="1" t="n">
+        <s:v>23119.09</s:v>
+      </s:c>
+      <s:c r="O2" s="1" t="n">
+        <s:v>4087.2</s:v>
+      </s:c>
+      <s:c r="P2" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="3" s="1" customFormat="1" spans="1:16">
       <s:c r="A3" s="6" t="n">
@@ -3888,17 +3718,39 @@
       <s:c r="E3" s="1" t="n">
         <s:v>392.95</s:v>
       </s:c>
-      <s:c r="F3" s="1"/>
-      <s:c r="G3" s="1"/>
-      <s:c r="H3" s="1"/>
-      <s:c r="I3" s="1"/>
-      <s:c r="J3" s="1"/>
-      <s:c r="K3" s="1"/>
-      <s:c r="L3" s="1"/>
-      <s:c r="M3" s="1"/>
-      <s:c r="N3" s="1"/>
-      <s:c r="O3" s="1"/>
-      <s:c r="P3" s="1"/>
+      <s:c r="F3" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G3" s="1" t="n">
+        <s:v>2309.75</s:v>
+      </s:c>
+      <s:c r="H3" s="1" t="n">
+        <s:v>1.12</s:v>
+      </s:c>
+      <s:c r="I3" s="1" t="n">
+        <s:v>3.65</s:v>
+      </s:c>
+      <s:c r="J3" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K3" s="1" t="n">
+        <s:v>299.7</s:v>
+      </s:c>
+      <s:c r="L3" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M3" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N3" s="1" t="n">
+        <s:v>22683.17</s:v>
+      </s:c>
+      <s:c r="O3" s="1" t="n">
+        <s:v>4196.4</s:v>
+      </s:c>
+      <s:c r="P3" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="4" s="1" customFormat="1" spans="1:16">
       <s:c r="A4" s="6" t="n">
@@ -3916,17 +3768,39 @@
       <s:c r="E4" s="1" t="n">
         <s:v>413.44</s:v>
       </s:c>
-      <s:c r="F4" s="1"/>
-      <s:c r="G4" s="1"/>
-      <s:c r="H4" s="1"/>
-      <s:c r="I4" s="1"/>
-      <s:c r="J4" s="1"/>
-      <s:c r="K4" s="1"/>
-      <s:c r="L4" s="1"/>
-      <s:c r="M4" s="1"/>
-      <s:c r="N4" s="1"/>
-      <s:c r="O4" s="1"/>
-      <s:c r="P4" s="1"/>
+      <s:c r="F4" s="1" t="n">
+        <s:v>30</s:v>
+      </s:c>
+      <s:c r="G4" s="1" t="n">
+        <s:v>2279.06</s:v>
+      </s:c>
+      <s:c r="H4" s="1" t="n">
+        <s:v>1.12</s:v>
+      </s:c>
+      <s:c r="I4" s="1" t="n">
+        <s:v>3.65</s:v>
+      </s:c>
+      <s:c r="J4" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K4" s="1" t="n">
+        <s:v>301.4</s:v>
+      </s:c>
+      <s:c r="L4" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M4" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N4" s="1" t="n">
+        <s:v>22532.01</s:v>
+      </s:c>
+      <s:c r="O4" s="1" t="n">
+        <s:v>4281.26</s:v>
+      </s:c>
+      <s:c r="P4" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="5" s="1" customFormat="1" spans="1:16">
       <s:c r="A5" s="6" t="n">
@@ -3944,17 +3818,39 @@
       <s:c r="E5" s="1" t="n">
         <s:v>422.33</s:v>
       </s:c>
-      <s:c r="F5" s="1"/>
-      <s:c r="G5" s="1"/>
-      <s:c r="H5" s="1"/>
-      <s:c r="I5" s="1"/>
-      <s:c r="J5" s="1"/>
-      <s:c r="K5" s="1"/>
-      <s:c r="L5" s="1"/>
-      <s:c r="M5" s="1"/>
-      <s:c r="N5" s="1"/>
-      <s:c r="O5" s="1"/>
-      <s:c r="P5" s="1"/>
+      <s:c r="F5" s="1" t="n">
+        <s:v>30</s:v>
+      </s:c>
+      <s:c r="G5" s="1" t="n">
+        <s:v>2269.37</s:v>
+      </s:c>
+      <s:c r="H5" s="1" t="n">
+        <s:v>1.12</s:v>
+      </s:c>
+      <s:c r="I5" s="1" t="n">
+        <s:v>3.65</s:v>
+      </s:c>
+      <s:c r="J5" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K5" s="1" t="n">
+        <s:v>301.1</s:v>
+      </s:c>
+      <s:c r="L5" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M5" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N5" s="1" t="n">
+        <s:v>22175.41</s:v>
+      </s:c>
+      <s:c r="O5" s="1" t="n">
+        <s:v>4362.45</s:v>
+      </s:c>
+      <s:c r="P5" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="6" s="1" customFormat="1" spans="1:16">
       <s:c r="A6" s="6" t="n">
@@ -3972,17 +3868,39 @@
       <s:c r="E6" s="1" t="n">
         <s:v>441.42</s:v>
       </s:c>
-      <s:c r="F6" s="1"/>
-      <s:c r="G6" s="1"/>
-      <s:c r="H6" s="1"/>
-      <s:c r="I6" s="1"/>
-      <s:c r="J6" s="1"/>
-      <s:c r="K6" s="1"/>
-      <s:c r="L6" s="1"/>
-      <s:c r="M6" s="1"/>
-      <s:c r="N6" s="1"/>
-      <s:c r="O6" s="1"/>
-      <s:c r="P6" s="1"/>
+      <s:c r="F6" s="1" t="n">
+        <s:v>30</s:v>
+      </s:c>
+      <s:c r="G6" s="1" t="n">
+        <s:v>2245.81</s:v>
+      </s:c>
+      <s:c r="H6" s="1" t="n">
+        <s:v>1.12</s:v>
+      </s:c>
+      <s:c r="I6" s="1" t="n">
+        <s:v>3.65</s:v>
+      </s:c>
+      <s:c r="J6" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K6" s="1" t="n">
+        <s:v>605.8</s:v>
+      </s:c>
+      <s:c r="L6" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M6" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N6" s="1" t="n">
+        <s:v>23360.6</s:v>
+      </s:c>
+      <s:c r="O6" s="1" t="n">
+        <s:v>4335.91</s:v>
+      </s:c>
+      <s:c r="P6" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="7" s="1" customFormat="1" spans="1:16">
       <s:c r="A7" s="6" t="n">
@@ -4000,17 +3918,39 @@
       <s:c r="E7" s="1" t="n">
         <s:v>440.7</s:v>
       </s:c>
-      <s:c r="F7" s="1"/>
-      <s:c r="G7" s="1"/>
-      <s:c r="H7" s="1"/>
-      <s:c r="I7" s="1"/>
-      <s:c r="J7" s="1"/>
-      <s:c r="K7" s="1"/>
-      <s:c r="L7" s="1"/>
-      <s:c r="M7" s="1"/>
-      <s:c r="N7" s="1"/>
-      <s:c r="O7" s="1"/>
-      <s:c r="P7" s="1"/>
+      <s:c r="F7" s="1" t="n">
+        <s:v>30</s:v>
+      </s:c>
+      <s:c r="G7" s="1" t="n">
+        <s:v>2240.22</s:v>
+      </s:c>
+      <s:c r="H7" s="1" t="n">
+        <s:v>1.12</s:v>
+      </s:c>
+      <s:c r="I7" s="1" t="n">
+        <s:v>3.65</s:v>
+      </s:c>
+      <s:c r="J7" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K7" s="1" t="n">
+        <s:v>548.7</s:v>
+      </s:c>
+      <s:c r="L7" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M7" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N7" s="1" t="n">
+        <s:v>23228.79</s:v>
+      </s:c>
+      <s:c r="O7" s="1" t="n">
+        <s:v>4359.41</s:v>
+      </s:c>
+      <s:c r="P7" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="8" s="1" customFormat="1" spans="1:16">
       <s:c r="A8" s="6" t="n">
@@ -4028,17 +3968,39 @@
       <s:c r="E8" s="1" t="n">
         <s:v>441.48</s:v>
       </s:c>
-      <s:c r="F8" s="1"/>
-      <s:c r="G8" s="1"/>
-      <s:c r="H8" s="1"/>
-      <s:c r="I8" s="1"/>
-      <s:c r="J8" s="1"/>
-      <s:c r="K8" s="1"/>
-      <s:c r="L8" s="1"/>
-      <s:c r="M8" s="1"/>
-      <s:c r="N8" s="1"/>
-      <s:c r="O8" s="1"/>
-      <s:c r="P8" s="1"/>
+      <s:c r="F8" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G8" s="1" t="n">
+        <s:v>2230.16</s:v>
+      </s:c>
+      <s:c r="H8" s="1" t="n">
+        <s:v>1.12</s:v>
+      </s:c>
+      <s:c r="I8" s="1" t="n">
+        <s:v>3.65</s:v>
+      </s:c>
+      <s:c r="J8" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K8" s="1" t="n">
+        <s:v>549.3</s:v>
+      </s:c>
+      <s:c r="L8" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M8" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N8" s="1" t="n">
+        <s:v>23403.42</s:v>
+      </s:c>
+      <s:c r="O8" s="1" t="n">
+        <s:v>4194.14</s:v>
+      </s:c>
+      <s:c r="P8" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="9" s="1" customFormat="1" spans="1:16">
       <s:c r="A9" s="6" t="n">
@@ -4056,17 +4018,39 @@
       <s:c r="E9" s="1" t="n">
         <s:v>423.6</s:v>
       </s:c>
-      <s:c r="F9" s="1"/>
-      <s:c r="G9" s="1"/>
-      <s:c r="H9" s="1"/>
-      <s:c r="I9" s="1"/>
-      <s:c r="J9" s="1"/>
-      <s:c r="K9" s="1"/>
-      <s:c r="L9" s="1"/>
-      <s:c r="M9" s="1"/>
-      <s:c r="N9" s="1"/>
-      <s:c r="O9" s="1"/>
-      <s:c r="P9" s="1"/>
+      <s:c r="F9" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G9" s="1" t="n">
+        <s:v>2244.01</s:v>
+      </s:c>
+      <s:c r="H9" s="1" t="n">
+        <s:v>1.12</s:v>
+      </s:c>
+      <s:c r="I9" s="1" t="n">
+        <s:v>3.65</s:v>
+      </s:c>
+      <s:c r="J9" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K9" s="1" t="n">
+        <s:v>553.1</s:v>
+      </s:c>
+      <s:c r="L9" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M9" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N9" s="1" t="n">
+        <s:v>22411.29</s:v>
+      </s:c>
+      <s:c r="O9" s="1" t="n">
+        <s:v>4148.93</s:v>
+      </s:c>
+      <s:c r="P9" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="10" s="1" customFormat="1" spans="1:16">
       <s:c r="A10" s="6" t="n">
@@ -4084,17 +4068,39 @@
       <s:c r="E10" s="1" t="n">
         <s:v>413.44</s:v>
       </s:c>
-      <s:c r="F10" s="1"/>
-      <s:c r="G10" s="1"/>
-      <s:c r="H10" s="1"/>
-      <s:c r="I10" s="1"/>
-      <s:c r="J10" s="1"/>
-      <s:c r="K10" s="1"/>
-      <s:c r="L10" s="1"/>
-      <s:c r="M10" s="1"/>
-      <s:c r="N10" s="1"/>
-      <s:c r="O10" s="1"/>
-      <s:c r="P10" s="1"/>
+      <s:c r="F10" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G10" s="1" t="n">
+        <s:v>2247.59</s:v>
+      </s:c>
+      <s:c r="H10" s="1" t="n">
+        <s:v>1.12</s:v>
+      </s:c>
+      <s:c r="I10" s="1" t="n">
+        <s:v>3.65</s:v>
+      </s:c>
+      <s:c r="J10" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K10" s="1" t="n">
+        <s:v>548.9</s:v>
+      </s:c>
+      <s:c r="L10" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M10" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N10" s="1" t="n">
+        <s:v>21972.15</s:v>
+      </s:c>
+      <s:c r="O10" s="1" t="n">
+        <s:v>4055.78</s:v>
+      </s:c>
+      <s:c r="P10" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="11" s="1" customFormat="1" spans="1:16">
       <s:c r="A11" s="6" t="n">
@@ -4112,17 +4118,39 @@
       <s:c r="E11" s="1" t="n">
         <s:v>392.42</s:v>
       </s:c>
-      <s:c r="F11" s="1"/>
-      <s:c r="G11" s="1"/>
-      <s:c r="H11" s="1"/>
-      <s:c r="I11" s="1"/>
-      <s:c r="J11" s="1"/>
-      <s:c r="K11" s="1"/>
-      <s:c r="L11" s="1"/>
-      <s:c r="M11" s="1"/>
-      <s:c r="N11" s="1"/>
-      <s:c r="O11" s="1"/>
-      <s:c r="P11" s="1"/>
+      <s:c r="F11" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G11" s="1" t="n">
+        <s:v>2301.7</s:v>
+      </s:c>
+      <s:c r="H11" s="1" t="n">
+        <s:v>1.12</s:v>
+      </s:c>
+      <s:c r="I11" s="1" t="n">
+        <s:v>3.65</s:v>
+      </s:c>
+      <s:c r="J11" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K11" s="1" t="n">
+        <s:v>549</s:v>
+      </s:c>
+      <s:c r="L11" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M11" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N11" s="1" t="n">
+        <s:v>21529.27</s:v>
+      </s:c>
+      <s:c r="O11" s="1" t="n">
+        <s:v>4011.36</s:v>
+      </s:c>
+      <s:c r="P11" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="12" s="1" customFormat="1" spans="1:16">
       <s:c r="A12" s="6" t="n">
@@ -4140,17 +4168,39 @@
       <s:c r="E12" s="1" t="n">
         <s:v>376.7</s:v>
       </s:c>
-      <s:c r="F12" s="1"/>
-      <s:c r="G12" s="1"/>
-      <s:c r="H12" s="1"/>
-      <s:c r="I12" s="1"/>
-      <s:c r="J12" s="1"/>
-      <s:c r="K12" s="1"/>
-      <s:c r="L12" s="1"/>
-      <s:c r="M12" s="1"/>
-      <s:c r="N12" s="1"/>
-      <s:c r="O12" s="1"/>
-      <s:c r="P12" s="1"/>
+      <s:c r="F12" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G12" s="1" t="n">
+        <s:v>2347.72</s:v>
+      </s:c>
+      <s:c r="H12" s="1" t="n">
+        <s:v>1.12</s:v>
+      </s:c>
+      <s:c r="I12" s="1" t="n">
+        <s:v>3.65</s:v>
+      </s:c>
+      <s:c r="J12" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K12" s="1" t="n">
+        <s:v>550.9</s:v>
+      </s:c>
+      <s:c r="L12" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M12" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N12" s="1" t="n">
+        <s:v>20883.13</s:v>
+      </s:c>
+      <s:c r="O12" s="1" t="n">
+        <s:v>4002.37</s:v>
+      </s:c>
+      <s:c r="P12" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="13" s="1" customFormat="1" spans="1:16">
       <s:c r="A13" s="6" t="n">
@@ -4168,17 +4218,39 @@
       <s:c r="E13" s="1" t="n">
         <s:v>363.86</s:v>
       </s:c>
-      <s:c r="F13" s="1"/>
-      <s:c r="G13" s="1"/>
-      <s:c r="H13" s="1"/>
-      <s:c r="I13" s="1"/>
-      <s:c r="J13" s="1"/>
-      <s:c r="K13" s="1"/>
-      <s:c r="L13" s="1"/>
-      <s:c r="M13" s="1"/>
-      <s:c r="N13" s="1"/>
-      <s:c r="O13" s="1"/>
-      <s:c r="P13" s="1"/>
+      <s:c r="F13" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G13" s="1" t="n">
+        <s:v>2343.87</s:v>
+      </s:c>
+      <s:c r="H13" s="1" t="n">
+        <s:v>1.12</s:v>
+      </s:c>
+      <s:c r="I13" s="1" t="n">
+        <s:v>3.65</s:v>
+      </s:c>
+      <s:c r="J13" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K13" s="1" t="n">
+        <s:v>548.1</s:v>
+      </s:c>
+      <s:c r="L13" s="1" t="n">
+        <s:v>651.68</s:v>
+      </s:c>
+      <s:c r="M13" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N13" s="1" t="n">
+        <s:v>20491.23</s:v>
+      </s:c>
+      <s:c r="O13" s="1" t="n">
+        <s:v>3980.65</s:v>
+      </s:c>
+      <s:c r="P13" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="14" s="1" customFormat="1" spans="1:16">
       <s:c r="A14" s="6" t="n">
@@ -4196,17 +4268,39 @@
       <s:c r="E14" s="1" t="n">
         <s:v>363.86</s:v>
       </s:c>
-      <s:c r="F14" s="1"/>
-      <s:c r="G14" s="1"/>
-      <s:c r="H14" s="1"/>
-      <s:c r="I14" s="1"/>
-      <s:c r="J14" s="1"/>
-      <s:c r="K14" s="1"/>
-      <s:c r="L14" s="1"/>
-      <s:c r="M14" s="1"/>
-      <s:c r="N14" s="1"/>
-      <s:c r="O14" s="1"/>
-      <s:c r="P14" s="1"/>
+      <s:c r="F14" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G14" s="1" t="n">
+        <s:v>2336.5</s:v>
+      </s:c>
+      <s:c r="H14" s="1" t="n">
+        <s:v>1.12</s:v>
+      </s:c>
+      <s:c r="I14" s="1" t="n">
+        <s:v>3.65</s:v>
+      </s:c>
+      <s:c r="J14" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K14" s="1" t="n">
+        <s:v>550.4</s:v>
+      </s:c>
+      <s:c r="L14" s="1" t="n">
+        <s:v>650.1</s:v>
+      </s:c>
+      <s:c r="M14" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N14" s="1" t="n">
+        <s:v>20460.28</s:v>
+      </s:c>
+      <s:c r="O14" s="1" t="n">
+        <s:v>3885.65</s:v>
+      </s:c>
+      <s:c r="P14" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="15" s="1" customFormat="1" spans="1:16">
       <s:c r="A15" s="6" t="n">
@@ -4224,17 +4318,39 @@
       <s:c r="E15" s="1" t="n">
         <s:v>364.54</s:v>
       </s:c>
-      <s:c r="F15" s="1"/>
-      <s:c r="G15" s="1"/>
-      <s:c r="H15" s="1"/>
-      <s:c r="I15" s="1"/>
-      <s:c r="J15" s="1"/>
-      <s:c r="K15" s="1"/>
-      <s:c r="L15" s="1"/>
-      <s:c r="M15" s="1"/>
-      <s:c r="N15" s="1"/>
-      <s:c r="O15" s="1"/>
-      <s:c r="P15" s="1"/>
+      <s:c r="F15" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G15" s="1" t="n">
+        <s:v>2317.11</s:v>
+      </s:c>
+      <s:c r="H15" s="1" t="n">
+        <s:v>1.12</s:v>
+      </s:c>
+      <s:c r="I15" s="1" t="n">
+        <s:v>3.65</s:v>
+      </s:c>
+      <s:c r="J15" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K15" s="1" t="n">
+        <s:v>548.7</s:v>
+      </s:c>
+      <s:c r="L15" s="1" t="n">
+        <s:v>245.24</s:v>
+      </s:c>
+      <s:c r="M15" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N15" s="1" t="n">
+        <s:v>20553.38</s:v>
+      </s:c>
+      <s:c r="O15" s="1" t="n">
+        <s:v>3894.1</s:v>
+      </s:c>
+      <s:c r="P15" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="16" s="1" customFormat="1" spans="1:16">
       <s:c r="A16" s="6" t="n">
@@ -4252,17 +4368,39 @@
       <s:c r="E16" s="1" t="n">
         <s:v>363.98</s:v>
       </s:c>
-      <s:c r="F16" s="1"/>
-      <s:c r="G16" s="1"/>
-      <s:c r="H16" s="1"/>
-      <s:c r="I16" s="1"/>
-      <s:c r="J16" s="1"/>
-      <s:c r="K16" s="1"/>
-      <s:c r="L16" s="1"/>
-      <s:c r="M16" s="1"/>
-      <s:c r="N16" s="1"/>
-      <s:c r="O16" s="1"/>
-      <s:c r="P16" s="1"/>
+      <s:c r="F16" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G16" s="1" t="n">
+        <s:v>2331.01</s:v>
+      </s:c>
+      <s:c r="H16" s="1" t="n">
+        <s:v>1.12</s:v>
+      </s:c>
+      <s:c r="I16" s="1" t="n">
+        <s:v>3.65</s:v>
+      </s:c>
+      <s:c r="J16" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K16" s="1" t="n">
+        <s:v>549.9</s:v>
+      </s:c>
+      <s:c r="L16" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M16" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N16" s="1" t="n">
+        <s:v>20482.41</s:v>
+      </s:c>
+      <s:c r="O16" s="1" t="n">
+        <s:v>3885.1</s:v>
+      </s:c>
+      <s:c r="P16" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="17" s="1" customFormat="1" spans="1:16">
       <s:c r="A17" s="6" t="n">
@@ -4280,17 +4418,39 @@
       <s:c r="E17" s="1" t="n">
         <s:v>363.2</s:v>
       </s:c>
-      <s:c r="F17" s="1"/>
-      <s:c r="G17" s="1"/>
-      <s:c r="H17" s="1"/>
-      <s:c r="I17" s="1"/>
-      <s:c r="J17" s="1"/>
-      <s:c r="K17" s="1"/>
-      <s:c r="L17" s="1"/>
-      <s:c r="M17" s="1"/>
-      <s:c r="N17" s="1"/>
-      <s:c r="O17" s="1"/>
-      <s:c r="P17" s="1"/>
+      <s:c r="F17" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G17" s="1" t="n">
+        <s:v>2317.3</s:v>
+      </s:c>
+      <s:c r="H17" s="1" t="n">
+        <s:v>1.12</s:v>
+      </s:c>
+      <s:c r="I17" s="1" t="n">
+        <s:v>3.65</s:v>
+      </s:c>
+      <s:c r="J17" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K17" s="1" t="n">
+        <s:v>550.2</s:v>
+      </s:c>
+      <s:c r="L17" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M17" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N17" s="1" t="n">
+        <s:v>20409.48</s:v>
+      </s:c>
+      <s:c r="O17" s="1" t="n">
+        <s:v>3710.44</s:v>
+      </s:c>
+      <s:c r="P17" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="18" s="1" customFormat="1" spans="1:16">
       <s:c r="A18" s="6" t="n">
@@ -4308,17 +4468,39 @@
       <s:c r="E18" s="1" t="n">
         <s:v>361.66</s:v>
       </s:c>
-      <s:c r="F18" s="1"/>
-      <s:c r="G18" s="1"/>
-      <s:c r="H18" s="1"/>
-      <s:c r="I18" s="1"/>
-      <s:c r="J18" s="1"/>
-      <s:c r="K18" s="1"/>
-      <s:c r="L18" s="1"/>
-      <s:c r="M18" s="1"/>
-      <s:c r="N18" s="1"/>
-      <s:c r="O18" s="1"/>
-      <s:c r="P18" s="1"/>
+      <s:c r="F18" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G18" s="1" t="n">
+        <s:v>2298.51</s:v>
+      </s:c>
+      <s:c r="H18" s="1" t="n">
+        <s:v>0.97</s:v>
+      </s:c>
+      <s:c r="I18" s="1" t="n">
+        <s:v>3.65</s:v>
+      </s:c>
+      <s:c r="J18" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K18" s="1" t="n">
+        <s:v>550</s:v>
+      </s:c>
+      <s:c r="L18" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M18" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N18" s="1" t="n">
+        <s:v>20090.52</s:v>
+      </s:c>
+      <s:c r="O18" s="1" t="n">
+        <s:v>3653.75</s:v>
+      </s:c>
+      <s:c r="P18" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="19" s="1" customFormat="1" spans="1:16">
       <s:c r="A19" s="6" t="n">
@@ -4336,17 +4518,39 @@
       <s:c r="E19" s="1" t="n">
         <s:v>363.2</s:v>
       </s:c>
-      <s:c r="F19" s="1"/>
-      <s:c r="G19" s="1"/>
-      <s:c r="H19" s="1"/>
-      <s:c r="I19" s="1"/>
-      <s:c r="J19" s="1"/>
-      <s:c r="K19" s="1"/>
-      <s:c r="L19" s="1"/>
-      <s:c r="M19" s="1"/>
-      <s:c r="N19" s="1"/>
-      <s:c r="O19" s="1"/>
-      <s:c r="P19" s="1"/>
+      <s:c r="F19" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G19" s="1" t="n">
+        <s:v>2291.79</s:v>
+      </s:c>
+      <s:c r="H19" s="1" t="n">
+        <s:v>0.97</s:v>
+      </s:c>
+      <s:c r="I19" s="1" t="n">
+        <s:v>3.65</s:v>
+      </s:c>
+      <s:c r="J19" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K19" s="1" t="n">
+        <s:v>547.3</s:v>
+      </s:c>
+      <s:c r="L19" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M19" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N19" s="1" t="n">
+        <s:v>20051.27</s:v>
+      </s:c>
+      <s:c r="O19" s="1" t="n">
+        <s:v>3594.22</s:v>
+      </s:c>
+      <s:c r="P19" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="20" s="1" customFormat="1" spans="1:16">
       <s:c r="A20" s="6" t="n">
@@ -4364,17 +4568,39 @@
       <s:c r="E20" s="1" t="n">
         <s:v>363.2</s:v>
       </s:c>
-      <s:c r="F20" s="1"/>
-      <s:c r="G20" s="1"/>
-      <s:c r="H20" s="1"/>
-      <s:c r="I20" s="1"/>
-      <s:c r="J20" s="1"/>
-      <s:c r="K20" s="1"/>
-      <s:c r="L20" s="1"/>
-      <s:c r="M20" s="1"/>
-      <s:c r="N20" s="1"/>
-      <s:c r="O20" s="1"/>
-      <s:c r="P20" s="1"/>
+      <s:c r="F20" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G20" s="1" t="n">
+        <s:v>2289.73</s:v>
+      </s:c>
+      <s:c r="H20" s="1" t="n">
+        <s:v>0.97</s:v>
+      </s:c>
+      <s:c r="I20" s="1" t="n">
+        <s:v>3.65</s:v>
+      </s:c>
+      <s:c r="J20" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K20" s="1" t="n">
+        <s:v>549.7</s:v>
+      </s:c>
+      <s:c r="L20" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M20" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N20" s="1" t="n">
+        <s:v>20024.18</s:v>
+      </s:c>
+      <s:c r="O20" s="1" t="n">
+        <s:v>3529.27</s:v>
+      </s:c>
+      <s:c r="P20" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="21" s="1" customFormat="1" spans="1:16">
       <s:c r="A21" s="6" t="n">
@@ -4392,17 +4618,39 @@
       <s:c r="E21" s="1" t="n">
         <s:v>364.54</s:v>
       </s:c>
-      <s:c r="F21" s="1"/>
-      <s:c r="G21" s="1"/>
-      <s:c r="H21" s="1"/>
-      <s:c r="I21" s="1"/>
-      <s:c r="J21" s="1"/>
-      <s:c r="K21" s="1"/>
-      <s:c r="L21" s="1"/>
-      <s:c r="M21" s="1"/>
-      <s:c r="N21" s="1"/>
-      <s:c r="O21" s="1"/>
-      <s:c r="P21" s="1"/>
+      <s:c r="F21" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G21" s="1" t="n">
+        <s:v>2290.15</s:v>
+      </s:c>
+      <s:c r="H21" s="1" t="n">
+        <s:v>0.97</s:v>
+      </s:c>
+      <s:c r="I21" s="1" t="n">
+        <s:v>3.65</s:v>
+      </s:c>
+      <s:c r="J21" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K21" s="1" t="n">
+        <s:v>551.1</s:v>
+      </s:c>
+      <s:c r="L21" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M21" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N21" s="1" t="n">
+        <s:v>20040.12</s:v>
+      </s:c>
+      <s:c r="O21" s="1" t="n">
+        <s:v>3311.91</s:v>
+      </s:c>
+      <s:c r="P21" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="22" s="1" customFormat="1" spans="1:16">
       <s:c r="A22" s="6" t="n">
@@ -4420,17 +4668,39 @@
       <s:c r="E22" s="1" t="n">
         <s:v>384.91</s:v>
       </s:c>
-      <s:c r="F22" s="1"/>
-      <s:c r="G22" s="1"/>
-      <s:c r="H22" s="1"/>
-      <s:c r="I22" s="1"/>
-      <s:c r="J22" s="1"/>
-      <s:c r="K22" s="1"/>
-      <s:c r="L22" s="1"/>
-      <s:c r="M22" s="1"/>
-      <s:c r="N22" s="1"/>
-      <s:c r="O22" s="1"/>
-      <s:c r="P22" s="1"/>
+      <s:c r="F22" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G22" s="1" t="n">
+        <s:v>2289.49</s:v>
+      </s:c>
+      <s:c r="H22" s="1" t="n">
+        <s:v>0.34</s:v>
+      </s:c>
+      <s:c r="I22" s="1" t="n">
+        <s:v>12.9</s:v>
+      </s:c>
+      <s:c r="J22" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K22" s="1" t="n">
+        <s:v>550.2</s:v>
+      </s:c>
+      <s:c r="L22" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M22" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N22" s="1" t="n">
+        <s:v>20496.28</s:v>
+      </s:c>
+      <s:c r="O22" s="1" t="n">
+        <s:v>3123.19</s:v>
+      </s:c>
+      <s:c r="P22" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="23" s="1" customFormat="1" spans="1:16">
       <s:c r="A23" s="6" t="n">
@@ -4448,17 +4718,39 @@
       <s:c r="E23" s="1" t="n">
         <s:v>389.91</s:v>
       </s:c>
-      <s:c r="F23" s="1"/>
-      <s:c r="G23" s="1"/>
-      <s:c r="H23" s="1"/>
-      <s:c r="I23" s="1"/>
-      <s:c r="J23" s="1"/>
-      <s:c r="K23" s="1"/>
-      <s:c r="L23" s="1"/>
-      <s:c r="M23" s="1"/>
-      <s:c r="N23" s="1"/>
-      <s:c r="O23" s="1"/>
-      <s:c r="P23" s="1"/>
+      <s:c r="F23" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G23" s="1" t="n">
+        <s:v>2302.56</s:v>
+      </s:c>
+      <s:c r="H23" s="1" t="n">
+        <s:v>0.34</s:v>
+      </s:c>
+      <s:c r="I23" s="1" t="n">
+        <s:v>85.38</s:v>
+      </s:c>
+      <s:c r="J23" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K23" s="1" t="n">
+        <s:v>549.4</s:v>
+      </s:c>
+      <s:c r="L23" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M23" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N23" s="1" t="n">
+        <s:v>20725.36</s:v>
+      </s:c>
+      <s:c r="O23" s="1" t="n">
+        <s:v>2979.24</s:v>
+      </s:c>
+      <s:c r="P23" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="24" s="1" customFormat="1" spans="1:16">
       <s:c r="A24" s="6" t="n">
@@ -4476,17 +4768,39 @@
       <s:c r="E24" s="1" t="n">
         <s:v>390.48</s:v>
       </s:c>
-      <s:c r="F24" s="1"/>
-      <s:c r="G24" s="1"/>
-      <s:c r="H24" s="1"/>
-      <s:c r="I24" s="1"/>
-      <s:c r="J24" s="1"/>
-      <s:c r="K24" s="1"/>
-      <s:c r="L24" s="1"/>
-      <s:c r="M24" s="1"/>
-      <s:c r="N24" s="1"/>
-      <s:c r="O24" s="1"/>
-      <s:c r="P24" s="1"/>
+      <s:c r="F24" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G24" s="1" t="n">
+        <s:v>2319.32</s:v>
+      </s:c>
+      <s:c r="H24" s="1" t="n">
+        <s:v>0.34</s:v>
+      </s:c>
+      <s:c r="I24" s="1" t="n">
+        <s:v>163.56</s:v>
+      </s:c>
+      <s:c r="J24" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K24" s="1" t="n">
+        <s:v>548.6</s:v>
+      </s:c>
+      <s:c r="L24" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M24" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N24" s="1" t="n">
+        <s:v>20818.97</s:v>
+      </s:c>
+      <s:c r="O24" s="1" t="n">
+        <s:v>3007.7</s:v>
+      </s:c>
+      <s:c r="P24" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="25" s="1" customFormat="1" spans="1:16">
       <s:c r="A25" s="6" t="n">
@@ -4504,17 +4818,39 @@
       <s:c r="E25" s="1" t="n">
         <s:v>412.22</s:v>
       </s:c>
-      <s:c r="F25" s="1"/>
-      <s:c r="G25" s="1"/>
-      <s:c r="H25" s="1"/>
-      <s:c r="I25" s="1"/>
-      <s:c r="J25" s="1"/>
-      <s:c r="K25" s="1"/>
-      <s:c r="L25" s="1"/>
-      <s:c r="M25" s="1"/>
-      <s:c r="N25" s="1"/>
-      <s:c r="O25" s="1"/>
-      <s:c r="P25" s="1"/>
+      <s:c r="F25" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G25" s="1" t="n">
+        <s:v>2333.67</s:v>
+      </s:c>
+      <s:c r="H25" s="1" t="n">
+        <s:v>0.34</s:v>
+      </s:c>
+      <s:c r="I25" s="1" t="n">
+        <s:v>315.17</s:v>
+      </s:c>
+      <s:c r="J25" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K25" s="1" t="n">
+        <s:v>300</s:v>
+      </s:c>
+      <s:c r="L25" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M25" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N25" s="1" t="n">
+        <s:v>21379.95</s:v>
+      </s:c>
+      <s:c r="O25" s="1" t="n">
+        <s:v>2964.37</s:v>
+      </s:c>
+      <s:c r="P25" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="26" s="1" customFormat="1" spans="1:16">
       <s:c r="A26" s="6" t="n">
@@ -4532,17 +4868,39 @@
       <s:c r="E26" s="1" t="n">
         <s:v>424.38</s:v>
       </s:c>
-      <s:c r="F26" s="1"/>
-      <s:c r="G26" s="1"/>
-      <s:c r="H26" s="1"/>
-      <s:c r="I26" s="1"/>
-      <s:c r="J26" s="1"/>
-      <s:c r="K26" s="1"/>
-      <s:c r="L26" s="1"/>
-      <s:c r="M26" s="1"/>
-      <s:c r="N26" s="1"/>
-      <s:c r="O26" s="1"/>
-      <s:c r="P26" s="1"/>
+      <s:c r="F26" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G26" s="1" t="n">
+        <s:v>2331</s:v>
+      </s:c>
+      <s:c r="H26" s="1" t="n">
+        <s:v>1.53</s:v>
+      </s:c>
+      <s:c r="I26" s="1" t="n">
+        <s:v>566.58</s:v>
+      </s:c>
+      <s:c r="J26" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K26" s="1" t="n">
+        <s:v>299.5</s:v>
+      </s:c>
+      <s:c r="L26" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M26" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N26" s="1" t="n">
+        <s:v>22016.11</s:v>
+      </s:c>
+      <s:c r="O26" s="1" t="n">
+        <s:v>2870.67</s:v>
+      </s:c>
+      <s:c r="P26" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="27" s="1" customFormat="1" spans="1:16">
       <s:c r="A27" s="6" t="n">
@@ -4560,17 +4918,39 @@
       <s:c r="E27" s="1" t="n">
         <s:v>422.51</s:v>
       </s:c>
-      <s:c r="F27" s="1"/>
-      <s:c r="G27" s="1"/>
-      <s:c r="H27" s="1"/>
-      <s:c r="I27" s="1"/>
-      <s:c r="J27" s="1"/>
-      <s:c r="K27" s="1"/>
-      <s:c r="L27" s="1"/>
-      <s:c r="M27" s="1"/>
-      <s:c r="N27" s="1"/>
-      <s:c r="O27" s="1"/>
-      <s:c r="P27" s="1"/>
+      <s:c r="F27" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G27" s="1" t="n">
+        <s:v>2329.16</s:v>
+      </s:c>
+      <s:c r="H27" s="1" t="n">
+        <s:v>1.53</s:v>
+      </s:c>
+      <s:c r="I27" s="1" t="n">
+        <s:v>924.31</s:v>
+      </s:c>
+      <s:c r="J27" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K27" s="1" t="n">
+        <s:v>149.7</s:v>
+      </s:c>
+      <s:c r="L27" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M27" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N27" s="1" t="n">
+        <s:v>22030.23</s:v>
+      </s:c>
+      <s:c r="O27" s="1" t="n">
+        <s:v>2809.77</s:v>
+      </s:c>
+      <s:c r="P27" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="28" s="1" customFormat="1" spans="1:16">
       <s:c r="A28" s="6" t="n">
@@ -4588,17 +4968,39 @@
       <s:c r="E28" s="1" t="n">
         <s:v>392.07</s:v>
       </s:c>
-      <s:c r="F28" s="1"/>
-      <s:c r="G28" s="1"/>
-      <s:c r="H28" s="1"/>
-      <s:c r="I28" s="1"/>
-      <s:c r="J28" s="1"/>
-      <s:c r="K28" s="1"/>
-      <s:c r="L28" s="1"/>
-      <s:c r="M28" s="1"/>
-      <s:c r="N28" s="1"/>
-      <s:c r="O28" s="1"/>
-      <s:c r="P28" s="1"/>
+      <s:c r="F28" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G28" s="1" t="n">
+        <s:v>2317.44</s:v>
+      </s:c>
+      <s:c r="H28" s="1" t="n">
+        <s:v>1.53</s:v>
+      </s:c>
+      <s:c r="I28" s="1" t="n">
+        <s:v>1348.24</s:v>
+      </s:c>
+      <s:c r="J28" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K28" s="1" t="n">
+        <s:v>149.7</s:v>
+      </s:c>
+      <s:c r="L28" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M28" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N28" s="1" t="n">
+        <s:v>21260.46</s:v>
+      </s:c>
+      <s:c r="O28" s="1" t="n">
+        <s:v>2809.23</s:v>
+      </s:c>
+      <s:c r="P28" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="29" s="1" customFormat="1" spans="1:16">
       <s:c r="A29" s="6" t="n">
@@ -4616,17 +5018,39 @@
       <s:c r="E29" s="1" t="n">
         <s:v>389.17</s:v>
       </s:c>
-      <s:c r="F29" s="1"/>
-      <s:c r="G29" s="1"/>
-      <s:c r="H29" s="1"/>
-      <s:c r="I29" s="1"/>
-      <s:c r="J29" s="1"/>
-      <s:c r="K29" s="1"/>
-      <s:c r="L29" s="1"/>
-      <s:c r="M29" s="1"/>
-      <s:c r="N29" s="1"/>
-      <s:c r="O29" s="1"/>
-      <s:c r="P29" s="1"/>
+      <s:c r="F29" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G29" s="1" t="n">
+        <s:v>2366.51</s:v>
+      </s:c>
+      <s:c r="H29" s="1" t="n">
+        <s:v>1.53</s:v>
+      </s:c>
+      <s:c r="I29" s="1" t="n">
+        <s:v>1755.29</s:v>
+      </s:c>
+      <s:c r="J29" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K29" s="1" t="n">
+        <s:v>148.9</s:v>
+      </s:c>
+      <s:c r="L29" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M29" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N29" s="1" t="n">
+        <s:v>20962.81</s:v>
+      </s:c>
+      <s:c r="O29" s="1" t="n">
+        <s:v>2740.35</s:v>
+      </s:c>
+      <s:c r="P29" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="30" s="1" customFormat="1" spans="1:16">
       <s:c r="A30" s="6" t="n">
@@ -4644,17 +5068,39 @@
       <s:c r="E30" s="1" t="n">
         <s:v>389.3</s:v>
       </s:c>
-      <s:c r="F30" s="1"/>
-      <s:c r="G30" s="1"/>
-      <s:c r="H30" s="1"/>
-      <s:c r="I30" s="1"/>
-      <s:c r="J30" s="1"/>
-      <s:c r="K30" s="1"/>
-      <s:c r="L30" s="1"/>
-      <s:c r="M30" s="1"/>
-      <s:c r="N30" s="1"/>
-      <s:c r="O30" s="1"/>
-      <s:c r="P30" s="1"/>
+      <s:c r="F30" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G30" s="1" t="n">
+        <s:v>2416.53</s:v>
+      </s:c>
+      <s:c r="H30" s="1" t="n">
+        <s:v>1.95</s:v>
+      </s:c>
+      <s:c r="I30" s="1" t="n">
+        <s:v>2239.66</s:v>
+      </s:c>
+      <s:c r="J30" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K30" s="1" t="n">
+        <s:v>149.3</s:v>
+      </s:c>
+      <s:c r="L30" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M30" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N30" s="1" t="n">
+        <s:v>20967.97</s:v>
+      </s:c>
+      <s:c r="O30" s="1" t="n">
+        <s:v>2618.69</s:v>
+      </s:c>
+      <s:c r="P30" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="31" s="1" customFormat="1" spans="1:16">
       <s:c r="A31" s="6" t="n">
@@ -4672,17 +5118,39 @@
       <s:c r="E31" s="1" t="n">
         <s:v>366.05</s:v>
       </s:c>
-      <s:c r="F31" s="1"/>
-      <s:c r="G31" s="1"/>
-      <s:c r="H31" s="1"/>
-      <s:c r="I31" s="1"/>
-      <s:c r="J31" s="1"/>
-      <s:c r="K31" s="1"/>
-      <s:c r="L31" s="1"/>
-      <s:c r="M31" s="1"/>
-      <s:c r="N31" s="1"/>
-      <s:c r="O31" s="1"/>
-      <s:c r="P31" s="1"/>
+      <s:c r="F31" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G31" s="1" t="n">
+        <s:v>2403.51</s:v>
+      </s:c>
+      <s:c r="H31" s="1" t="n">
+        <s:v>1.95</s:v>
+      </s:c>
+      <s:c r="I31" s="1" t="n">
+        <s:v>2670.55</s:v>
+      </s:c>
+      <s:c r="J31" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K31" s="1" t="n">
+        <s:v>151.5</s:v>
+      </s:c>
+      <s:c r="L31" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M31" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N31" s="1" t="n">
+        <s:v>20308.6</s:v>
+      </s:c>
+      <s:c r="O31" s="1" t="n">
+        <s:v>2469.28</s:v>
+      </s:c>
+      <s:c r="P31" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="32" s="1" customFormat="1" spans="1:16">
       <s:c r="A32" s="6" t="n">
@@ -4700,17 +5168,39 @@
       <s:c r="E32" s="1" t="n">
         <s:v>351.83</s:v>
       </s:c>
-      <s:c r="F32" s="1"/>
-      <s:c r="G32" s="1"/>
-      <s:c r="H32" s="1"/>
-      <s:c r="I32" s="1"/>
-      <s:c r="J32" s="1"/>
-      <s:c r="K32" s="1"/>
-      <s:c r="L32" s="1"/>
-      <s:c r="M32" s="1"/>
-      <s:c r="N32" s="1"/>
-      <s:c r="O32" s="1"/>
-      <s:c r="P32" s="1"/>
+      <s:c r="F32" s="1" t="n">
+        <s:v>-20</s:v>
+      </s:c>
+      <s:c r="G32" s="1" t="n">
+        <s:v>2395.93</s:v>
+      </s:c>
+      <s:c r="H32" s="1" t="n">
+        <s:v>1.95</s:v>
+      </s:c>
+      <s:c r="I32" s="1" t="n">
+        <s:v>3059.14</s:v>
+      </s:c>
+      <s:c r="J32" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K32" s="1" t="n">
+        <s:v>302.3</s:v>
+      </s:c>
+      <s:c r="L32" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M32" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N32" s="1" t="n">
+        <s:v>19741.59</s:v>
+      </s:c>
+      <s:c r="O32" s="1" t="n">
+        <s:v>2260.29</s:v>
+      </s:c>
+      <s:c r="P32" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="33" s="1" customFormat="1" spans="1:16">
       <s:c r="A33" s="6" t="n">
@@ -4728,17 +5218,39 @@
       <s:c r="E33" s="1" t="n">
         <s:v>355.16</s:v>
       </s:c>
-      <s:c r="F33" s="1"/>
-      <s:c r="G33" s="1"/>
-      <s:c r="H33" s="1"/>
-      <s:c r="I33" s="1"/>
-      <s:c r="J33" s="1"/>
-      <s:c r="K33" s="1"/>
-      <s:c r="L33" s="1"/>
-      <s:c r="M33" s="1"/>
-      <s:c r="N33" s="1"/>
-      <s:c r="O33" s="1"/>
-      <s:c r="P33" s="1"/>
+      <s:c r="F33" s="1" t="n">
+        <s:v>-50</s:v>
+      </s:c>
+      <s:c r="G33" s="1" t="n">
+        <s:v>2383.38</s:v>
+      </s:c>
+      <s:c r="H33" s="1" t="n">
+        <s:v>1.95</s:v>
+      </s:c>
+      <s:c r="I33" s="1" t="n">
+        <s:v>3339.98</s:v>
+      </s:c>
+      <s:c r="J33" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K33" s="1" t="n">
+        <s:v>-7.9</s:v>
+      </s:c>
+      <s:c r="L33" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M33" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N33" s="1" t="n">
+        <s:v>20231.47</s:v>
+      </s:c>
+      <s:c r="O33" s="1" t="n">
+        <s:v>1967.01</s:v>
+      </s:c>
+      <s:c r="P33" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="34" s="1" customFormat="1" spans="1:16">
       <s:c r="A34" s="6" t="n">
@@ -4756,17 +5268,39 @@
       <s:c r="E34" s="1" t="n">
         <s:v>412.22</s:v>
       </s:c>
-      <s:c r="F34" s="1"/>
-      <s:c r="G34" s="1"/>
-      <s:c r="H34" s="1"/>
-      <s:c r="I34" s="1"/>
-      <s:c r="J34" s="1"/>
-      <s:c r="K34" s="1"/>
-      <s:c r="L34" s="1"/>
-      <s:c r="M34" s="1"/>
-      <s:c r="N34" s="1"/>
-      <s:c r="O34" s="1"/>
-      <s:c r="P34" s="1"/>
+      <s:c r="F34" s="1" t="n">
+        <s:v>-50</s:v>
+      </s:c>
+      <s:c r="G34" s="1" t="n">
+        <s:v>2381.23</s:v>
+      </s:c>
+      <s:c r="H34" s="1" t="n">
+        <s:v>3.51</s:v>
+      </s:c>
+      <s:c r="I34" s="1" t="n">
+        <s:v>3760.33</s:v>
+      </s:c>
+      <s:c r="J34" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K34" s="1" t="n">
+        <s:v>-576.7</s:v>
+      </s:c>
+      <s:c r="L34" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M34" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N34" s="1" t="n">
+        <s:v>21844.38</s:v>
+      </s:c>
+      <s:c r="O34" s="1" t="n">
+        <s:v>1822.24</s:v>
+      </s:c>
+      <s:c r="P34" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="35" s="1" customFormat="1" spans="1:16">
       <s:c r="A35" s="6" t="n">
@@ -4784,17 +5318,39 @@
       <s:c r="E35" s="1" t="n">
         <s:v>399.42</s:v>
       </s:c>
-      <s:c r="F35" s="1"/>
-      <s:c r="G35" s="1"/>
-      <s:c r="H35" s="1"/>
-      <s:c r="I35" s="1"/>
-      <s:c r="J35" s="1"/>
-      <s:c r="K35" s="1"/>
-      <s:c r="L35" s="1"/>
-      <s:c r="M35" s="1"/>
-      <s:c r="N35" s="1"/>
-      <s:c r="O35" s="1"/>
-      <s:c r="P35" s="1"/>
+      <s:c r="F35" s="1" t="n">
+        <s:v>-110</s:v>
+      </s:c>
+      <s:c r="G35" s="1" t="n">
+        <s:v>2434.46</s:v>
+      </s:c>
+      <s:c r="H35" s="1" t="n">
+        <s:v>3.51</s:v>
+      </s:c>
+      <s:c r="I35" s="1" t="n">
+        <s:v>4166.56</s:v>
+      </s:c>
+      <s:c r="J35" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K35" s="1" t="n">
+        <s:v>-1091</s:v>
+      </s:c>
+      <s:c r="L35" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M35" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N35" s="1" t="n">
+        <s:v>21926.24</s:v>
+      </s:c>
+      <s:c r="O35" s="1" t="n">
+        <s:v>1766.12</s:v>
+      </s:c>
+      <s:c r="P35" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="36" s="1" customFormat="1" spans="1:16">
       <s:c r="A36" s="6" t="n">
@@ -4812,17 +5368,39 @@
       <s:c r="E36" s="1" t="n">
         <s:v>418.98</s:v>
       </s:c>
-      <s:c r="F36" s="1"/>
-      <s:c r="G36" s="1"/>
-      <s:c r="H36" s="1"/>
-      <s:c r="I36" s="1"/>
-      <s:c r="J36" s="1"/>
-      <s:c r="K36" s="1"/>
-      <s:c r="L36" s="1"/>
-      <s:c r="M36" s="1"/>
-      <s:c r="N36" s="1"/>
-      <s:c r="O36" s="1"/>
-      <s:c r="P36" s="1"/>
+      <s:c r="F36" s="1" t="n">
+        <s:v>-350</s:v>
+      </s:c>
+      <s:c r="G36" s="1" t="n">
+        <s:v>2413.03</s:v>
+      </s:c>
+      <s:c r="H36" s="1" t="n">
+        <s:v>3.51</s:v>
+      </s:c>
+      <s:c r="I36" s="1" t="n">
+        <s:v>4592.08</s:v>
+      </s:c>
+      <s:c r="J36" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K36" s="1" t="n">
+        <s:v>-1633.1</s:v>
+      </s:c>
+      <s:c r="L36" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M36" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N36" s="1" t="n">
+        <s:v>22318.94</s:v>
+      </s:c>
+      <s:c r="O36" s="1" t="n">
+        <s:v>1797.14</s:v>
+      </s:c>
+      <s:c r="P36" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="37" s="1" customFormat="1" spans="1:16">
       <s:c r="A37" s="6" t="n">
@@ -4840,17 +5418,39 @@
       <s:c r="E37" s="1" t="n">
         <s:v>362.86</s:v>
       </s:c>
-      <s:c r="F37" s="1"/>
-      <s:c r="G37" s="1"/>
-      <s:c r="H37" s="1"/>
-      <s:c r="I37" s="1"/>
-      <s:c r="J37" s="1"/>
-      <s:c r="K37" s="1"/>
-      <s:c r="L37" s="1"/>
-      <s:c r="M37" s="1"/>
-      <s:c r="N37" s="1"/>
-      <s:c r="O37" s="1"/>
-      <s:c r="P37" s="1"/>
+      <s:c r="F37" s="1" t="n">
+        <s:v>-560</s:v>
+      </s:c>
+      <s:c r="G37" s="1" t="n">
+        <s:v>2403.52</s:v>
+      </s:c>
+      <s:c r="H37" s="1" t="n">
+        <s:v>3.51</s:v>
+      </s:c>
+      <s:c r="I37" s="1" t="n">
+        <s:v>4896.93</s:v>
+      </s:c>
+      <s:c r="J37" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K37" s="1" t="n">
+        <s:v>-1642.7</s:v>
+      </s:c>
+      <s:c r="L37" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M37" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N37" s="1" t="n">
+        <s:v>22059.15</s:v>
+      </s:c>
+      <s:c r="O37" s="1" t="n">
+        <s:v>1787.07</s:v>
+      </s:c>
+      <s:c r="P37" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="38" s="1" customFormat="1" spans="1:16">
       <s:c r="A38" s="6" t="n">
@@ -4868,17 +5468,39 @@
       <s:c r="E38" s="1" t="n">
         <s:v>363.98</s:v>
       </s:c>
-      <s:c r="F38" s="1"/>
-      <s:c r="G38" s="1"/>
-      <s:c r="H38" s="1"/>
-      <s:c r="I38" s="1"/>
-      <s:c r="J38" s="1"/>
-      <s:c r="K38" s="1"/>
-      <s:c r="L38" s="1"/>
-      <s:c r="M38" s="1"/>
-      <s:c r="N38" s="1"/>
-      <s:c r="O38" s="1"/>
-      <s:c r="P38" s="1"/>
+      <s:c r="F38" s="1" t="n">
+        <s:v>-913</s:v>
+      </s:c>
+      <s:c r="G38" s="1" t="n">
+        <s:v>2435.21</s:v>
+      </s:c>
+      <s:c r="H38" s="1" t="n">
+        <s:v>2.06</s:v>
+      </s:c>
+      <s:c r="I38" s="1" t="n">
+        <s:v>5316.87</s:v>
+      </s:c>
+      <s:c r="J38" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K38" s="1" t="n">
+        <s:v>-1640.5</s:v>
+      </s:c>
+      <s:c r="L38" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M38" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N38" s="1" t="n">
+        <s:v>21771.25</s:v>
+      </s:c>
+      <s:c r="O38" s="1" t="n">
+        <s:v>1765.5</s:v>
+      </s:c>
+      <s:c r="P38" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="39" s="1" customFormat="1" spans="1:16">
       <s:c r="A39" s="6" t="n">
@@ -4896,17 +5518,39 @@
       <s:c r="E39" s="1" t="n">
         <s:v>391.58</s:v>
       </s:c>
-      <s:c r="F39" s="1"/>
-      <s:c r="G39" s="1"/>
-      <s:c r="H39" s="1"/>
-      <s:c r="I39" s="1"/>
-      <s:c r="J39" s="1"/>
-      <s:c r="K39" s="1"/>
-      <s:c r="L39" s="1"/>
-      <s:c r="M39" s="1"/>
-      <s:c r="N39" s="1"/>
-      <s:c r="O39" s="1"/>
-      <s:c r="P39" s="1"/>
+      <s:c r="F39" s="1" t="n">
+        <s:v>-1093</s:v>
+      </s:c>
+      <s:c r="G39" s="1" t="n">
+        <s:v>2468.78</s:v>
+      </s:c>
+      <s:c r="H39" s="1" t="n">
+        <s:v>2.06</s:v>
+      </s:c>
+      <s:c r="I39" s="1" t="n">
+        <s:v>5411.04</s:v>
+      </s:c>
+      <s:c r="J39" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K39" s="1" t="n">
+        <s:v>-1339.5</s:v>
+      </s:c>
+      <s:c r="L39" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M39" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N39" s="1" t="n">
+        <s:v>22126.02</s:v>
+      </s:c>
+      <s:c r="O39" s="1" t="n">
+        <s:v>1687.39</s:v>
+      </s:c>
+      <s:c r="P39" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="40" s="1" customFormat="1" spans="1:16">
       <s:c r="A40" s="6" t="n">
@@ -4924,17 +5568,39 @@
       <s:c r="E40" s="1" t="n">
         <s:v>378.94</s:v>
       </s:c>
-      <s:c r="F40" s="1"/>
-      <s:c r="G40" s="1"/>
-      <s:c r="H40" s="1"/>
-      <s:c r="I40" s="1"/>
-      <s:c r="J40" s="1"/>
-      <s:c r="K40" s="1"/>
-      <s:c r="L40" s="1"/>
-      <s:c r="M40" s="1"/>
-      <s:c r="N40" s="1"/>
-      <s:c r="O40" s="1"/>
-      <s:c r="P40" s="1"/>
+      <s:c r="F40" s="1" t="n">
+        <s:v>-1093</s:v>
+      </s:c>
+      <s:c r="G40" s="1" t="n">
+        <s:v>2502.57</s:v>
+      </s:c>
+      <s:c r="H40" s="1" t="n">
+        <s:v>2.06</s:v>
+      </s:c>
+      <s:c r="I40" s="1" t="n">
+        <s:v>5738.51</s:v>
+      </s:c>
+      <s:c r="J40" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K40" s="1" t="n">
+        <s:v>-1342.1</s:v>
+      </s:c>
+      <s:c r="L40" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M40" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N40" s="1" t="n">
+        <s:v>21963.14</s:v>
+      </s:c>
+      <s:c r="O40" s="1" t="n">
+        <s:v>1615.01</s:v>
+      </s:c>
+      <s:c r="P40" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="41" s="1" customFormat="1" spans="1:16">
       <s:c r="A41" s="6" t="n">
@@ -4952,17 +5618,39 @@
       <s:c r="E41" s="1" t="n">
         <s:v>390.23</s:v>
       </s:c>
-      <s:c r="F41" s="1"/>
-      <s:c r="G41" s="1"/>
-      <s:c r="H41" s="1"/>
-      <s:c r="I41" s="1"/>
-      <s:c r="J41" s="1"/>
-      <s:c r="K41" s="1"/>
-      <s:c r="L41" s="1"/>
-      <s:c r="M41" s="1"/>
-      <s:c r="N41" s="1"/>
-      <s:c r="O41" s="1"/>
-      <s:c r="P41" s="1"/>
+      <s:c r="F41" s="1" t="n">
+        <s:v>-1223</s:v>
+      </s:c>
+      <s:c r="G41" s="1" t="n">
+        <s:v>2529.13</s:v>
+      </s:c>
+      <s:c r="H41" s="1" t="n">
+        <s:v>2.06</s:v>
+      </s:c>
+      <s:c r="I41" s="1" t="n">
+        <s:v>6111.87</s:v>
+      </s:c>
+      <s:c r="J41" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K41" s="1" t="n">
+        <s:v>-1620.9</s:v>
+      </s:c>
+      <s:c r="L41" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M41" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N41" s="1" t="n">
+        <s:v>21937.01</s:v>
+      </s:c>
+      <s:c r="O41" s="1" t="n">
+        <s:v>1475.32</s:v>
+      </s:c>
+      <s:c r="P41" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="42" s="1" customFormat="1" spans="1:16">
       <s:c r="A42" s="6" t="n">
@@ -4980,17 +5668,39 @@
       <s:c r="E42" s="1" t="n">
         <s:v>389.39</s:v>
       </s:c>
-      <s:c r="F42" s="1"/>
-      <s:c r="G42" s="1"/>
-      <s:c r="H42" s="1"/>
-      <s:c r="I42" s="1"/>
-      <s:c r="J42" s="1"/>
-      <s:c r="K42" s="1"/>
-      <s:c r="L42" s="1"/>
-      <s:c r="M42" s="1"/>
-      <s:c r="N42" s="1"/>
-      <s:c r="O42" s="1"/>
-      <s:c r="P42" s="1"/>
+      <s:c r="F42" s="1" t="n">
+        <s:v>-1193</s:v>
+      </s:c>
+      <s:c r="G42" s="1" t="n">
+        <s:v>2571.11</s:v>
+      </s:c>
+      <s:c r="H42" s="1" t="n">
+        <s:v>2.18</s:v>
+      </s:c>
+      <s:c r="I42" s="1" t="n">
+        <s:v>6547.07</s:v>
+      </s:c>
+      <s:c r="J42" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K42" s="1" t="n">
+        <s:v>-1626.1</s:v>
+      </s:c>
+      <s:c r="L42" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M42" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N42" s="1" t="n">
+        <s:v>21718.75</s:v>
+      </s:c>
+      <s:c r="O42" s="1" t="n">
+        <s:v>1357.37</s:v>
+      </s:c>
+      <s:c r="P42" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="43" s="1" customFormat="1" spans="1:16">
       <s:c r="A43" s="6" t="n">
@@ -5008,17 +5718,39 @@
       <s:c r="E43" s="1" t="n">
         <s:v>378.94</s:v>
       </s:c>
-      <s:c r="F43" s="1"/>
-      <s:c r="G43" s="1"/>
-      <s:c r="H43" s="1"/>
-      <s:c r="I43" s="1"/>
-      <s:c r="J43" s="1"/>
-      <s:c r="K43" s="1"/>
-      <s:c r="L43" s="1"/>
-      <s:c r="M43" s="1"/>
-      <s:c r="N43" s="1"/>
-      <s:c r="O43" s="1"/>
-      <s:c r="P43" s="1"/>
+      <s:c r="F43" s="1" t="n">
+        <s:v>-1143</s:v>
+      </s:c>
+      <s:c r="G43" s="1" t="n">
+        <s:v>2634.88</s:v>
+      </s:c>
+      <s:c r="H43" s="1" t="n">
+        <s:v>2.18</s:v>
+      </s:c>
+      <s:c r="I43" s="1" t="n">
+        <s:v>6814.72</s:v>
+      </s:c>
+      <s:c r="J43" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K43" s="1" t="n">
+        <s:v>-1620.4</s:v>
+      </s:c>
+      <s:c r="L43" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M43" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N43" s="1" t="n">
+        <s:v>21406.07</s:v>
+      </s:c>
+      <s:c r="O43" s="1" t="n">
+        <s:v>1276.93</s:v>
+      </s:c>
+      <s:c r="P43" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="44" s="1" customFormat="1" spans="1:16">
       <s:c r="A44" s="6" t="n">
@@ -5036,17 +5768,39 @@
       <s:c r="E44" s="1" t="n">
         <s:v>364.79</s:v>
       </s:c>
-      <s:c r="F44" s="1"/>
-      <s:c r="G44" s="1"/>
-      <s:c r="H44" s="1"/>
-      <s:c r="I44" s="1"/>
-      <s:c r="J44" s="1"/>
-      <s:c r="K44" s="1"/>
-      <s:c r="L44" s="1"/>
-      <s:c r="M44" s="1"/>
-      <s:c r="N44" s="1"/>
-      <s:c r="O44" s="1"/>
-      <s:c r="P44" s="1"/>
+      <s:c r="F44" s="1" t="n">
+        <s:v>-1003</s:v>
+      </s:c>
+      <s:c r="G44" s="1" t="n">
+        <s:v>2706.28</s:v>
+      </s:c>
+      <s:c r="H44" s="1" t="n">
+        <s:v>2.18</s:v>
+      </s:c>
+      <s:c r="I44" s="1" t="n">
+        <s:v>7055.76</s:v>
+      </s:c>
+      <s:c r="J44" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K44" s="1" t="n">
+        <s:v>-1615.4</s:v>
+      </s:c>
+      <s:c r="L44" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M44" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N44" s="1" t="n">
+        <s:v>20882.54</s:v>
+      </s:c>
+      <s:c r="O44" s="1" t="n">
+        <s:v>1271.64</s:v>
+      </s:c>
+      <s:c r="P44" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="45" s="1" customFormat="1" spans="1:16">
       <s:c r="A45" s="6" t="n">
@@ -5064,17 +5818,39 @@
       <s:c r="E45" s="1" t="n">
         <s:v>364.54</s:v>
       </s:c>
-      <s:c r="F45" s="1"/>
-      <s:c r="G45" s="1"/>
-      <s:c r="H45" s="1"/>
-      <s:c r="I45" s="1"/>
-      <s:c r="J45" s="1"/>
-      <s:c r="K45" s="1"/>
-      <s:c r="L45" s="1"/>
-      <s:c r="M45" s="1"/>
-      <s:c r="N45" s="1"/>
-      <s:c r="O45" s="1"/>
-      <s:c r="P45" s="1"/>
+      <s:c r="F45" s="1" t="n">
+        <s:v>-703</s:v>
+      </s:c>
+      <s:c r="G45" s="1" t="n">
+        <s:v>2763.16</s:v>
+      </s:c>
+      <s:c r="H45" s="1" t="n">
+        <s:v>2.18</s:v>
+      </s:c>
+      <s:c r="I45" s="1" t="n">
+        <s:v>7315.48</s:v>
+      </s:c>
+      <s:c r="J45" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K45" s="1" t="n">
+        <s:v>-1611.3</s:v>
+      </s:c>
+      <s:c r="L45" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M45" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N45" s="1" t="n">
+        <s:v>20572.31</s:v>
+      </s:c>
+      <s:c r="O45" s="1" t="n">
+        <s:v>1271.47</s:v>
+      </s:c>
+      <s:c r="P45" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="46" s="1" customFormat="1" spans="1:16">
       <s:c r="A46" s="6" t="n">
@@ -5092,17 +5868,39 @@
       <s:c r="E46" s="1" t="n">
         <s:v>362.8</s:v>
       </s:c>
-      <s:c r="F46" s="1"/>
-      <s:c r="G46" s="1"/>
-      <s:c r="H46" s="1"/>
-      <s:c r="I46" s="1"/>
-      <s:c r="J46" s="1"/>
-      <s:c r="K46" s="1"/>
-      <s:c r="L46" s="1"/>
-      <s:c r="M46" s="1"/>
-      <s:c r="N46" s="1"/>
-      <s:c r="O46" s="1"/>
-      <s:c r="P46" s="1"/>
+      <s:c r="F46" s="1" t="n">
+        <s:v>-400</s:v>
+      </s:c>
+      <s:c r="G46" s="1" t="n">
+        <s:v>2788.57</s:v>
+      </s:c>
+      <s:c r="H46" s="1" t="n">
+        <s:v>1.7</s:v>
+      </s:c>
+      <s:c r="I46" s="1" t="n">
+        <s:v>7534.4</s:v>
+      </s:c>
+      <s:c r="J46" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K46" s="1" t="n">
+        <s:v>-1602.8</s:v>
+      </s:c>
+      <s:c r="L46" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M46" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N46" s="1" t="n">
+        <s:v>20370.39</s:v>
+      </s:c>
+      <s:c r="O46" s="1" t="n">
+        <s:v>1199.03</s:v>
+      </s:c>
+      <s:c r="P46" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="47" s="1" customFormat="1" spans="1:16">
       <s:c r="A47" s="6" t="n">
@@ -5120,17 +5918,39 @@
       <s:c r="E47" s="1" t="n">
         <s:v>362.8</s:v>
       </s:c>
-      <s:c r="F47" s="1"/>
-      <s:c r="G47" s="1"/>
-      <s:c r="H47" s="1"/>
-      <s:c r="I47" s="1"/>
-      <s:c r="J47" s="1"/>
-      <s:c r="K47" s="1"/>
-      <s:c r="L47" s="1"/>
-      <s:c r="M47" s="1"/>
-      <s:c r="N47" s="1"/>
-      <s:c r="O47" s="1"/>
-      <s:c r="P47" s="1"/>
+      <s:c r="F47" s="1" t="n">
+        <s:v>-160</s:v>
+      </s:c>
+      <s:c r="G47" s="1" t="n">
+        <s:v>2799.94</s:v>
+      </s:c>
+      <s:c r="H47" s="1" t="n">
+        <s:v>1.7</s:v>
+      </s:c>
+      <s:c r="I47" s="1" t="n">
+        <s:v>7822.51</s:v>
+      </s:c>
+      <s:c r="J47" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K47" s="1" t="n">
+        <s:v>-1600.6</s:v>
+      </s:c>
+      <s:c r="L47" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M47" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N47" s="1" t="n">
+        <s:v>20423.21</s:v>
+      </s:c>
+      <s:c r="O47" s="1" t="n">
+        <s:v>1184.62</s:v>
+      </s:c>
+      <s:c r="P47" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="48" s="1" customFormat="1" spans="1:16">
       <s:c r="A48" s="6" t="n">
@@ -5148,17 +5968,39 @@
       <s:c r="E48" s="1" t="n">
         <s:v>350.63</s:v>
       </s:c>
-      <s:c r="F48" s="1"/>
-      <s:c r="G48" s="1"/>
-      <s:c r="H48" s="1"/>
-      <s:c r="I48" s="1"/>
-      <s:c r="J48" s="1"/>
-      <s:c r="K48" s="1"/>
-      <s:c r="L48" s="1"/>
-      <s:c r="M48" s="1"/>
-      <s:c r="N48" s="1"/>
-      <s:c r="O48" s="1"/>
-      <s:c r="P48" s="1"/>
+      <s:c r="F48" s="1" t="n">
+        <s:v>-40</s:v>
+      </s:c>
+      <s:c r="G48" s="1" t="n">
+        <s:v>2827.99</s:v>
+      </s:c>
+      <s:c r="H48" s="1" t="n">
+        <s:v>1.7</s:v>
+      </s:c>
+      <s:c r="I48" s="1" t="n">
+        <s:v>8271.91</s:v>
+      </s:c>
+      <s:c r="J48" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K48" s="1" t="n">
+        <s:v>-1602.2</s:v>
+      </s:c>
+      <s:c r="L48" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M48" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N48" s="1" t="n">
+        <s:v>20114.44</s:v>
+      </s:c>
+      <s:c r="O48" s="1" t="n">
+        <s:v>1174.66</s:v>
+      </s:c>
+      <s:c r="P48" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="49" s="1" customFormat="1" spans="1:16">
       <s:c r="A49" s="6" t="n">
@@ -5176,17 +6018,39 @@
       <s:c r="E49" s="1" t="n">
         <s:v>343.95</s:v>
       </s:c>
-      <s:c r="F49" s="1"/>
-      <s:c r="G49" s="1"/>
-      <s:c r="H49" s="1"/>
-      <s:c r="I49" s="1"/>
-      <s:c r="J49" s="1"/>
-      <s:c r="K49" s="1"/>
-      <s:c r="L49" s="1"/>
-      <s:c r="M49" s="1"/>
-      <s:c r="N49" s="1"/>
-      <s:c r="O49" s="1"/>
-      <s:c r="P49" s="1"/>
+      <s:c r="F49" s="1" t="n">
+        <s:v>-30</s:v>
+      </s:c>
+      <s:c r="G49" s="1" t="n">
+        <s:v>2917.41</s:v>
+      </s:c>
+      <s:c r="H49" s="1" t="n">
+        <s:v>1.7</s:v>
+      </s:c>
+      <s:c r="I49" s="1" t="n">
+        <s:v>8238.21</s:v>
+      </s:c>
+      <s:c r="J49" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K49" s="1" t="n">
+        <s:v>-1592.4</s:v>
+      </s:c>
+      <s:c r="L49" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M49" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N49" s="1" t="n">
+        <s:v>19775.07</s:v>
+      </s:c>
+      <s:c r="O49" s="1" t="n">
+        <s:v>1170.42</s:v>
+      </s:c>
+      <s:c r="P49" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="50" s="1" customFormat="1" spans="1:16">
       <s:c r="A50" s="6" t="n">
@@ -5204,17 +6068,39 @@
       <s:c r="E50" s="1" t="n">
         <s:v>422.79</s:v>
       </s:c>
-      <s:c r="F50" s="1"/>
-      <s:c r="G50" s="1"/>
-      <s:c r="H50" s="1"/>
-      <s:c r="I50" s="1"/>
-      <s:c r="J50" s="1"/>
-      <s:c r="K50" s="1"/>
-      <s:c r="L50" s="1"/>
-      <s:c r="M50" s="1"/>
-      <s:c r="N50" s="1"/>
-      <s:c r="O50" s="1"/>
-      <s:c r="P50" s="1"/>
+      <s:c r="F50" s="1" t="n">
+        <s:v>60</s:v>
+      </s:c>
+      <s:c r="G50" s="1" t="n">
+        <s:v>2953.02</s:v>
+      </s:c>
+      <s:c r="H50" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I50" s="1" t="n">
+        <s:v>8140.43</s:v>
+      </s:c>
+      <s:c r="J50" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K50" s="1" t="n">
+        <s:v>-1341.3</s:v>
+      </s:c>
+      <s:c r="L50" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M50" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N50" s="1" t="n">
+        <s:v>22252.16</s:v>
+      </s:c>
+      <s:c r="O50" s="1" t="n">
+        <s:v>1191.3</s:v>
+      </s:c>
+      <s:c r="P50" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="51" s="1" customFormat="1" spans="1:16">
       <s:c r="A51" s="6" t="n">
@@ -5232,17 +6118,39 @@
       <s:c r="E51" s="1" t="n">
         <s:v>390.48</s:v>
       </s:c>
-      <s:c r="F51" s="1"/>
-      <s:c r="G51" s="1"/>
-      <s:c r="H51" s="1"/>
-      <s:c r="I51" s="1"/>
-      <s:c r="J51" s="1"/>
-      <s:c r="K51" s="1"/>
-      <s:c r="L51" s="1"/>
-      <s:c r="M51" s="1"/>
-      <s:c r="N51" s="1"/>
-      <s:c r="O51" s="1"/>
-      <s:c r="P51" s="1"/>
+      <s:c r="F51" s="1" t="n">
+        <s:v>60</s:v>
+      </s:c>
+      <s:c r="G51" s="1" t="n">
+        <s:v>2728.72</s:v>
+      </s:c>
+      <s:c r="H51" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I51" s="1" t="n">
+        <s:v>8102.26</s:v>
+      </s:c>
+      <s:c r="J51" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K51" s="1" t="n">
+        <s:v>-804.4</s:v>
+      </s:c>
+      <s:c r="L51" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M51" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N51" s="1" t="n">
+        <s:v>21437.92</s:v>
+      </s:c>
+      <s:c r="O51" s="1" t="n">
+        <s:v>1308.4</s:v>
+      </s:c>
+      <s:c r="P51" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="52" s="1" customFormat="1" spans="1:16">
       <s:c r="A52" s="6" t="n">
@@ -5260,17 +6168,39 @@
       <s:c r="E52" s="1" t="n">
         <s:v>391.73</s:v>
       </s:c>
-      <s:c r="F52" s="1"/>
-      <s:c r="G52" s="1"/>
-      <s:c r="H52" s="1"/>
-      <s:c r="I52" s="1"/>
-      <s:c r="J52" s="1"/>
-      <s:c r="K52" s="1"/>
-      <s:c r="L52" s="1"/>
-      <s:c r="M52" s="1"/>
-      <s:c r="N52" s="1"/>
-      <s:c r="O52" s="1"/>
-      <s:c r="P52" s="1"/>
+      <s:c r="F52" s="1" t="n">
+        <s:v>60</s:v>
+      </s:c>
+      <s:c r="G52" s="1" t="n">
+        <s:v>2723.55</s:v>
+      </s:c>
+      <s:c r="H52" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I52" s="1" t="n">
+        <s:v>8217.04</s:v>
+      </s:c>
+      <s:c r="J52" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K52" s="1" t="n">
+        <s:v>-805.2</s:v>
+      </s:c>
+      <s:c r="L52" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M52" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N52" s="1" t="n">
+        <s:v>21636.32</s:v>
+      </s:c>
+      <s:c r="O52" s="1" t="n">
+        <s:v>1401.78</s:v>
+      </s:c>
+      <s:c r="P52" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="53" s="1" customFormat="1" spans="1:16">
       <s:c r="A53" s="6" t="n">
@@ -5288,17 +6218,39 @@
       <s:c r="E53" s="1" t="n">
         <s:v>371.51</s:v>
       </s:c>
-      <s:c r="F53" s="1"/>
-      <s:c r="G53" s="1"/>
-      <s:c r="H53" s="1"/>
-      <s:c r="I53" s="1"/>
-      <s:c r="J53" s="1"/>
-      <s:c r="K53" s="1"/>
-      <s:c r="L53" s="1"/>
-      <s:c r="M53" s="1"/>
-      <s:c r="N53" s="1"/>
-      <s:c r="O53" s="1"/>
-      <s:c r="P53" s="1"/>
+      <s:c r="F53" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G53" s="1" t="n">
+        <s:v>2664.02</s:v>
+      </s:c>
+      <s:c r="H53" s="1" t="n">
+        <s:v>1.69</s:v>
+      </s:c>
+      <s:c r="I53" s="1" t="n">
+        <s:v>8118.35</s:v>
+      </s:c>
+      <s:c r="J53" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K53" s="1" t="n">
+        <s:v>-1097.1</s:v>
+      </s:c>
+      <s:c r="L53" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M53" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N53" s="1" t="n">
+        <s:v>20953.79</s:v>
+      </s:c>
+      <s:c r="O53" s="1" t="n">
+        <s:v>1496.74</s:v>
+      </s:c>
+      <s:c r="P53" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="54" s="1" customFormat="1" spans="1:16">
       <s:c r="A54" s="6" t="n">
@@ -5316,17 +6268,39 @@
       <s:c r="E54" s="1" t="n">
         <s:v>390.39</s:v>
       </s:c>
-      <s:c r="F54" s="1"/>
-      <s:c r="G54" s="1"/>
-      <s:c r="H54" s="1"/>
-      <s:c r="I54" s="1"/>
-      <s:c r="J54" s="1"/>
-      <s:c r="K54" s="1"/>
-      <s:c r="L54" s="1"/>
-      <s:c r="M54" s="1"/>
-      <s:c r="N54" s="1"/>
-      <s:c r="O54" s="1"/>
-      <s:c r="P54" s="1"/>
+      <s:c r="F54" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G54" s="1" t="n">
+        <s:v>2669.17</s:v>
+      </s:c>
+      <s:c r="H54" s="1" t="n">
+        <s:v>1.39</s:v>
+      </s:c>
+      <s:c r="I54" s="1" t="n">
+        <s:v>7881.9</s:v>
+      </s:c>
+      <s:c r="J54" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K54" s="1" t="n">
+        <s:v>-1093.2</s:v>
+      </s:c>
+      <s:c r="L54" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M54" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N54" s="1" t="n">
+        <s:v>21291.21</s:v>
+      </s:c>
+      <s:c r="O54" s="1" t="n">
+        <s:v>1559.93</s:v>
+      </s:c>
+      <s:c r="P54" s="1" t="n">
+        <s:v>92</s:v>
+      </s:c>
     </s:row>
     <s:row r="55" s="1" customFormat="1" spans="1:16">
       <s:c r="A55" s="6" t="n">
@@ -5344,17 +6318,39 @@
       <s:c r="E55" s="1" t="n">
         <s:v>377.82</s:v>
       </s:c>
-      <s:c r="F55" s="1"/>
-      <s:c r="G55" s="1"/>
-      <s:c r="H55" s="1"/>
-      <s:c r="I55" s="1"/>
-      <s:c r="J55" s="1"/>
-      <s:c r="K55" s="1"/>
-      <s:c r="L55" s="1"/>
-      <s:c r="M55" s="1"/>
-      <s:c r="N55" s="1"/>
-      <s:c r="O55" s="1"/>
-      <s:c r="P55" s="1"/>
+      <s:c r="F55" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G55" s="1" t="n">
+        <s:v>2650.73</s:v>
+      </s:c>
+      <s:c r="H55" s="1" t="n">
+        <s:v>1.39</s:v>
+      </s:c>
+      <s:c r="I55" s="1" t="n">
+        <s:v>7694.48</s:v>
+      </s:c>
+      <s:c r="J55" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K55" s="1" t="n">
+        <s:v>-1094.3</s:v>
+      </s:c>
+      <s:c r="L55" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M55" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N55" s="1" t="n">
+        <s:v>21041.14</s:v>
+      </s:c>
+      <s:c r="O55" s="1" t="n">
+        <s:v>1592.35</s:v>
+      </s:c>
+      <s:c r="P55" s="1" t="n">
+        <s:v>92</s:v>
+      </s:c>
     </s:row>
     <s:row r="56" s="1" customFormat="1" spans="1:16">
       <s:c r="A56" s="6" t="n">
@@ -5372,17 +6368,39 @@
       <s:c r="E56" s="1" t="n">
         <s:v>363.2</s:v>
       </s:c>
-      <s:c r="F56" s="1"/>
-      <s:c r="G56" s="1"/>
-      <s:c r="H56" s="1"/>
-      <s:c r="I56" s="1"/>
-      <s:c r="J56" s="1"/>
-      <s:c r="K56" s="1"/>
-      <s:c r="L56" s="1"/>
-      <s:c r="M56" s="1"/>
-      <s:c r="N56" s="1"/>
-      <s:c r="O56" s="1"/>
-      <s:c r="P56" s="1"/>
+      <s:c r="F56" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G56" s="1" t="n">
+        <s:v>2654.73</s:v>
+      </s:c>
+      <s:c r="H56" s="1" t="n">
+        <s:v>1.39</s:v>
+      </s:c>
+      <s:c r="I56" s="1" t="n">
+        <s:v>7298.13</s:v>
+      </s:c>
+      <s:c r="J56" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K56" s="1" t="n">
+        <s:v>-1095.8</s:v>
+      </s:c>
+      <s:c r="L56" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M56" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N56" s="1" t="n">
+        <s:v>20454.99</s:v>
+      </s:c>
+      <s:c r="O56" s="1" t="n">
+        <s:v>1718.55</s:v>
+      </s:c>
+      <s:c r="P56" s="1" t="n">
+        <s:v>92</s:v>
+      </s:c>
     </s:row>
     <s:row r="57" s="1" customFormat="1" spans="1:16">
       <s:c r="A57" s="6" t="n">
@@ -5400,17 +6418,39 @@
       <s:c r="E57" s="1" t="n">
         <s:v>356.2</s:v>
       </s:c>
-      <s:c r="F57" s="1"/>
-      <s:c r="G57" s="1"/>
-      <s:c r="H57" s="1"/>
-      <s:c r="I57" s="1"/>
-      <s:c r="J57" s="1"/>
-      <s:c r="K57" s="1"/>
-      <s:c r="L57" s="1"/>
-      <s:c r="M57" s="1"/>
-      <s:c r="N57" s="1"/>
-      <s:c r="O57" s="1"/>
-      <s:c r="P57" s="1"/>
+      <s:c r="F57" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G57" s="1" t="n">
+        <s:v>2632.75</s:v>
+      </s:c>
+      <s:c r="H57" s="1" t="n">
+        <s:v>1.39</s:v>
+      </s:c>
+      <s:c r="I57" s="1" t="n">
+        <s:v>7064.81</s:v>
+      </s:c>
+      <s:c r="J57" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K57" s="1" t="n">
+        <s:v>-791.4</s:v>
+      </s:c>
+      <s:c r="L57" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M57" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N57" s="1" t="n">
+        <s:v>19877.53</s:v>
+      </s:c>
+      <s:c r="O57" s="1" t="n">
+        <s:v>1817.62</s:v>
+      </s:c>
+      <s:c r="P57" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="58" s="1" customFormat="1" spans="1:16">
       <s:c r="A58" s="6" t="n">
@@ -5428,17 +6468,39 @@
       <s:c r="E58" s="1" t="n">
         <s:v>345</s:v>
       </s:c>
-      <s:c r="F58" s="1"/>
-      <s:c r="G58" s="1"/>
-      <s:c r="H58" s="1"/>
-      <s:c r="I58" s="1"/>
-      <s:c r="J58" s="1"/>
-      <s:c r="K58" s="1"/>
-      <s:c r="L58" s="1"/>
-      <s:c r="M58" s="1"/>
-      <s:c r="N58" s="1"/>
-      <s:c r="O58" s="1"/>
-      <s:c r="P58" s="1"/>
+      <s:c r="F58" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G58" s="1" t="n">
+        <s:v>2619.5</s:v>
+      </s:c>
+      <s:c r="H58" s="1" t="n">
+        <s:v>2.01</s:v>
+      </s:c>
+      <s:c r="I58" s="1" t="n">
+        <s:v>6725.11</s:v>
+      </s:c>
+      <s:c r="J58" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K58" s="1" t="n">
+        <s:v>-1336.9</s:v>
+      </s:c>
+      <s:c r="L58" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M58" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N58" s="1" t="n">
+        <s:v>19664.39</s:v>
+      </s:c>
+      <s:c r="O58" s="1" t="n">
+        <s:v>1975.88</s:v>
+      </s:c>
+      <s:c r="P58" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="59" s="1" customFormat="1" spans="1:16">
       <s:c r="A59" s="6" t="n">
@@ -5456,17 +6518,39 @@
       <s:c r="E59" s="1" t="n">
         <s:v>358.33</s:v>
       </s:c>
-      <s:c r="F59" s="1"/>
-      <s:c r="G59" s="1"/>
-      <s:c r="H59" s="1"/>
-      <s:c r="I59" s="1"/>
-      <s:c r="J59" s="1"/>
-      <s:c r="K59" s="1"/>
-      <s:c r="L59" s="1"/>
-      <s:c r="M59" s="1"/>
-      <s:c r="N59" s="1"/>
-      <s:c r="O59" s="1"/>
-      <s:c r="P59" s="1"/>
+      <s:c r="F59" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G59" s="1" t="n">
+        <s:v>2593.06</s:v>
+      </s:c>
+      <s:c r="H59" s="1" t="n">
+        <s:v>2.01</s:v>
+      </s:c>
+      <s:c r="I59" s="1" t="n">
+        <s:v>6471.89</s:v>
+      </s:c>
+      <s:c r="J59" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K59" s="1" t="n">
+        <s:v>-1565.1</s:v>
+      </s:c>
+      <s:c r="L59" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M59" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N59" s="1" t="n">
+        <s:v>20028.23</s:v>
+      </s:c>
+      <s:c r="O59" s="1" t="n">
+        <s:v>2147.89</s:v>
+      </s:c>
+      <s:c r="P59" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="60" s="1" customFormat="1" spans="1:16">
       <s:c r="A60" s="6" t="n">
@@ -5484,17 +6568,39 @@
       <s:c r="E60" s="1" t="n">
         <s:v>378.94</s:v>
       </s:c>
-      <s:c r="F60" s="1"/>
-      <s:c r="G60" s="1"/>
-      <s:c r="H60" s="1"/>
-      <s:c r="I60" s="1"/>
-      <s:c r="J60" s="1"/>
-      <s:c r="K60" s="1"/>
-      <s:c r="L60" s="1"/>
-      <s:c r="M60" s="1"/>
-      <s:c r="N60" s="1"/>
-      <s:c r="O60" s="1"/>
-      <s:c r="P60" s="1"/>
+      <s:c r="F60" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G60" s="1" t="n">
+        <s:v>2595.33</s:v>
+      </s:c>
+      <s:c r="H60" s="1" t="n">
+        <s:v>2.01</s:v>
+      </s:c>
+      <s:c r="I60" s="1" t="n">
+        <s:v>6091.53</s:v>
+      </s:c>
+      <s:c r="J60" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K60" s="1" t="n">
+        <s:v>-1572.2</s:v>
+      </s:c>
+      <s:c r="L60" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M60" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N60" s="1" t="n">
+        <s:v>20924.79</s:v>
+      </s:c>
+      <s:c r="O60" s="1" t="n">
+        <s:v>2337.14</s:v>
+      </s:c>
+      <s:c r="P60" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="61" s="1" customFormat="1" spans="1:16">
       <s:c r="A61" s="6" t="n">
@@ -5512,17 +6618,39 @@
       <s:c r="E61" s="1" t="n">
         <s:v>397.45</s:v>
       </s:c>
-      <s:c r="F61" s="1"/>
-      <s:c r="G61" s="1"/>
-      <s:c r="H61" s="1"/>
-      <s:c r="I61" s="1"/>
-      <s:c r="J61" s="1"/>
-      <s:c r="K61" s="1"/>
-      <s:c r="L61" s="1"/>
-      <s:c r="M61" s="1"/>
-      <s:c r="N61" s="1"/>
-      <s:c r="O61" s="1"/>
-      <s:c r="P61" s="1"/>
+      <s:c r="F61" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G61" s="1" t="n">
+        <s:v>2596.59</s:v>
+      </s:c>
+      <s:c r="H61" s="1" t="n">
+        <s:v>2.01</s:v>
+      </s:c>
+      <s:c r="I61" s="1" t="n">
+        <s:v>5382.73</s:v>
+      </s:c>
+      <s:c r="J61" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K61" s="1" t="n">
+        <s:v>-1565.5</s:v>
+      </s:c>
+      <s:c r="L61" s="1" t="n">
+        <s:v>200</s:v>
+      </s:c>
+      <s:c r="M61" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N61" s="1" t="n">
+        <s:v>21776.12</s:v>
+      </s:c>
+      <s:c r="O61" s="1" t="n">
+        <s:v>2551.04</s:v>
+      </s:c>
+      <s:c r="P61" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="62" s="1" customFormat="1" spans="1:16">
       <s:c r="A62" s="6" t="n">
@@ -5540,17 +6668,39 @@
       <s:c r="E62" s="1" t="n">
         <s:v>424.86</s:v>
       </s:c>
-      <s:c r="F62" s="1"/>
-      <s:c r="G62" s="1"/>
-      <s:c r="H62" s="1"/>
-      <s:c r="I62" s="1"/>
-      <s:c r="J62" s="1"/>
-      <s:c r="K62" s="1"/>
-      <s:c r="L62" s="1"/>
-      <s:c r="M62" s="1"/>
-      <s:c r="N62" s="1"/>
-      <s:c r="O62" s="1"/>
-      <s:c r="P62" s="1"/>
+      <s:c r="F62" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G62" s="1" t="n">
+        <s:v>2530.91</s:v>
+      </s:c>
+      <s:c r="H62" s="1" t="n">
+        <s:v>2.23</s:v>
+      </s:c>
+      <s:c r="I62" s="1" t="n">
+        <s:v>4820.88</s:v>
+      </s:c>
+      <s:c r="J62" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K62" s="1" t="n">
+        <s:v>-1555.2</s:v>
+      </s:c>
+      <s:c r="L62" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M62" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N62" s="1" t="n">
+        <s:v>22845.49</s:v>
+      </s:c>
+      <s:c r="O62" s="1" t="n">
+        <s:v>2655.57</s:v>
+      </s:c>
+      <s:c r="P62" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="63" s="1" customFormat="1" spans="1:16">
       <s:c r="A63" s="6" t="n">
@@ -5568,17 +6718,39 @@
       <s:c r="E63" s="1" t="n">
         <s:v>440</s:v>
       </s:c>
-      <s:c r="F63" s="1"/>
-      <s:c r="G63" s="1"/>
-      <s:c r="H63" s="1"/>
-      <s:c r="I63" s="1"/>
-      <s:c r="J63" s="1"/>
-      <s:c r="K63" s="1"/>
-      <s:c r="L63" s="1"/>
-      <s:c r="M63" s="1"/>
-      <s:c r="N63" s="1"/>
-      <s:c r="O63" s="1"/>
-      <s:c r="P63" s="1"/>
+      <s:c r="F63" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G63" s="1" t="n">
+        <s:v>2503.75</s:v>
+      </s:c>
+      <s:c r="H63" s="1" t="n">
+        <s:v>2.23</s:v>
+      </s:c>
+      <s:c r="I63" s="1" t="n">
+        <s:v>4276.38</s:v>
+      </s:c>
+      <s:c r="J63" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K63" s="1" t="n">
+        <s:v>-1315.1</s:v>
+      </s:c>
+      <s:c r="L63" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M63" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N63" s="1" t="n">
+        <s:v>23364.66</s:v>
+      </s:c>
+      <s:c r="O63" s="1" t="n">
+        <s:v>2735.58</s:v>
+      </s:c>
+      <s:c r="P63" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="64" s="1" customFormat="1" spans="1:16">
       <s:c r="A64" s="6" t="n">
@@ -5596,17 +6768,39 @@
       <s:c r="E64" s="1" t="n">
         <s:v>441.42</s:v>
       </s:c>
-      <s:c r="F64" s="1"/>
-      <s:c r="G64" s="1"/>
-      <s:c r="H64" s="1"/>
-      <s:c r="I64" s="1"/>
-      <s:c r="J64" s="1"/>
-      <s:c r="K64" s="1"/>
-      <s:c r="L64" s="1"/>
-      <s:c r="M64" s="1"/>
-      <s:c r="N64" s="1"/>
-      <s:c r="O64" s="1"/>
-      <s:c r="P64" s="1"/>
+      <s:c r="F64" s="1" t="n">
+        <s:v>60</s:v>
+      </s:c>
+      <s:c r="G64" s="1" t="n">
+        <s:v>2475.26</s:v>
+      </s:c>
+      <s:c r="H64" s="1" t="n">
+        <s:v>2.23</s:v>
+      </s:c>
+      <s:c r="I64" s="1" t="n">
+        <s:v>3947.01</s:v>
+      </s:c>
+      <s:c r="J64" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K64" s="1" t="n">
+        <s:v>-1068.9</s:v>
+      </s:c>
+      <s:c r="L64" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M64" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N64" s="1" t="n">
+        <s:v>23936.96</s:v>
+      </s:c>
+      <s:c r="O64" s="1" t="n">
+        <s:v>2854.24</s:v>
+      </s:c>
+      <s:c r="P64" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="65" s="1" customFormat="1" spans="1:16">
       <s:c r="A65" s="6" t="n">
@@ -5624,17 +6818,39 @@
       <s:c r="E65" s="1" t="n">
         <s:v>440.3</s:v>
       </s:c>
-      <s:c r="F65" s="1"/>
-      <s:c r="G65" s="1"/>
-      <s:c r="H65" s="1"/>
-      <s:c r="I65" s="1"/>
-      <s:c r="J65" s="1"/>
-      <s:c r="K65" s="1"/>
-      <s:c r="L65" s="1"/>
-      <s:c r="M65" s="1"/>
-      <s:c r="N65" s="1"/>
-      <s:c r="O65" s="1"/>
-      <s:c r="P65" s="1"/>
+      <s:c r="F65" s="1" t="n">
+        <s:v>150</s:v>
+      </s:c>
+      <s:c r="G65" s="1" t="n">
+        <s:v>2419.05</s:v>
+      </s:c>
+      <s:c r="H65" s="1" t="n">
+        <s:v>2.23</s:v>
+      </s:c>
+      <s:c r="I65" s="1" t="n">
+        <s:v>3520.74</s:v>
+      </s:c>
+      <s:c r="J65" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K65" s="1" t="n">
+        <s:v>-589</s:v>
+      </s:c>
+      <s:c r="L65" s="1" t="n">
+        <s:v>107.96</s:v>
+      </s:c>
+      <s:c r="M65" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N65" s="1" t="n">
+        <s:v>23861.58</s:v>
+      </s:c>
+      <s:c r="O65" s="1" t="n">
+        <s:v>3114.32</s:v>
+      </s:c>
+      <s:c r="P65" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="66" s="1" customFormat="1" spans="1:16">
       <s:c r="A66" s="6" t="n">
@@ -5652,17 +6868,39 @@
       <s:c r="E66" s="1" t="n">
         <s:v>441.44</s:v>
       </s:c>
-      <s:c r="F66" s="1"/>
-      <s:c r="G66" s="1"/>
-      <s:c r="H66" s="1"/>
-      <s:c r="I66" s="1"/>
-      <s:c r="J66" s="1"/>
-      <s:c r="K66" s="1"/>
-      <s:c r="L66" s="1"/>
-      <s:c r="M66" s="1"/>
-      <s:c r="N66" s="1"/>
-      <s:c r="O66" s="1"/>
-      <s:c r="P66" s="1"/>
+      <s:c r="F66" s="1" t="n">
+        <s:v>440</s:v>
+      </s:c>
+      <s:c r="G66" s="1" t="n">
+        <s:v>2375.36</s:v>
+      </s:c>
+      <s:c r="H66" s="1" t="n">
+        <s:v>1.75</s:v>
+      </s:c>
+      <s:c r="I66" s="1" t="n">
+        <s:v>3185.81</s:v>
+      </s:c>
+      <s:c r="J66" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K66" s="1" t="n">
+        <s:v>-589.4</s:v>
+      </s:c>
+      <s:c r="L66" s="1" t="n">
+        <s:v>132.97</s:v>
+      </s:c>
+      <s:c r="M66" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N66" s="1" t="n">
+        <s:v>24391.96</s:v>
+      </s:c>
+      <s:c r="O66" s="1" t="n">
+        <s:v>3150.24</s:v>
+      </s:c>
+      <s:c r="P66" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="67" s="1" customFormat="1" spans="1:16">
       <s:c r="A67" s="6" t="n">
@@ -5680,17 +6918,39 @@
       <s:c r="E67" s="1" t="n">
         <s:v>443.35</s:v>
       </s:c>
-      <s:c r="F67" s="1"/>
-      <s:c r="G67" s="1"/>
-      <s:c r="H67" s="1"/>
-      <s:c r="I67" s="1"/>
-      <s:c r="J67" s="1"/>
-      <s:c r="K67" s="1"/>
-      <s:c r="L67" s="1"/>
-      <s:c r="M67" s="1"/>
-      <s:c r="N67" s="1"/>
-      <s:c r="O67" s="1"/>
-      <s:c r="P67" s="1"/>
+      <s:c r="F67" s="1" t="n">
+        <s:v>685</s:v>
+      </s:c>
+      <s:c r="G67" s="1" t="n">
+        <s:v>2368.59</s:v>
+      </s:c>
+      <s:c r="H67" s="1" t="n">
+        <s:v>1.75</s:v>
+      </s:c>
+      <s:c r="I67" s="1" t="n">
+        <s:v>2809.84</s:v>
+      </s:c>
+      <s:c r="J67" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K67" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="L67" s="1" t="n">
+        <s:v>134.55</s:v>
+      </s:c>
+      <s:c r="M67" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N67" s="1" t="n">
+        <s:v>24781.21</s:v>
+      </s:c>
+      <s:c r="O67" s="1" t="n">
+        <s:v>3120.74</s:v>
+      </s:c>
+      <s:c r="P67" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="68" s="1" customFormat="1" spans="1:16">
       <s:c r="A68" s="6" t="n">
@@ -5708,17 +6968,39 @@
       <s:c r="E68" s="1" t="n">
         <s:v>452.95</s:v>
       </s:c>
-      <s:c r="F68" s="1"/>
-      <s:c r="G68" s="1"/>
-      <s:c r="H68" s="1"/>
-      <s:c r="I68" s="1"/>
-      <s:c r="J68" s="1"/>
-      <s:c r="K68" s="1"/>
-      <s:c r="L68" s="1"/>
-      <s:c r="M68" s="1"/>
-      <s:c r="N68" s="1"/>
-      <s:c r="O68" s="1"/>
-      <s:c r="P68" s="1"/>
+      <s:c r="F68" s="1" t="n">
+        <s:v>915</s:v>
+      </s:c>
+      <s:c r="G68" s="1" t="n">
+        <s:v>2346.19</s:v>
+      </s:c>
+      <s:c r="H68" s="1" t="n">
+        <s:v>1.75</s:v>
+      </s:c>
+      <s:c r="I68" s="1" t="n">
+        <s:v>2545.8</s:v>
+      </s:c>
+      <s:c r="J68" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K68" s="1" t="n">
+        <s:v>150.1</s:v>
+      </s:c>
+      <s:c r="L68" s="1" t="n">
+        <s:v>166.48</s:v>
+      </s:c>
+      <s:c r="M68" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N68" s="1" t="n">
+        <s:v>25406.27</s:v>
+      </s:c>
+      <s:c r="O68" s="1" t="n">
+        <s:v>3211.9</s:v>
+      </s:c>
+      <s:c r="P68" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="69" s="1" customFormat="1" spans="1:16">
       <s:c r="A69" s="6" t="n">
@@ -5736,17 +7018,39 @@
       <s:c r="E69" s="1" t="n">
         <s:v>453.86</s:v>
       </s:c>
-      <s:c r="F69" s="1"/>
-      <s:c r="G69" s="1"/>
-      <s:c r="H69" s="1"/>
-      <s:c r="I69" s="1"/>
-      <s:c r="J69" s="1"/>
-      <s:c r="K69" s="1"/>
-      <s:c r="L69" s="1"/>
-      <s:c r="M69" s="1"/>
-      <s:c r="N69" s="1"/>
-      <s:c r="O69" s="1"/>
-      <s:c r="P69" s="1"/>
+      <s:c r="F69" s="1" t="n">
+        <s:v>1000</s:v>
+      </s:c>
+      <s:c r="G69" s="1" t="n">
+        <s:v>2332.39</s:v>
+      </s:c>
+      <s:c r="H69" s="1" t="n">
+        <s:v>1.75</s:v>
+      </s:c>
+      <s:c r="I69" s="1" t="n">
+        <s:v>2318.19</s:v>
+      </s:c>
+      <s:c r="J69" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K69" s="1" t="n">
+        <s:v>282.4</s:v>
+      </s:c>
+      <s:c r="L69" s="1" t="n">
+        <s:v>238.37</s:v>
+      </s:c>
+      <s:c r="M69" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N69" s="1" t="n">
+        <s:v>25533.93</s:v>
+      </s:c>
+      <s:c r="O69" s="1" t="n">
+        <s:v>3374.17</s:v>
+      </s:c>
+      <s:c r="P69" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="70" s="1" customFormat="1" spans="1:16">
       <s:c r="A70" s="6" t="n">
@@ -5764,17 +7068,39 @@
       <s:c r="E70" s="1" t="n">
         <s:v>458.22</s:v>
       </s:c>
-      <s:c r="F70" s="1"/>
-      <s:c r="G70" s="1"/>
-      <s:c r="H70" s="1"/>
-      <s:c r="I70" s="1"/>
-      <s:c r="J70" s="1"/>
-      <s:c r="K70" s="1"/>
-      <s:c r="L70" s="1"/>
-      <s:c r="M70" s="1"/>
-      <s:c r="N70" s="1"/>
-      <s:c r="O70" s="1"/>
-      <s:c r="P70" s="1"/>
+      <s:c r="F70" s="1" t="n">
+        <s:v>1055</s:v>
+      </s:c>
+      <s:c r="G70" s="1" t="n">
+        <s:v>2303.02</s:v>
+      </s:c>
+      <s:c r="H70" s="1" t="n">
+        <s:v>0.51</s:v>
+      </s:c>
+      <s:c r="I70" s="1" t="n">
+        <s:v>2072.8</s:v>
+      </s:c>
+      <s:c r="J70" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K70" s="1" t="n">
+        <s:v>594.7</s:v>
+      </s:c>
+      <s:c r="L70" s="1" t="n">
+        <s:v>387.03</s:v>
+      </s:c>
+      <s:c r="M70" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N70" s="1" t="n">
+        <s:v>25914.65</s:v>
+      </s:c>
+      <s:c r="O70" s="1" t="n">
+        <s:v>3390.49</s:v>
+      </s:c>
+      <s:c r="P70" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="71" s="1" customFormat="1" spans="1:16">
       <s:c r="A71" s="6" t="n">
@@ -5792,17 +7118,39 @@
       <s:c r="E71" s="1" t="n">
         <s:v>453.29</s:v>
       </s:c>
-      <s:c r="F71" s="1"/>
-      <s:c r="G71" s="1"/>
-      <s:c r="H71" s="1"/>
-      <s:c r="I71" s="1"/>
-      <s:c r="J71" s="1"/>
-      <s:c r="K71" s="1"/>
-      <s:c r="L71" s="1"/>
-      <s:c r="M71" s="1"/>
-      <s:c r="N71" s="1"/>
-      <s:c r="O71" s="1"/>
-      <s:c r="P71" s="1"/>
+      <s:c r="F71" s="1" t="n">
+        <s:v>1010</s:v>
+      </s:c>
+      <s:c r="G71" s="1" t="n">
+        <s:v>2285.87</s:v>
+      </s:c>
+      <s:c r="H71" s="1" t="n">
+        <s:v>0.51</s:v>
+      </s:c>
+      <s:c r="I71" s="1" t="n">
+        <s:v>1725.46</s:v>
+      </s:c>
+      <s:c r="J71" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K71" s="1" t="n">
+        <s:v>595.7</s:v>
+      </s:c>
+      <s:c r="L71" s="1" t="n">
+        <s:v>439.83</s:v>
+      </s:c>
+      <s:c r="M71" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N71" s="1" t="n">
+        <s:v>25465.44</s:v>
+      </s:c>
+      <s:c r="O71" s="1" t="n">
+        <s:v>3433.4</s:v>
+      </s:c>
+      <s:c r="P71" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="72" s="1" customFormat="1" spans="1:16">
       <s:c r="A72" s="6" t="n">
@@ -5820,17 +7168,39 @@
       <s:c r="E72" s="1" t="n">
         <s:v>448.5</s:v>
       </s:c>
-      <s:c r="F72" s="1"/>
-      <s:c r="G72" s="1"/>
-      <s:c r="H72" s="1"/>
-      <s:c r="I72" s="1"/>
-      <s:c r="J72" s="1"/>
-      <s:c r="K72" s="1"/>
-      <s:c r="L72" s="1"/>
-      <s:c r="M72" s="1"/>
-      <s:c r="N72" s="1"/>
-      <s:c r="O72" s="1"/>
-      <s:c r="P72" s="1"/>
+      <s:c r="F72" s="1" t="n">
+        <s:v>1010</s:v>
+      </s:c>
+      <s:c r="G72" s="1" t="n">
+        <s:v>2276.97</s:v>
+      </s:c>
+      <s:c r="H72" s="1" t="n">
+        <s:v>0.51</s:v>
+      </s:c>
+      <s:c r="I72" s="1" t="n">
+        <s:v>1347.54</s:v>
+      </s:c>
+      <s:c r="J72" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K72" s="1" t="n">
+        <s:v>750.9</s:v>
+      </s:c>
+      <s:c r="L72" s="1" t="n">
+        <s:v>455.9</s:v>
+      </s:c>
+      <s:c r="M72" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N72" s="1" t="n">
+        <s:v>24945.12</s:v>
+      </s:c>
+      <s:c r="O72" s="1" t="n">
+        <s:v>3506.06</s:v>
+      </s:c>
+      <s:c r="P72" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="73" s="1" customFormat="1" spans="1:16">
       <s:c r="A73" s="6" t="n">
@@ -5848,17 +7218,39 @@
       <s:c r="E73" s="1" t="n">
         <s:v>439.26</s:v>
       </s:c>
-      <s:c r="F73" s="1"/>
-      <s:c r="G73" s="1"/>
-      <s:c r="H73" s="1"/>
-      <s:c r="I73" s="1"/>
-      <s:c r="J73" s="1"/>
-      <s:c r="K73" s="1"/>
-      <s:c r="L73" s="1"/>
-      <s:c r="M73" s="1"/>
-      <s:c r="N73" s="1"/>
-      <s:c r="O73" s="1"/>
-      <s:c r="P73" s="1"/>
+      <s:c r="F73" s="1" t="n">
+        <s:v>825</s:v>
+      </s:c>
+      <s:c r="G73" s="1" t="n">
+        <s:v>2316.35</s:v>
+      </s:c>
+      <s:c r="H73" s="1" t="n">
+        <s:v>0.51</s:v>
+      </s:c>
+      <s:c r="I73" s="1" t="n">
+        <s:v>1058.32</s:v>
+      </s:c>
+      <s:c r="J73" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K73" s="1" t="n">
+        <s:v>750.1</s:v>
+      </s:c>
+      <s:c r="L73" s="1" t="n">
+        <s:v>580.98</s:v>
+      </s:c>
+      <s:c r="M73" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N73" s="1" t="n">
+        <s:v>23888.35</s:v>
+      </s:c>
+      <s:c r="O73" s="1" t="n">
+        <s:v>3660.29</s:v>
+      </s:c>
+      <s:c r="P73" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="74" s="1" customFormat="1" spans="1:16">
       <s:c r="A74" s="6" t="n">
@@ -5876,17 +7268,39 @@
       <s:c r="E74" s="1" t="n">
         <s:v>424.86</s:v>
       </s:c>
-      <s:c r="F74" s="1"/>
-      <s:c r="G74" s="1"/>
-      <s:c r="H74" s="1"/>
-      <s:c r="I74" s="1"/>
-      <s:c r="J74" s="1"/>
-      <s:c r="K74" s="1"/>
-      <s:c r="L74" s="1"/>
-      <s:c r="M74" s="1"/>
-      <s:c r="N74" s="1"/>
-      <s:c r="O74" s="1"/>
-      <s:c r="P74" s="1"/>
+      <s:c r="F74" s="1" t="n">
+        <s:v>480</s:v>
+      </s:c>
+      <s:c r="G74" s="1" t="n">
+        <s:v>2284.43</s:v>
+      </s:c>
+      <s:c r="H74" s="1" t="n">
+        <s:v>0.08</s:v>
+      </s:c>
+      <s:c r="I74" s="1" t="n">
+        <s:v>838.53</s:v>
+      </s:c>
+      <s:c r="J74" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K74" s="1" t="n">
+        <s:v>750.8</s:v>
+      </s:c>
+      <s:c r="L74" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M74" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N74" s="1" t="n">
+        <s:v>23382.3</s:v>
+      </s:c>
+      <s:c r="O74" s="1" t="n">
+        <s:v>3946.75</s:v>
+      </s:c>
+      <s:c r="P74" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="75" s="1" customFormat="1" spans="1:16">
       <s:c r="A75" s="6" t="n">
@@ -5904,17 +7318,39 @@
       <s:c r="E75" s="1" t="n">
         <s:v>424.86</s:v>
       </s:c>
-      <s:c r="F75" s="1"/>
-      <s:c r="G75" s="1"/>
-      <s:c r="H75" s="1"/>
-      <s:c r="I75" s="1"/>
-      <s:c r="J75" s="1"/>
-      <s:c r="K75" s="1"/>
-      <s:c r="L75" s="1"/>
-      <s:c r="M75" s="1"/>
-      <s:c r="N75" s="1"/>
-      <s:c r="O75" s="1"/>
-      <s:c r="P75" s="1"/>
+      <s:c r="F75" s="1" t="n">
+        <s:v>270</s:v>
+      </s:c>
+      <s:c r="G75" s="1" t="n">
+        <s:v>2306.06</s:v>
+      </s:c>
+      <s:c r="H75" s="1" t="n">
+        <s:v>0.08</s:v>
+      </s:c>
+      <s:c r="I75" s="1" t="n">
+        <s:v>642.24</s:v>
+      </s:c>
+      <s:c r="J75" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K75" s="1" t="n">
+        <s:v>750.1</s:v>
+      </s:c>
+      <s:c r="L75" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M75" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N75" s="1" t="n">
+        <s:v>23063.49</s:v>
+      </s:c>
+      <s:c r="O75" s="1" t="n">
+        <s:v>4314.22</s:v>
+      </s:c>
+      <s:c r="P75" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="76" s="1" customFormat="1" spans="1:16">
       <s:c r="A76" s="6" t="n">
@@ -5932,17 +7368,39 @@
       <s:c r="E76" s="1" t="n">
         <s:v>423.29</s:v>
       </s:c>
-      <s:c r="F76" s="1"/>
-      <s:c r="G76" s="1"/>
-      <s:c r="H76" s="1"/>
-      <s:c r="I76" s="1"/>
-      <s:c r="J76" s="1"/>
-      <s:c r="K76" s="1"/>
-      <s:c r="L76" s="1"/>
-      <s:c r="M76" s="1"/>
-      <s:c r="N76" s="1"/>
-      <s:c r="O76" s="1"/>
-      <s:c r="P76" s="1"/>
+      <s:c r="F76" s="1" t="n">
+        <s:v>210</s:v>
+      </s:c>
+      <s:c r="G76" s="1" t="n">
+        <s:v>2290.42</s:v>
+      </s:c>
+      <s:c r="H76" s="1" t="n">
+        <s:v>0.08</s:v>
+      </s:c>
+      <s:c r="I76" s="1" t="n">
+        <s:v>429.67</s:v>
+      </s:c>
+      <s:c r="J76" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K76" s="1" t="n">
+        <s:v>749.6</s:v>
+      </s:c>
+      <s:c r="L76" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M76" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N76" s="1" t="n">
+        <s:v>22793.07</s:v>
+      </s:c>
+      <s:c r="O76" s="1" t="n">
+        <s:v>4505.05</s:v>
+      </s:c>
+      <s:c r="P76" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="77" s="1" customFormat="1" spans="1:16">
       <s:c r="A77" s="6" t="n">
@@ -5960,17 +7418,39 @@
       <s:c r="E77" s="1" t="n">
         <s:v>422.94</s:v>
       </s:c>
-      <s:c r="F77" s="1"/>
-      <s:c r="G77" s="1"/>
-      <s:c r="H77" s="1"/>
-      <s:c r="I77" s="1"/>
-      <s:c r="J77" s="1"/>
-      <s:c r="K77" s="1"/>
-      <s:c r="L77" s="1"/>
-      <s:c r="M77" s="1"/>
-      <s:c r="N77" s="1"/>
-      <s:c r="O77" s="1"/>
-      <s:c r="P77" s="1"/>
+      <s:c r="F77" s="1" t="n">
+        <s:v>90</s:v>
+      </s:c>
+      <s:c r="G77" s="1" t="n">
+        <s:v>2257.04</s:v>
+      </s:c>
+      <s:c r="H77" s="1" t="n">
+        <s:v>0.08</s:v>
+      </s:c>
+      <s:c r="I77" s="1" t="n">
+        <s:v>354.36</s:v>
+      </s:c>
+      <s:c r="J77" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K77" s="1" t="n">
+        <s:v>751.2</s:v>
+      </s:c>
+      <s:c r="L77" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M77" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N77" s="1" t="n">
+        <s:v>22798.97</s:v>
+      </s:c>
+      <s:c r="O77" s="1" t="n">
+        <s:v>4384.05</s:v>
+      </s:c>
+      <s:c r="P77" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="78" s="1" customFormat="1" spans="1:16">
       <s:c r="A78" s="6" t="n">
@@ -5988,17 +7468,39 @@
       <s:c r="E78" s="1" t="n">
         <s:v>422.94</s:v>
       </s:c>
-      <s:c r="F78" s="1"/>
-      <s:c r="G78" s="1"/>
-      <s:c r="H78" s="1"/>
-      <s:c r="I78" s="1"/>
-      <s:c r="J78" s="1"/>
-      <s:c r="K78" s="1"/>
-      <s:c r="L78" s="1"/>
-      <s:c r="M78" s="1"/>
-      <s:c r="N78" s="1"/>
-      <s:c r="O78" s="1"/>
-      <s:c r="P78" s="1"/>
+      <s:c r="F78" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G78" s="1" t="n">
+        <s:v>2268.97</s:v>
+      </s:c>
+      <s:c r="H78" s="1" t="n">
+        <s:v>0.34</s:v>
+      </s:c>
+      <s:c r="I78" s="1" t="n">
+        <s:v>270.48</s:v>
+      </s:c>
+      <s:c r="J78" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K78" s="1" t="n">
+        <s:v>750.8</s:v>
+      </s:c>
+      <s:c r="L78" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M78" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N78" s="1" t="n">
+        <s:v>22755.21</s:v>
+      </s:c>
+      <s:c r="O78" s="1" t="n">
+        <s:v>4154</s:v>
+      </s:c>
+      <s:c r="P78" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="79" s="1" customFormat="1" spans="1:16">
       <s:c r="A79" s="6" t="n">
@@ -6016,17 +7518,39 @@
       <s:c r="E79" s="1" t="n">
         <s:v>418.98</s:v>
       </s:c>
-      <s:c r="F79" s="1"/>
-      <s:c r="G79" s="1"/>
-      <s:c r="H79" s="1"/>
-      <s:c r="I79" s="1"/>
-      <s:c r="J79" s="1"/>
-      <s:c r="K79" s="1"/>
-      <s:c r="L79" s="1"/>
-      <s:c r="M79" s="1"/>
-      <s:c r="N79" s="1"/>
-      <s:c r="O79" s="1"/>
-      <s:c r="P79" s="1"/>
+      <s:c r="F79" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G79" s="1" t="n">
+        <s:v>2215.86</s:v>
+      </s:c>
+      <s:c r="H79" s="1" t="n">
+        <s:v>0.34</s:v>
+      </s:c>
+      <s:c r="I79" s="1" t="n">
+        <s:v>185.54</s:v>
+      </s:c>
+      <s:c r="J79" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K79" s="1" t="n">
+        <s:v>754.9</s:v>
+      </s:c>
+      <s:c r="L79" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M79" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N79" s="1" t="n">
+        <s:v>22370.53</s:v>
+      </s:c>
+      <s:c r="O79" s="1" t="n">
+        <s:v>4465.02</s:v>
+      </s:c>
+      <s:c r="P79" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="80" s="1" customFormat="1" spans="1:16">
       <s:c r="A80" s="6" t="n">
@@ -6044,17 +7568,39 @@
       <s:c r="E80" s="1" t="n">
         <s:v>423.6</s:v>
       </s:c>
-      <s:c r="F80" s="1"/>
-      <s:c r="G80" s="1"/>
-      <s:c r="H80" s="1"/>
-      <s:c r="I80" s="1"/>
-      <s:c r="J80" s="1"/>
-      <s:c r="K80" s="1"/>
-      <s:c r="L80" s="1"/>
-      <s:c r="M80" s="1"/>
-      <s:c r="N80" s="1"/>
-      <s:c r="O80" s="1"/>
-      <s:c r="P80" s="1"/>
+      <s:c r="F80" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G80" s="1" t="n">
+        <s:v>2198.39</s:v>
+      </s:c>
+      <s:c r="H80" s="1" t="n">
+        <s:v>0.34</s:v>
+      </s:c>
+      <s:c r="I80" s="1" t="n">
+        <s:v>162.22</s:v>
+      </s:c>
+      <s:c r="J80" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K80" s="1" t="n">
+        <s:v>751.3</s:v>
+      </s:c>
+      <s:c r="L80" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M80" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N80" s="1" t="n">
+        <s:v>22797.71</s:v>
+      </s:c>
+      <s:c r="O80" s="1" t="n">
+        <s:v>4597.83</s:v>
+      </s:c>
+      <s:c r="P80" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="81" s="1" customFormat="1" spans="1:16">
       <s:c r="A81" s="6" t="n">
@@ -6072,17 +7618,39 @@
       <s:c r="E81" s="1" t="n">
         <s:v>413.44</s:v>
       </s:c>
-      <s:c r="F81" s="1"/>
-      <s:c r="G81" s="1"/>
-      <s:c r="H81" s="1"/>
-      <s:c r="I81" s="1"/>
-      <s:c r="J81" s="1"/>
-      <s:c r="K81" s="1"/>
-      <s:c r="L81" s="1"/>
-      <s:c r="M81" s="1"/>
-      <s:c r="N81" s="1"/>
-      <s:c r="O81" s="1"/>
-      <s:c r="P81" s="1"/>
+      <s:c r="F81" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G81" s="1" t="n">
+        <s:v>2227.19</s:v>
+      </s:c>
+      <s:c r="H81" s="1" t="n">
+        <s:v>0.34</s:v>
+      </s:c>
+      <s:c r="I81" s="1" t="n">
+        <s:v>166.8</s:v>
+      </s:c>
+      <s:c r="J81" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K81" s="1" t="n">
+        <s:v>746.6</s:v>
+      </s:c>
+      <s:c r="L81" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M81" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N81" s="1" t="n">
+        <s:v>22736.24</s:v>
+      </s:c>
+      <s:c r="O81" s="1" t="n">
+        <s:v>4410.33</s:v>
+      </s:c>
+      <s:c r="P81" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="82" s="1" customFormat="1" spans="1:16">
       <s:c r="A82" s="6" t="n">
@@ -6100,17 +7668,39 @@
       <s:c r="E82" s="1" t="n">
         <s:v>405.76</s:v>
       </s:c>
-      <s:c r="F82" s="1"/>
-      <s:c r="G82" s="1"/>
-      <s:c r="H82" s="1"/>
-      <s:c r="I82" s="1"/>
-      <s:c r="J82" s="1"/>
-      <s:c r="K82" s="1"/>
-      <s:c r="L82" s="1"/>
-      <s:c r="M82" s="1"/>
-      <s:c r="N82" s="1"/>
-      <s:c r="O82" s="1"/>
-      <s:c r="P82" s="1"/>
+      <s:c r="F82" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G82" s="1" t="n">
+        <s:v>2203.39</s:v>
+      </s:c>
+      <s:c r="H82" s="1" t="n">
+        <s:v>0.34</s:v>
+      </s:c>
+      <s:c r="I82" s="1" t="n">
+        <s:v>168.5</s:v>
+      </s:c>
+      <s:c r="J82" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K82" s="1" t="n">
+        <s:v>752.3</s:v>
+      </s:c>
+      <s:c r="L82" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M82" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N82" s="1" t="n">
+        <s:v>22718.09</s:v>
+      </s:c>
+      <s:c r="O82" s="1" t="n">
+        <s:v>4155.18</s:v>
+      </s:c>
+      <s:c r="P82" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="83" s="1" customFormat="1" spans="1:16">
       <s:c r="A83" s="6" t="n">
@@ -6128,17 +7718,39 @@
       <s:c r="E83" s="1" t="n">
         <s:v>390.91</s:v>
       </s:c>
-      <s:c r="F83" s="1"/>
-      <s:c r="G83" s="1"/>
-      <s:c r="H83" s="1"/>
-      <s:c r="I83" s="1"/>
-      <s:c r="J83" s="1"/>
-      <s:c r="K83" s="1"/>
-      <s:c r="L83" s="1"/>
-      <s:c r="M83" s="1"/>
-      <s:c r="N83" s="1"/>
-      <s:c r="O83" s="1"/>
-      <s:c r="P83" s="1"/>
+      <s:c r="F83" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G83" s="1" t="n">
+        <s:v>2202.52</s:v>
+      </s:c>
+      <s:c r="H83" s="1" t="n">
+        <s:v>0.34</s:v>
+      </s:c>
+      <s:c r="I83" s="1" t="n">
+        <s:v>182.5</s:v>
+      </s:c>
+      <s:c r="J83" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K83" s="1" t="n">
+        <s:v>747</s:v>
+      </s:c>
+      <s:c r="L83" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M83" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N83" s="1" t="n">
+        <s:v>22259.55</s:v>
+      </s:c>
+      <s:c r="O83" s="1" t="n">
+        <s:v>4463.78</s:v>
+      </s:c>
+      <s:c r="P83" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="84" s="1" customFormat="1" spans="1:16">
       <s:c r="A84" s="6" t="n">
@@ -6156,17 +7768,39 @@
       <s:c r="E84" s="1" t="n">
         <s:v>391.2</s:v>
       </s:c>
-      <s:c r="F84" s="1"/>
-      <s:c r="G84" s="1"/>
-      <s:c r="H84" s="1"/>
-      <s:c r="I84" s="1"/>
-      <s:c r="J84" s="1"/>
-      <s:c r="K84" s="1"/>
-      <s:c r="L84" s="1"/>
-      <s:c r="M84" s="1"/>
-      <s:c r="N84" s="1"/>
-      <s:c r="O84" s="1"/>
-      <s:c r="P84" s="1"/>
+      <s:c r="F84" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G84" s="1" t="n">
+        <s:v>2203.92</s:v>
+      </s:c>
+      <s:c r="H84" s="1" t="n">
+        <s:v>0.34</s:v>
+      </s:c>
+      <s:c r="I84" s="1" t="n">
+        <s:v>115.6</s:v>
+      </s:c>
+      <s:c r="J84" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K84" s="1" t="n">
+        <s:v>750.6</s:v>
+      </s:c>
+      <s:c r="L84" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M84" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N84" s="1" t="n">
+        <s:v>22416.58</s:v>
+      </s:c>
+      <s:c r="O84" s="1" t="n">
+        <s:v>4316.95</s:v>
+      </s:c>
+      <s:c r="P84" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="85" s="1" customFormat="1" spans="1:16">
       <s:c r="A85" s="6" t="n">
@@ -6184,17 +7818,39 @@
       <s:c r="E85" s="1" t="n">
         <s:v>390.23</s:v>
       </s:c>
-      <s:c r="F85" s="1"/>
-      <s:c r="G85" s="1"/>
-      <s:c r="H85" s="1"/>
-      <s:c r="I85" s="1"/>
-      <s:c r="J85" s="1"/>
-      <s:c r="K85" s="1"/>
-      <s:c r="L85" s="1"/>
-      <s:c r="M85" s="1"/>
-      <s:c r="N85" s="1"/>
-      <s:c r="O85" s="1"/>
-      <s:c r="P85" s="1"/>
+      <s:c r="F85" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="G85" s="1" t="n">
+        <s:v>2238.1</s:v>
+      </s:c>
+      <s:c r="H85" s="1" t="n">
+        <s:v>0.34</s:v>
+      </s:c>
+      <s:c r="I85" s="1" t="n">
+        <s:v>106.15</s:v>
+      </s:c>
+      <s:c r="J85" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K85" s="1" t="n">
+        <s:v>750.5</s:v>
+      </s:c>
+      <s:c r="L85" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M85" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N85" s="1" t="n">
+        <s:v>22282.02</s:v>
+      </s:c>
+      <s:c r="O85" s="1" t="n">
+        <s:v>3917.89</s:v>
+      </s:c>
+      <s:c r="P85" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="86" s="1" customFormat="1" spans="1:16">
       <s:c r="A86" s="6" t="n">
@@ -6212,17 +7868,39 @@
       <s:c r="E86" s="1" t="n">
         <s:v>390.76</s:v>
       </s:c>
-      <s:c r="F86" s="1"/>
-      <s:c r="G86" s="1"/>
-      <s:c r="H86" s="1"/>
-      <s:c r="I86" s="1"/>
-      <s:c r="J86" s="1"/>
-      <s:c r="K86" s="1"/>
-      <s:c r="L86" s="1"/>
-      <s:c r="M86" s="1"/>
-      <s:c r="N86" s="1"/>
-      <s:c r="O86" s="1"/>
-      <s:c r="P86" s="1"/>
+      <s:c r="F86" s="1" t="n">
+        <s:v>100</s:v>
+      </s:c>
+      <s:c r="G86" s="1" t="n">
+        <s:v>2133.18</s:v>
+      </s:c>
+      <s:c r="H86" s="1" t="n">
+        <s:v>0.34</s:v>
+      </s:c>
+      <s:c r="I86" s="1" t="n">
+        <s:v>92.4</s:v>
+      </s:c>
+      <s:c r="J86" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K86" s="1" t="n">
+        <s:v>751.4</s:v>
+      </s:c>
+      <s:c r="L86" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M86" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N86" s="1" t="n">
+        <s:v>22343.71</s:v>
+      </s:c>
+      <s:c r="O86" s="1" t="n">
+        <s:v>3756.57</s:v>
+      </s:c>
+      <s:c r="P86" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="87" s="1" customFormat="1" spans="1:16">
       <s:c r="A87" s="6" t="n">
@@ -6240,17 +7918,39 @@
       <s:c r="E87" s="1" t="n">
         <s:v>390.48</s:v>
       </s:c>
-      <s:c r="F87" s="1"/>
-      <s:c r="G87" s="1"/>
-      <s:c r="H87" s="1"/>
-      <s:c r="I87" s="1"/>
-      <s:c r="J87" s="1"/>
-      <s:c r="K87" s="1"/>
-      <s:c r="L87" s="1"/>
-      <s:c r="M87" s="1"/>
-      <s:c r="N87" s="1"/>
-      <s:c r="O87" s="1"/>
-      <s:c r="P87" s="1"/>
+      <s:c r="F87" s="1" t="n">
+        <s:v>100</s:v>
+      </s:c>
+      <s:c r="G87" s="1" t="n">
+        <s:v>2120.43</s:v>
+      </s:c>
+      <s:c r="H87" s="1" t="n">
+        <s:v>0.34</s:v>
+      </s:c>
+      <s:c r="I87" s="1" t="n">
+        <s:v>91.5</s:v>
+      </s:c>
+      <s:c r="J87" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K87" s="1" t="n">
+        <s:v>749.5</s:v>
+      </s:c>
+      <s:c r="L87" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M87" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N87" s="1" t="n">
+        <s:v>22248.09</s:v>
+      </s:c>
+      <s:c r="O87" s="1" t="n">
+        <s:v>3734.63</s:v>
+      </s:c>
+      <s:c r="P87" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="88" s="1" customFormat="1" spans="1:16">
       <s:c r="A88" s="6" t="n">
@@ -6268,17 +7968,39 @@
       <s:c r="E88" s="1" t="n">
         <s:v>397.45</s:v>
       </s:c>
-      <s:c r="F88" s="1"/>
-      <s:c r="G88" s="1"/>
-      <s:c r="H88" s="1"/>
-      <s:c r="I88" s="1"/>
-      <s:c r="J88" s="1"/>
-      <s:c r="K88" s="1"/>
-      <s:c r="L88" s="1"/>
-      <s:c r="M88" s="1"/>
-      <s:c r="N88" s="1"/>
-      <s:c r="O88" s="1"/>
-      <s:c r="P88" s="1"/>
+      <s:c r="F88" s="1" t="n">
+        <s:v>100</s:v>
+      </s:c>
+      <s:c r="G88" s="1" t="n">
+        <s:v>2052.69</s:v>
+      </s:c>
+      <s:c r="H88" s="1" t="n">
+        <s:v>0.34</s:v>
+      </s:c>
+      <s:c r="I88" s="1" t="n">
+        <s:v>91.5</s:v>
+      </s:c>
+      <s:c r="J88" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K88" s="1" t="n">
+        <s:v>751.7</s:v>
+      </s:c>
+      <s:c r="L88" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M88" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N88" s="1" t="n">
+        <s:v>22698.33</s:v>
+      </s:c>
+      <s:c r="O88" s="1" t="n">
+        <s:v>3914.74</s:v>
+      </s:c>
+      <s:c r="P88" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="89" s="1" customFormat="1" spans="1:16">
       <s:c r="A89" s="6" t="n">
@@ -6296,17 +8018,39 @@
       <s:c r="E89" s="1" t="n">
         <s:v>407.8</s:v>
       </s:c>
-      <s:c r="F89" s="1"/>
-      <s:c r="G89" s="1"/>
-      <s:c r="H89" s="1"/>
-      <s:c r="I89" s="1"/>
-      <s:c r="J89" s="1"/>
-      <s:c r="K89" s="1"/>
-      <s:c r="L89" s="1"/>
-      <s:c r="M89" s="1"/>
-      <s:c r="N89" s="1"/>
-      <s:c r="O89" s="1"/>
-      <s:c r="P89" s="1"/>
+      <s:c r="F89" s="1" t="n">
+        <s:v>100</s:v>
+      </s:c>
+      <s:c r="G89" s="1" t="n">
+        <s:v>2058.8</s:v>
+      </s:c>
+      <s:c r="H89" s="1" t="n">
+        <s:v>0.34</s:v>
+      </s:c>
+      <s:c r="I89" s="1" t="n">
+        <s:v>91.5</s:v>
+      </s:c>
+      <s:c r="J89" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K89" s="1" t="n">
+        <s:v>750.2</s:v>
+      </s:c>
+      <s:c r="L89" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M89" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N89" s="1" t="n">
+        <s:v>22825.58</s:v>
+      </s:c>
+      <s:c r="O89" s="1" t="n">
+        <s:v>3721.47</s:v>
+      </s:c>
+      <s:c r="P89" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="90" s="1" customFormat="1" spans="1:16">
       <s:c r="A90" s="6" t="n">
@@ -6324,17 +8068,39 @@
       <s:c r="E90" s="1" t="n">
         <s:v>392.92</s:v>
       </s:c>
-      <s:c r="F90" s="1"/>
-      <s:c r="G90" s="1"/>
-      <s:c r="H90" s="1"/>
-      <s:c r="I90" s="1"/>
-      <s:c r="J90" s="1"/>
-      <s:c r="K90" s="1"/>
-      <s:c r="L90" s="1"/>
-      <s:c r="M90" s="1"/>
-      <s:c r="N90" s="1"/>
-      <s:c r="O90" s="1"/>
-      <s:c r="P90" s="1"/>
+      <s:c r="F90" s="1" t="n">
+        <s:v>220</s:v>
+      </s:c>
+      <s:c r="G90" s="1" t="n">
+        <s:v>2012.56</s:v>
+      </s:c>
+      <s:c r="H90" s="1" t="n">
+        <s:v>0.34</s:v>
+      </s:c>
+      <s:c r="I90" s="1" t="n">
+        <s:v>91.5</s:v>
+      </s:c>
+      <s:c r="J90" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K90" s="1" t="n">
+        <s:v>750.2</s:v>
+      </s:c>
+      <s:c r="L90" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M90" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N90" s="1" t="n">
+        <s:v>22627.04</s:v>
+      </s:c>
+      <s:c r="O90" s="1" t="n">
+        <s:v>3911.35</s:v>
+      </s:c>
+      <s:c r="P90" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="91" s="1" customFormat="1" spans="1:16">
       <s:c r="A91" s="6" t="n">
@@ -6352,17 +8118,39 @@
       <s:c r="E91" s="1" t="n">
         <s:v>392.92</s:v>
       </s:c>
-      <s:c r="F91" s="1"/>
-      <s:c r="G91" s="1"/>
-      <s:c r="H91" s="1"/>
-      <s:c r="I91" s="1"/>
-      <s:c r="J91" s="1"/>
-      <s:c r="K91" s="1"/>
-      <s:c r="L91" s="1"/>
-      <s:c r="M91" s="1"/>
-      <s:c r="N91" s="1"/>
-      <s:c r="O91" s="1"/>
-      <s:c r="P91" s="1"/>
+      <s:c r="F91" s="1" t="n">
+        <s:v>320</s:v>
+      </s:c>
+      <s:c r="G91" s="1" t="n">
+        <s:v>2022.92</s:v>
+      </s:c>
+      <s:c r="H91" s="1" t="n">
+        <s:v>0.34</s:v>
+      </s:c>
+      <s:c r="I91" s="1" t="n">
+        <s:v>91.5</s:v>
+      </s:c>
+      <s:c r="J91" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K91" s="1" t="n">
+        <s:v>748.1</s:v>
+      </s:c>
+      <s:c r="L91" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M91" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N91" s="1" t="n">
+        <s:v>22660.94</s:v>
+      </s:c>
+      <s:c r="O91" s="1" t="n">
+        <s:v>3983</s:v>
+      </s:c>
+      <s:c r="P91" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="92" s="1" customFormat="1" spans="1:16">
       <s:c r="A92" s="6" t="n">
@@ -6380,17 +8168,39 @@
       <s:c r="E92" s="1" t="n">
         <s:v>399.42</s:v>
       </s:c>
-      <s:c r="F92" s="1"/>
-      <s:c r="G92" s="1"/>
-      <s:c r="H92" s="1"/>
-      <s:c r="I92" s="1"/>
-      <s:c r="J92" s="1"/>
-      <s:c r="K92" s="1"/>
-      <s:c r="L92" s="1"/>
-      <s:c r="M92" s="1"/>
-      <s:c r="N92" s="1"/>
-      <s:c r="O92" s="1"/>
-      <s:c r="P92" s="1"/>
+      <s:c r="F92" s="1" t="n">
+        <s:v>320</s:v>
+      </s:c>
+      <s:c r="G92" s="1" t="n">
+        <s:v>2033.4</s:v>
+      </s:c>
+      <s:c r="H92" s="1" t="n">
+        <s:v>0.34</s:v>
+      </s:c>
+      <s:c r="I92" s="1" t="n">
+        <s:v>23.5</s:v>
+      </s:c>
+      <s:c r="J92" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K92" s="1" t="n">
+        <s:v>750.7</s:v>
+      </s:c>
+      <s:c r="L92" s="1" t="n">
+        <s:v>800</s:v>
+      </s:c>
+      <s:c r="M92" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N92" s="1" t="n">
+        <s:v>22750.34</s:v>
+      </s:c>
+      <s:c r="O92" s="1" t="n">
+        <s:v>3902.02</s:v>
+      </s:c>
+      <s:c r="P92" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="93" s="1" customFormat="1" spans="1:16">
       <s:c r="A93" s="6" t="n">
@@ -6408,17 +8218,39 @@
       <s:c r="E93" s="1" t="n">
         <s:v>392.92</s:v>
       </s:c>
-      <s:c r="F93" s="1"/>
-      <s:c r="G93" s="1"/>
-      <s:c r="H93" s="1"/>
-      <s:c r="I93" s="1"/>
-      <s:c r="J93" s="1"/>
-      <s:c r="K93" s="1"/>
-      <s:c r="L93" s="1"/>
-      <s:c r="M93" s="1"/>
-      <s:c r="N93" s="1"/>
-      <s:c r="O93" s="1"/>
-      <s:c r="P93" s="1"/>
+      <s:c r="F93" s="1" t="n">
+        <s:v>320</s:v>
+      </s:c>
+      <s:c r="G93" s="1" t="n">
+        <s:v>2096.15</s:v>
+      </s:c>
+      <s:c r="H93" s="1" t="n">
+        <s:v>0.34</s:v>
+      </s:c>
+      <s:c r="I93" s="1" t="n">
+        <s:v>23.5</s:v>
+      </s:c>
+      <s:c r="J93" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K93" s="1" t="n">
+        <s:v>748.6</s:v>
+      </s:c>
+      <s:c r="L93" s="1" t="n">
+        <s:v>681.56</s:v>
+      </s:c>
+      <s:c r="M93" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N93" s="1" t="n">
+        <s:v>22795.38</s:v>
+      </s:c>
+      <s:c r="O93" s="1" t="n">
+        <s:v>3658.46</s:v>
+      </s:c>
+      <s:c r="P93" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="94" s="1" customFormat="1" spans="1:16">
       <s:c r="A94" s="6" t="n">
@@ -6436,17 +8268,39 @@
       <s:c r="E94" s="1" t="n">
         <s:v>410</s:v>
       </s:c>
-      <s:c r="F94" s="1"/>
-      <s:c r="G94" s="1"/>
-      <s:c r="H94" s="1"/>
-      <s:c r="I94" s="1"/>
-      <s:c r="J94" s="1"/>
-      <s:c r="K94" s="1"/>
-      <s:c r="L94" s="1"/>
-      <s:c r="M94" s="1"/>
-      <s:c r="N94" s="1"/>
-      <s:c r="O94" s="1"/>
-      <s:c r="P94" s="1"/>
+      <s:c r="F94" s="1" t="n">
+        <s:v>220</s:v>
+      </s:c>
+      <s:c r="G94" s="1" t="n">
+        <s:v>2083.31</s:v>
+      </s:c>
+      <s:c r="H94" s="1" t="n">
+        <s:v>0.34</s:v>
+      </s:c>
+      <s:c r="I94" s="1" t="n">
+        <s:v>23.5</s:v>
+      </s:c>
+      <s:c r="J94" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K94" s="1" t="n">
+        <s:v>600.1</s:v>
+      </s:c>
+      <s:c r="L94" s="1" t="n">
+        <s:v>772.56</s:v>
+      </s:c>
+      <s:c r="M94" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N94" s="1" t="n">
+        <s:v>23095.24</s:v>
+      </s:c>
+      <s:c r="O94" s="1" t="n">
+        <s:v>3564.74</s:v>
+      </s:c>
+      <s:c r="P94" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="95" s="1" customFormat="1" spans="1:16">
       <s:c r="A95" s="6" t="n">
@@ -6464,17 +8318,39 @@
       <s:c r="E95" s="1" t="n">
         <s:v>392.1</s:v>
       </s:c>
-      <s:c r="F95" s="1"/>
-      <s:c r="G95" s="1"/>
-      <s:c r="H95" s="1"/>
-      <s:c r="I95" s="1"/>
-      <s:c r="J95" s="1"/>
-      <s:c r="K95" s="1"/>
-      <s:c r="L95" s="1"/>
-      <s:c r="M95" s="1"/>
-      <s:c r="N95" s="1"/>
-      <s:c r="O95" s="1"/>
-      <s:c r="P95" s="1"/>
+      <s:c r="F95" s="1" t="n">
+        <s:v>220</s:v>
+      </s:c>
+      <s:c r="G95" s="1" t="n">
+        <s:v>2072.79</s:v>
+      </s:c>
+      <s:c r="H95" s="1" t="n">
+        <s:v>0.34</s:v>
+      </s:c>
+      <s:c r="I95" s="1" t="n">
+        <s:v>15.5</s:v>
+      </s:c>
+      <s:c r="J95" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K95" s="1" t="n">
+        <s:v>449</s:v>
+      </s:c>
+      <s:c r="L95" s="1" t="n">
+        <s:v>711.87</s:v>
+      </s:c>
+      <s:c r="M95" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N95" s="1" t="n">
+        <s:v>22708.15</s:v>
+      </s:c>
+      <s:c r="O95" s="1" t="n">
+        <s:v>3416.65</s:v>
+      </s:c>
+      <s:c r="P95" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="96" s="1" customFormat="1" spans="1:16">
       <s:c r="A96" s="6" t="n">
@@ -6492,17 +8368,39 @@
       <s:c r="E96" s="1" t="n">
         <s:v>397.2</s:v>
       </s:c>
-      <s:c r="F96" s="1"/>
-      <s:c r="G96" s="1"/>
-      <s:c r="H96" s="1"/>
-      <s:c r="I96" s="1"/>
-      <s:c r="J96" s="1"/>
-      <s:c r="K96" s="1"/>
-      <s:c r="L96" s="1"/>
-      <s:c r="M96" s="1"/>
-      <s:c r="N96" s="1"/>
-      <s:c r="O96" s="1"/>
-      <s:c r="P96" s="1"/>
+      <s:c r="F96" s="1" t="n">
+        <s:v>220</s:v>
+      </s:c>
+      <s:c r="G96" s="1" t="n">
+        <s:v>2061.53</s:v>
+      </s:c>
+      <s:c r="H96" s="1" t="n">
+        <s:v>0.34</s:v>
+      </s:c>
+      <s:c r="I96" s="1" t="n">
+        <s:v>14.5</s:v>
+      </s:c>
+      <s:c r="J96" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K96" s="1" t="n">
+        <s:v>449.1</s:v>
+      </s:c>
+      <s:c r="L96" s="1" t="n">
+        <s:v>356.23</s:v>
+      </s:c>
+      <s:c r="M96" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N96" s="1" t="n">
+        <s:v>22942.22</s:v>
+      </s:c>
+      <s:c r="O96" s="1" t="n">
+        <s:v>3206.37</s:v>
+      </s:c>
+      <s:c r="P96" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
     <s:row r="97" s="1" customFormat="1" spans="1:16">
       <s:c r="A97" s="6" t="n">
@@ -6522,17 +8420,39 @@
       <s:c r="E97" s="1" t="n">
         <s:v>422.94</s:v>
       </s:c>
-      <s:c r="F97" s="1"/>
-      <s:c r="G97" s="1"/>
-      <s:c r="H97" s="1"/>
-      <s:c r="I97" s="1"/>
-      <s:c r="J97" s="1"/>
-      <s:c r="K97" s="1"/>
-      <s:c r="L97" s="1"/>
-      <s:c r="M97" s="1"/>
-      <s:c r="N97" s="1"/>
-      <s:c r="O97" s="1"/>
-      <s:c r="P97" s="1"/>
+      <s:c r="F97" s="1" t="n">
+        <s:v>120</s:v>
+      </s:c>
+      <s:c r="G97" s="1" t="n">
+        <s:v>2064.49</s:v>
+      </s:c>
+      <s:c r="H97" s="1" t="n">
+        <s:v>0.34</s:v>
+      </s:c>
+      <s:c r="I97" s="1" t="n">
+        <s:v>3.5</s:v>
+      </s:c>
+      <s:c r="J97" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="K97" s="1" t="n">
+        <s:v>150.9</s:v>
+      </s:c>
+      <s:c r="L97" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="M97" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="N97" s="1" t="n">
+        <s:v>23336.21</s:v>
+      </s:c>
+      <s:c r="O97" s="1" t="n">
+        <s:v>3231.56</s:v>
+      </s:c>
+      <s:c r="P97" s="1" t="n">
+        <s:v>91</s:v>
+      </s:c>
     </s:row>
   </s:sheetData>
   <conditionalFormatting sqref="A1:B1">

--- a/review-results/河北实时运行及市场出清数据-20260731.xlsx
+++ b/review-results/河北实时运行及市场出清数据-20260731.xlsx
@@ -1386,12 +1386,18 @@
       <s:c r="C2" s="11" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D2" s="12"/>
-      <s:c r="E2" s="13"/>
+      <s:c r="D2" s="12" t="n">
+        <s:v>36793</s:v>
+      </s:c>
+      <s:c r="E2" s="13" t="n">
+        <s:v>13206.17</s:v>
+      </s:c>
       <s:c r="F2" s="14" t="n">
         <s:v>4222</s:v>
       </s:c>
-      <s:c r="G2" s="15"/>
+      <s:c r="G2" s="15" t="n">
+        <s:v>5966.02</s:v>
+      </s:c>
       <s:c r="J2"/>
       <s:c r="K2"/>
       <s:c r="L2"/>
@@ -1408,12 +1414,18 @@
       <s:c r="C3" s="11" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D3" s="12"/>
-      <s:c r="E3" s="13"/>
+      <s:c r="D3" s="12" t="n">
+        <s:v>36626.9</s:v>
+      </s:c>
+      <s:c r="E3" s="13" t="n">
+        <s:v>12927.37</s:v>
+      </s:c>
       <s:c r="F3" s="14" t="n">
         <s:v>4278.5</s:v>
       </s:c>
-      <s:c r="G3" s="15"/>
+      <s:c r="G3" s="15" t="n">
+        <s:v>6290</s:v>
+      </s:c>
       <s:c r="J3"/>
       <s:c r="K3"/>
       <s:c r="L3"/>
@@ -1430,12 +1442,18 @@
       <s:c r="C4" s="11" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D4" s="12"/>
-      <s:c r="E4" s="13"/>
+      <s:c r="D4" s="12" t="n">
+        <s:v>36190.4</s:v>
+      </s:c>
+      <s:c r="E4" s="13" t="n">
+        <s:v>12341.39</s:v>
+      </s:c>
       <s:c r="F4" s="14" t="n">
         <s:v>4277.1</s:v>
       </s:c>
-      <s:c r="G4" s="15"/>
+      <s:c r="G4" s="15" t="n">
+        <s:v>6327.64</s:v>
+      </s:c>
       <s:c r="J4"/>
       <s:c r="K4"/>
       <s:c r="L4"/>
@@ -1452,12 +1470,18 @@
       <s:c r="C5" s="11" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D5" s="12"/>
-      <s:c r="E5" s="13"/>
+      <s:c r="D5" s="12" t="n">
+        <s:v>36002.4</s:v>
+      </s:c>
+      <s:c r="E5" s="13" t="n">
+        <s:v>11993.55</s:v>
+      </s:c>
       <s:c r="F5" s="14" t="n">
         <s:v>4167.7</s:v>
       </s:c>
-      <s:c r="G5" s="15"/>
+      <s:c r="G5" s="15" t="n">
+        <s:v>6274.15</s:v>
+      </s:c>
       <s:c r="J5"/>
       <s:c r="K5"/>
       <s:c r="L5"/>
@@ -1474,12 +1498,18 @@
       <s:c r="C6" s="11" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D6" s="12"/>
-      <s:c r="E6" s="13"/>
+      <s:c r="D6" s="12" t="n">
+        <s:v>38137.3</s:v>
+      </s:c>
+      <s:c r="E6" s="13" t="n">
+        <s:v>12394.62</s:v>
+      </s:c>
       <s:c r="F6" s="14" t="n">
         <s:v>4140.3</s:v>
       </s:c>
-      <s:c r="G6" s="15"/>
+      <s:c r="G6" s="15" t="n">
+        <s:v>6943.91</s:v>
+      </s:c>
       <s:c r="J6"/>
       <s:c r="K6"/>
       <s:c r="L6"/>
@@ -1496,12 +1526,18 @@
       <s:c r="C7" s="11" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D7" s="12"/>
-      <s:c r="E7" s="13"/>
+      <s:c r="D7" s="12" t="n">
+        <s:v>38079.1</s:v>
+      </s:c>
+      <s:c r="E7" s="13" t="n">
+        <s:v>12393.75</s:v>
+      </s:c>
       <s:c r="F7" s="14" t="n">
         <s:v>4073.7</s:v>
       </s:c>
-      <s:c r="G7" s="15"/>
+      <s:c r="G7" s="15" t="n">
+        <s:v>6853.01</s:v>
+      </s:c>
       <s:c r="J7"/>
       <s:c r="K7"/>
       <s:c r="L7"/>
@@ -1518,12 +1554,18 @@
       <s:c r="C8" s="11" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D8" s="12"/>
-      <s:c r="E8" s="13"/>
+      <s:c r="D8" s="12" t="n">
+        <s:v>37123</s:v>
+      </s:c>
+      <s:c r="E8" s="13" t="n">
+        <s:v>12422.29</s:v>
+      </s:c>
       <s:c r="F8" s="14" t="n">
         <s:v>4022.1</s:v>
       </s:c>
-      <s:c r="G8" s="15"/>
+      <s:c r="G8" s="15" t="n">
+        <s:v>6152.18</s:v>
+      </s:c>
       <s:c r="J8"/>
       <s:c r="K8"/>
       <s:c r="L8"/>
@@ -1540,12 +1582,18 @@
       <s:c r="C9" s="11" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D9" s="12"/>
-      <s:c r="E9" s="13"/>
+      <s:c r="D9" s="12" t="n">
+        <s:v>36356.2</s:v>
+      </s:c>
+      <s:c r="E9" s="13" t="n">
+        <s:v>12048.32</s:v>
+      </s:c>
       <s:c r="F9" s="14" t="n">
         <s:v>4005</s:v>
       </s:c>
-      <s:c r="G9" s="15"/>
+      <s:c r="G9" s="15" t="n">
+        <s:v>6430.28</s:v>
+      </s:c>
       <s:c r="J9"/>
       <s:c r="K9"/>
       <s:c r="L9"/>
@@ -1562,12 +1610,18 @@
       <s:c r="C10" s="11" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D10" s="12"/>
-      <s:c r="E10" s="13"/>
+      <s:c r="D10" s="12" t="n">
+        <s:v>35759</s:v>
+      </s:c>
+      <s:c r="E10" s="13" t="n">
+        <s:v>11914.26</s:v>
+      </s:c>
       <s:c r="F10" s="14" t="n">
         <s:v>3947.3</s:v>
       </s:c>
-      <s:c r="G10" s="15"/>
+      <s:c r="G10" s="15" t="n">
+        <s:v>6195.17</s:v>
+      </s:c>
       <s:c r="J10"/>
       <s:c r="K10"/>
       <s:c r="L10"/>
@@ -1584,12 +1638,18 @@
       <s:c r="C11" s="11" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D11" s="12"/>
-      <s:c r="E11" s="13"/>
+      <s:c r="D11" s="12" t="n">
+        <s:v>35204.4</s:v>
+      </s:c>
+      <s:c r="E11" s="13" t="n">
+        <s:v>11750.01</s:v>
+      </s:c>
       <s:c r="F11" s="14" t="n">
         <s:v>3919.9</s:v>
       </s:c>
-      <s:c r="G11" s="15"/>
+      <s:c r="G11" s="15" t="n">
+        <s:v>6067.49</s:v>
+      </s:c>
       <s:c r="J11"/>
       <s:c r="K11"/>
       <s:c r="L11"/>
@@ -1606,12 +1666,18 @@
       <s:c r="C12" s="11" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D12" s="12"/>
-      <s:c r="E12" s="13"/>
+      <s:c r="D12" s="12" t="n">
+        <s:v>34641.6</s:v>
+      </s:c>
+      <s:c r="E12" s="13" t="n">
+        <s:v>11589.43</s:v>
+      </s:c>
       <s:c r="F12" s="14" t="n">
         <s:v>3911.1</s:v>
       </s:c>
-      <s:c r="G12" s="15"/>
+      <s:c r="G12" s="15" t="n">
+        <s:v>6388.89</s:v>
+      </s:c>
       <s:c r="J12"/>
       <s:c r="K12"/>
       <s:c r="L12"/>
@@ -1628,12 +1694,18 @@
       <s:c r="C13" s="11" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D13" s="12"/>
-      <s:c r="E13" s="13"/>
+      <s:c r="D13" s="12" t="n">
+        <s:v>34419.4</s:v>
+      </s:c>
+      <s:c r="E13" s="13" t="n">
+        <s:v>11071.07</s:v>
+      </s:c>
       <s:c r="F13" s="14" t="n">
         <s:v>3874.8</s:v>
       </s:c>
-      <s:c r="G13" s="15"/>
+      <s:c r="G13" s="15" t="n">
+        <s:v>6131.2</s:v>
+      </s:c>
       <s:c r="J13"/>
       <s:c r="K13"/>
       <s:c r="L13"/>
@@ -1650,12 +1722,18 @@
       <s:c r="C14" s="11" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D14" s="12"/>
-      <s:c r="E14" s="13"/>
+      <s:c r="D14" s="12" t="n">
+        <s:v>34022</s:v>
+      </s:c>
+      <s:c r="E14" s="13" t="n">
+        <s:v>10702.1</s:v>
+      </s:c>
       <s:c r="F14" s="14" t="n">
         <s:v>3692.9</s:v>
       </s:c>
-      <s:c r="G14" s="15"/>
+      <s:c r="G14" s="15" t="n">
+        <s:v>6223.6</s:v>
+      </s:c>
       <s:c r="J14"/>
       <s:c r="K14"/>
       <s:c r="L14"/>
@@ -1672,12 +1750,18 @@
       <s:c r="C15" s="11" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D15" s="12"/>
-      <s:c r="E15" s="13"/>
+      <s:c r="D15" s="12" t="n">
+        <s:v>33691.5</s:v>
+      </s:c>
+      <s:c r="E15" s="13" t="n">
+        <s:v>10486.02</s:v>
+      </s:c>
       <s:c r="F15" s="14" t="n">
         <s:v>3628.4</s:v>
       </s:c>
-      <s:c r="G15" s="15"/>
+      <s:c r="G15" s="15" t="n">
+        <s:v>6169.01</s:v>
+      </s:c>
       <s:c r="J15"/>
       <s:c r="K15"/>
       <s:c r="L15"/>
@@ -1694,12 +1778,18 @@
       <s:c r="C16" s="11" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D16" s="12"/>
-      <s:c r="E16" s="13"/>
+      <s:c r="D16" s="12" t="n">
+        <s:v>33432.9</s:v>
+      </s:c>
+      <s:c r="E16" s="13" t="n">
+        <s:v>10270.68</s:v>
+      </s:c>
       <s:c r="F16" s="14" t="n">
         <s:v>3548.1</s:v>
       </s:c>
-      <s:c r="G16" s="15"/>
+      <s:c r="G16" s="15" t="n">
+        <s:v>6152.05</s:v>
+      </s:c>
       <s:c r="J16"/>
       <s:c r="K16"/>
       <s:c r="L16"/>
@@ -1716,12 +1806,18 @@
       <s:c r="C17" s="11" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D17" s="12"/>
-      <s:c r="E17" s="13"/>
+      <s:c r="D17" s="12" t="n">
+        <s:v>32847.3</s:v>
+      </s:c>
+      <s:c r="E17" s="13" t="n">
+        <s:v>10257.06</s:v>
+      </s:c>
       <s:c r="F17" s="14" t="n">
         <s:v>3413.8</s:v>
       </s:c>
-      <s:c r="G17" s="15"/>
+      <s:c r="G17" s="15" t="n">
+        <s:v>5894.12</s:v>
+      </s:c>
       <s:c r="J17"/>
       <s:c r="K17"/>
       <s:c r="L17"/>
@@ -1738,12 +1834,18 @@
       <s:c r="C18" s="11" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D18" s="12"/>
-      <s:c r="E18" s="13"/>
+      <s:c r="D18" s="12" t="n">
+        <s:v>32872.2</s:v>
+      </s:c>
+      <s:c r="E18" s="13" t="n">
+        <s:v>10197.61</s:v>
+      </s:c>
       <s:c r="F18" s="14" t="n">
         <s:v>3248.8</s:v>
       </s:c>
-      <s:c r="G18" s="15"/>
+      <s:c r="G18" s="15" t="n">
+        <s:v>6076.5</s:v>
+      </s:c>
       <s:c r="J18"/>
       <s:c r="K18"/>
       <s:c r="L18"/>
@@ -1760,12 +1862,18 @@
       <s:c r="C19" s="11" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D19" s="12"/>
-      <s:c r="E19" s="13"/>
+      <s:c r="D19" s="12" t="n">
+        <s:v>32660.9</s:v>
+      </s:c>
+      <s:c r="E19" s="13" t="n">
+        <s:v>10187.89</s:v>
+      </s:c>
       <s:c r="F19" s="14" t="n">
         <s:v>3064.6</s:v>
       </s:c>
-      <s:c r="G19" s="15"/>
+      <s:c r="G19" s="15" t="n">
+        <s:v>6250.65</s:v>
+      </s:c>
       <s:c r="J19"/>
       <s:c r="K19"/>
       <s:c r="L19"/>
@@ -1782,12 +1890,18 @@
       <s:c r="C20" s="11" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D20" s="12"/>
-      <s:c r="E20" s="13"/>
+      <s:c r="D20" s="12" t="n">
+        <s:v>32377.4</s:v>
+      </s:c>
+      <s:c r="E20" s="13" t="n">
+        <s:v>10027.42</s:v>
+      </s:c>
       <s:c r="F20" s="14" t="n">
         <s:v>2932.6</s:v>
       </s:c>
-      <s:c r="G20" s="15"/>
+      <s:c r="G20" s="15" t="n">
+        <s:v>5963.3</s:v>
+      </s:c>
       <s:c r="J20"/>
       <s:c r="K20"/>
       <s:c r="L20"/>
@@ -1804,12 +1918,18 @@
       <s:c r="C21" s="11" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D21" s="12"/>
-      <s:c r="E21" s="13"/>
+      <s:c r="D21" s="12" t="n">
+        <s:v>32435.1</s:v>
+      </s:c>
+      <s:c r="E21" s="13" t="n">
+        <s:v>9868.1</s:v>
+      </s:c>
       <s:c r="F21" s="14" t="n">
         <s:v>2910.1</s:v>
       </s:c>
-      <s:c r="G21" s="15"/>
+      <s:c r="G21" s="15" t="n">
+        <s:v>5911.71</s:v>
+      </s:c>
       <s:c r="J21"/>
       <s:c r="K21"/>
       <s:c r="L21"/>
@@ -1826,12 +1946,18 @@
       <s:c r="C22" s="11" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D22" s="12"/>
-      <s:c r="E22" s="13"/>
+      <s:c r="D22" s="12" t="n">
+        <s:v>32558.2</s:v>
+      </s:c>
+      <s:c r="E22" s="13" t="n">
+        <s:v>9859.22</s:v>
+      </s:c>
       <s:c r="F22" s="14" t="n">
         <s:v>2846.6</s:v>
       </s:c>
-      <s:c r="G22" s="15"/>
+      <s:c r="G22" s="15" t="n">
+        <s:v>5967.08</s:v>
+      </s:c>
       <s:c r="J22"/>
       <s:c r="K22"/>
       <s:c r="L22"/>
@@ -1848,12 +1974,18 @@
       <s:c r="C23" s="11" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D23" s="12"/>
-      <s:c r="E23" s="13"/>
+      <s:c r="D23" s="12" t="n">
+        <s:v>32874.9</s:v>
+      </s:c>
+      <s:c r="E23" s="13" t="n">
+        <s:v>9854.78</s:v>
+      </s:c>
       <s:c r="F23" s="14" t="n">
         <s:v>2836.7</s:v>
       </s:c>
-      <s:c r="G23" s="15"/>
+      <s:c r="G23" s="15" t="n">
+        <s:v>6192.63</s:v>
+      </s:c>
       <s:c r="J23"/>
       <s:c r="K23"/>
       <s:c r="L23"/>
@@ -1870,12 +2002,18 @@
       <s:c r="C24" s="11" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D24" s="12"/>
-      <s:c r="E24" s="13"/>
+      <s:c r="D24" s="12" t="n">
+        <s:v>33033.1</s:v>
+      </s:c>
+      <s:c r="E24" s="13" t="n">
+        <s:v>9853.76</s:v>
+      </s:c>
       <s:c r="F24" s="14" t="n">
         <s:v>2930.2</s:v>
       </s:c>
-      <s:c r="G24" s="15"/>
+      <s:c r="G24" s="15" t="n">
+        <s:v>6024.89</s:v>
+      </s:c>
       <s:c r="J24"/>
       <s:c r="K24"/>
       <s:c r="L24"/>
@@ -1892,12 +2030,18 @@
       <s:c r="C25" s="11" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D25" s="12"/>
-      <s:c r="E25" s="13"/>
+      <s:c r="D25" s="12" t="n">
+        <s:v>33214.6</s:v>
+      </s:c>
+      <s:c r="E25" s="13" t="n">
+        <s:v>9853.54</s:v>
+      </s:c>
       <s:c r="F25" s="14" t="n">
         <s:v>3186</s:v>
       </s:c>
-      <s:c r="G25" s="15"/>
+      <s:c r="G25" s="15" t="n">
+        <s:v>5891.91</s:v>
+      </s:c>
       <s:c r="J25"/>
       <s:c r="K25"/>
       <s:c r="L25"/>
@@ -1914,12 +2058,18 @@
       <s:c r="C26" s="11" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D26" s="12"/>
-      <s:c r="E26" s="13"/>
+      <s:c r="D26" s="12" t="n">
+        <s:v>33393.7</s:v>
+      </s:c>
+      <s:c r="E26" s="13" t="n">
+        <s:v>9749.11</s:v>
+      </s:c>
       <s:c r="F26" s="14" t="n">
         <s:v>3416.1</s:v>
       </s:c>
-      <s:c r="G26" s="15"/>
+      <s:c r="G26" s="15" t="n">
+        <s:v>5542.05</s:v>
+      </s:c>
       <s:c r="J26"/>
       <s:c r="K26"/>
       <s:c r="L26"/>
@@ -1936,12 +2086,18 @@
       <s:c r="C27" s="11" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D27" s="12"/>
-      <s:c r="E27" s="13"/>
+      <s:c r="D27" s="12" t="n">
+        <s:v>33221</s:v>
+      </s:c>
+      <s:c r="E27" s="13" t="n">
+        <s:v>9759.69</s:v>
+      </s:c>
       <s:c r="F27" s="14" t="n">
         <s:v>3680</s:v>
       </s:c>
-      <s:c r="G27" s="15"/>
+      <s:c r="G27" s="15" t="n">
+        <s:v>5155.54</s:v>
+      </s:c>
       <s:c r="J27"/>
       <s:c r="K27"/>
       <s:c r="L27"/>
@@ -1958,12 +2114,18 @@
       <s:c r="C28" s="11" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D28" s="12"/>
-      <s:c r="E28" s="13"/>
+      <s:c r="D28" s="12" t="n">
+        <s:v>33231</s:v>
+      </s:c>
+      <s:c r="E28" s="13" t="n">
+        <s:v>9707.67</s:v>
+      </s:c>
       <s:c r="F28" s="14" t="n">
         <s:v>3866.8</s:v>
       </s:c>
-      <s:c r="G28" s="15"/>
+      <s:c r="G28" s="15" t="n">
+        <s:v>4910.43</s:v>
+      </s:c>
       <s:c r="J28"/>
       <s:c r="K28"/>
       <s:c r="L28"/>
@@ -1980,12 +2142,18 @@
       <s:c r="C29" s="11" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D29" s="12"/>
-      <s:c r="E29" s="13"/>
+      <s:c r="D29" s="12" t="n">
+        <s:v>32770.9</s:v>
+      </s:c>
+      <s:c r="E29" s="13" t="n">
+        <s:v>9426.27</s:v>
+      </s:c>
       <s:c r="F29" s="14" t="n">
         <s:v>3780.5</s:v>
       </s:c>
-      <s:c r="G29" s="15"/>
+      <s:c r="G29" s="15" t="n">
+        <s:v>4358.68</s:v>
+      </s:c>
       <s:c r="J29"/>
       <s:c r="K29"/>
       <s:c r="L29"/>
@@ -2002,12 +2170,18 @@
       <s:c r="C30" s="11" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D30" s="12"/>
-      <s:c r="E30" s="13"/>
+      <s:c r="D30" s="12" t="n">
+        <s:v>33181.7</s:v>
+      </s:c>
+      <s:c r="E30" s="13" t="n">
+        <s:v>9046.66</s:v>
+      </s:c>
       <s:c r="F30" s="14" t="n">
         <s:v>3877.6</s:v>
       </s:c>
-      <s:c r="G30" s="15"/>
+      <s:c r="G30" s="15" t="n">
+        <s:v>4630.1</s:v>
+      </s:c>
       <s:c r="J30"/>
       <s:c r="K30"/>
       <s:c r="L30"/>
@@ -2024,12 +2198,18 @@
       <s:c r="C31" s="11" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D31" s="12"/>
-      <s:c r="E31" s="13"/>
+      <s:c r="D31" s="12" t="n">
+        <s:v>33395.8</s:v>
+      </s:c>
+      <s:c r="E31" s="13" t="n">
+        <s:v>8221.61</s:v>
+      </s:c>
       <s:c r="F31" s="14" t="n">
         <s:v>3842.6</s:v>
       </s:c>
-      <s:c r="G31" s="15"/>
+      <s:c r="G31" s="15" t="n">
+        <s:v>4909.53</s:v>
+      </s:c>
       <s:c r="J31"/>
       <s:c r="K31"/>
       <s:c r="L31"/>
@@ -2046,12 +2226,18 @@
       <s:c r="C32" s="11" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D32" s="12"/>
-      <s:c r="E32" s="13"/>
+      <s:c r="D32" s="12" t="n">
+        <s:v>33995.2</s:v>
+      </s:c>
+      <s:c r="E32" s="13" t="n">
+        <s:v>7212.26</s:v>
+      </s:c>
       <s:c r="F32" s="14" t="n">
         <s:v>3983.6</s:v>
       </s:c>
-      <s:c r="G32" s="15"/>
+      <s:c r="G32" s="15" t="n">
+        <s:v>5621.49</s:v>
+      </s:c>
       <s:c r="J32"/>
       <s:c r="K32"/>
       <s:c r="L32"/>
@@ -2068,12 +2254,18 @@
       <s:c r="C33" s="11" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D33" s="12"/>
-      <s:c r="E33" s="13"/>
+      <s:c r="D33" s="12" t="n">
+        <s:v>34783.2</s:v>
+      </s:c>
+      <s:c r="E33" s="13" t="n">
+        <s:v>6240.01</s:v>
+      </s:c>
       <s:c r="F33" s="14" t="n">
         <s:v>4427.6</s:v>
       </s:c>
-      <s:c r="G33" s="15"/>
+      <s:c r="G33" s="15" t="n">
+        <s:v>6719.95</s:v>
+      </s:c>
       <s:c r="J33"/>
       <s:c r="K33"/>
       <s:c r="L33"/>
@@ -2090,12 +2282,18 @@
       <s:c r="C34" s="11" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D34" s="12"/>
-      <s:c r="E34" s="13"/>
+      <s:c r="D34" s="12" t="n">
+        <s:v>36303.4</s:v>
+      </s:c>
+      <s:c r="E34" s="13" t="n">
+        <s:v>6191.15</s:v>
+      </s:c>
       <s:c r="F34" s="14" t="n">
         <s:v>4814.5</s:v>
       </s:c>
-      <s:c r="G34" s="15"/>
+      <s:c r="G34" s="15" t="n">
+        <s:v>6955.79</s:v>
+      </s:c>
       <s:c r="J34"/>
       <s:c r="K34"/>
       <s:c r="L34"/>
@@ -2112,12 +2310,18 @@
       <s:c r="C35" s="11" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D35" s="12"/>
-      <s:c r="E35" s="13"/>
+      <s:c r="D35" s="12" t="n">
+        <s:v>36893.3</s:v>
+      </s:c>
+      <s:c r="E35" s="13" t="n">
+        <s:v>6092.47</s:v>
+      </s:c>
       <s:c r="F35" s="14" t="n">
         <s:v>5160.6</s:v>
       </s:c>
-      <s:c r="G35" s="15"/>
+      <s:c r="G35" s="15" t="n">
+        <s:v>7489.12</s:v>
+      </s:c>
       <s:c r="J35"/>
       <s:c r="K35"/>
       <s:c r="L35"/>
@@ -2134,12 +2338,18 @@
       <s:c r="C36" s="11" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D36" s="12"/>
-      <s:c r="E36" s="13"/>
+      <s:c r="D36" s="12" t="n">
+        <s:v>37343.6</s:v>
+      </s:c>
+      <s:c r="E36" s="13" t="n">
+        <s:v>5787.65</s:v>
+      </s:c>
       <s:c r="F36" s="14" t="n">
         <s:v>5274.2</s:v>
       </s:c>
-      <s:c r="G36" s="15"/>
+      <s:c r="G36" s="15" t="n">
+        <s:v>7833.91</s:v>
+      </s:c>
       <s:c r="J36"/>
       <s:c r="K36"/>
       <s:c r="L36"/>
@@ -2156,12 +2366,18 @@
       <s:c r="C37" s="11" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D37" s="12"/>
-      <s:c r="E37" s="13"/>
+      <s:c r="D37" s="12" t="n">
+        <s:v>37617.3</s:v>
+      </s:c>
+      <s:c r="E37" s="13" t="n">
+        <s:v>5511.85</s:v>
+      </s:c>
       <s:c r="F37" s="14" t="n">
         <s:v>5208</s:v>
       </s:c>
-      <s:c r="G37" s="15"/>
+      <s:c r="G37" s="15" t="n">
+        <s:v>9152.81</s:v>
+      </s:c>
       <s:c r="J37"/>
       <s:c r="K37"/>
       <s:c r="L37"/>
@@ -2178,12 +2394,18 @@
       <s:c r="C38" s="11" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D38" s="12"/>
-      <s:c r="E38" s="13"/>
+      <s:c r="D38" s="12" t="n">
+        <s:v>38419.7</s:v>
+      </s:c>
+      <s:c r="E38" s="13" t="n">
+        <s:v>5540.31</s:v>
+      </s:c>
       <s:c r="F38" s="14" t="n">
         <s:v>5621.7</s:v>
       </s:c>
-      <s:c r="G38" s="15"/>
+      <s:c r="G38" s="15" t="n">
+        <s:v>9225.33</s:v>
+      </s:c>
       <s:c r="J38"/>
       <s:c r="K38"/>
       <s:c r="L38"/>
@@ -2200,12 +2422,18 @@
       <s:c r="C39" s="11" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D39" s="12"/>
-      <s:c r="E39" s="13"/>
+      <s:c r="D39" s="12" t="n">
+        <s:v>38389</s:v>
+      </s:c>
+      <s:c r="E39" s="13" t="n">
+        <s:v>5580.73</s:v>
+      </s:c>
       <s:c r="F39" s="14" t="n">
         <s:v>5961.4</s:v>
       </s:c>
-      <s:c r="G39" s="15"/>
+      <s:c r="G39" s="15" t="n">
+        <s:v>8831.05</s:v>
+      </s:c>
       <s:c r="J39"/>
       <s:c r="K39"/>
       <s:c r="L39"/>
@@ -2222,12 +2450,18 @@
       <s:c r="C40" s="11" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D40" s="12"/>
-      <s:c r="E40" s="13"/>
+      <s:c r="D40" s="12" t="n">
+        <s:v>38408.3</s:v>
+      </s:c>
+      <s:c r="E40" s="13" t="n">
+        <s:v>5615.15</s:v>
+      </s:c>
       <s:c r="F40" s="14" t="n">
         <s:v>6409.4</s:v>
       </s:c>
-      <s:c r="G40" s="15"/>
+      <s:c r="G40" s="15" t="n">
+        <s:v>9165.93</s:v>
+      </s:c>
       <s:c r="J40"/>
       <s:c r="K40"/>
       <s:c r="L40"/>
@@ -2244,12 +2478,18 @@
       <s:c r="C41" s="11" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D41" s="12"/>
-      <s:c r="E41" s="13"/>
+      <s:c r="D41" s="12" t="n">
+        <s:v>38611.1</s:v>
+      </s:c>
+      <s:c r="E41" s="13" t="n">
+        <s:v>5635.66</s:v>
+      </s:c>
       <s:c r="F41" s="14" t="n">
         <s:v>6975</s:v>
       </s:c>
-      <s:c r="G41" s="15"/>
+      <s:c r="G41" s="15" t="n">
+        <s:v>9181.17</s:v>
+      </s:c>
       <s:c r="J41"/>
       <s:c r="K41"/>
       <s:c r="L41"/>
@@ -2266,12 +2506,18 @@
       <s:c r="C42" s="11" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D42" s="12"/>
-      <s:c r="E42" s="13"/>
+      <s:c r="D42" s="12" t="n">
+        <s:v>38539.9</s:v>
+      </s:c>
+      <s:c r="E42" s="13" t="n">
+        <s:v>5661.12</s:v>
+      </s:c>
       <s:c r="F42" s="14" t="n">
         <s:v>7256.9</s:v>
       </s:c>
-      <s:c r="G42" s="15"/>
+      <s:c r="G42" s="15" t="n">
+        <s:v>9313.31</s:v>
+      </s:c>
       <s:c r="J42"/>
       <s:c r="K42"/>
       <s:c r="L42"/>
@@ -2288,12 +2534,18 @@
       <s:c r="C43" s="11" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D43" s="12"/>
-      <s:c r="E43" s="13"/>
+      <s:c r="D43" s="12" t="n">
+        <s:v>38439.3</s:v>
+      </s:c>
+      <s:c r="E43" s="13" t="n">
+        <s:v>5672.36</s:v>
+      </s:c>
       <s:c r="F43" s="14" t="n">
         <s:v>7572.6</s:v>
       </s:c>
-      <s:c r="G43" s="15"/>
+      <s:c r="G43" s="15" t="n">
+        <s:v>9165.76</s:v>
+      </s:c>
       <s:c r="J43"/>
       <s:c r="K43"/>
       <s:c r="L43"/>
@@ -2310,12 +2562,18 @@
       <s:c r="C44" s="11" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D44" s="12"/>
-      <s:c r="E44" s="13"/>
+      <s:c r="D44" s="12" t="n">
+        <s:v>38647.6</s:v>
+      </s:c>
+      <s:c r="E44" s="13" t="n">
+        <s:v>5684.46</s:v>
+      </s:c>
       <s:c r="F44" s="14" t="n">
         <s:v>7840.6</s:v>
       </s:c>
-      <s:c r="G44" s="15"/>
+      <s:c r="G44" s="15" t="n">
+        <s:v>9237.29</s:v>
+      </s:c>
       <s:c r="J44"/>
       <s:c r="K44"/>
       <s:c r="L44"/>
@@ -2332,12 +2590,18 @@
       <s:c r="C45" s="11" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D45" s="12"/>
-      <s:c r="E45" s="13"/>
+      <s:c r="D45" s="12" t="n">
+        <s:v>38774.9</s:v>
+      </s:c>
+      <s:c r="E45" s="13" t="n">
+        <s:v>5694.57</s:v>
+      </s:c>
       <s:c r="F45" s="14" t="n">
         <s:v>8284.3</s:v>
       </s:c>
-      <s:c r="G45" s="15"/>
+      <s:c r="G45" s="15" t="n">
+        <s:v>9091.86</s:v>
+      </s:c>
       <s:c r="J45"/>
       <s:c r="K45"/>
       <s:c r="L45"/>
@@ -2354,12 +2618,18 @@
       <s:c r="C46" s="11" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D46" s="12"/>
-      <s:c r="E46" s="13"/>
+      <s:c r="D46" s="12" t="n">
+        <s:v>39211.8</s:v>
+      </s:c>
+      <s:c r="E46" s="13" t="n">
+        <s:v>5698.51</s:v>
+      </s:c>
       <s:c r="F46" s="14" t="n">
         <s:v>8294.4</s:v>
       </s:c>
-      <s:c r="G46" s="15"/>
+      <s:c r="G46" s="15" t="n">
+        <s:v>9231.24</s:v>
+      </s:c>
       <s:c r="J46"/>
       <s:c r="K46"/>
       <s:c r="L46"/>
@@ -2376,12 +2646,18 @@
       <s:c r="C47" s="11" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D47" s="12"/>
-      <s:c r="E47" s="13"/>
+      <s:c r="D47" s="12" t="n">
+        <s:v>39005.7</s:v>
+      </s:c>
+      <s:c r="E47" s="13" t="n">
+        <s:v>5720.6</s:v>
+      </s:c>
       <s:c r="F47" s="14" t="n">
         <s:v>8614.2</s:v>
       </s:c>
-      <s:c r="G47" s="15"/>
+      <s:c r="G47" s="15" t="n">
+        <s:v>8387.81</s:v>
+      </s:c>
       <s:c r="J47"/>
       <s:c r="K47"/>
       <s:c r="L47"/>
@@ -2398,12 +2674,18 @@
       <s:c r="C48" s="11" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D48" s="12"/>
-      <s:c r="E48" s="13"/>
+      <s:c r="D48" s="12" t="n">
+        <s:v>38422.3</s:v>
+      </s:c>
+      <s:c r="E48" s="13" t="n">
+        <s:v>5722.46</s:v>
+      </s:c>
       <s:c r="F48" s="14" t="n">
         <s:v>9096.1</s:v>
       </s:c>
-      <s:c r="G48" s="15"/>
+      <s:c r="G48" s="15" t="n">
+        <s:v>7908.52</s:v>
+      </s:c>
       <s:c r="J48"/>
       <s:c r="K48"/>
       <s:c r="L48"/>
@@ -2420,12 +2702,18 @@
       <s:c r="C49" s="11" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D49" s="12"/>
-      <s:c r="E49" s="13"/>
+      <s:c r="D49" s="12" t="n">
+        <s:v>37952.9</s:v>
+      </s:c>
+      <s:c r="E49" s="13" t="n">
+        <s:v>5728.74</s:v>
+      </s:c>
       <s:c r="F49" s="14" t="n">
         <s:v>9394</s:v>
       </s:c>
-      <s:c r="G49" s="15"/>
+      <s:c r="G49" s="15" t="n">
+        <s:v>7374.35</s:v>
+      </s:c>
       <s:c r="J49"/>
       <s:c r="K49"/>
       <s:c r="L49"/>
@@ -2442,12 +2730,18 @@
       <s:c r="C50" s="11" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D50" s="12"/>
-      <s:c r="E50" s="13"/>
+      <s:c r="D50" s="12" t="n">
+        <s:v>39617.2</s:v>
+      </s:c>
+      <s:c r="E50" s="13" t="n">
+        <s:v>6348.17</s:v>
+      </s:c>
       <s:c r="F50" s="14" t="n">
         <s:v>9552.8</s:v>
       </s:c>
-      <s:c r="G50" s="15"/>
+      <s:c r="G50" s="15" t="n">
+        <s:v>6907.48</s:v>
+      </s:c>
       <s:c r="J50"/>
       <s:c r="K50"/>
       <s:c r="L50"/>
@@ -2464,12 +2758,18 @@
       <s:c r="C51" s="11" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D51" s="12"/>
-      <s:c r="E51" s="13"/>
+      <s:c r="D51" s="12" t="n">
+        <s:v>40042</s:v>
+      </s:c>
+      <s:c r="E51" s="13" t="n">
+        <s:v>7048.51</s:v>
+      </s:c>
       <s:c r="F51" s="14" t="n">
         <s:v>9600.4</s:v>
       </s:c>
-      <s:c r="G51" s="15"/>
+      <s:c r="G51" s="15" t="n">
+        <s:v>6983</s:v>
+      </s:c>
       <s:c r="J51"/>
       <s:c r="K51"/>
       <s:c r="L51"/>
@@ -2486,12 +2786,18 @@
       <s:c r="C52" s="11" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D52" s="12"/>
-      <s:c r="E52" s="13"/>
+      <s:c r="D52" s="12" t="n">
+        <s:v>39521.4</s:v>
+      </s:c>
+      <s:c r="E52" s="13" t="n">
+        <s:v>7771.7</s:v>
+      </s:c>
       <s:c r="F52" s="14" t="n">
         <s:v>9459.4</s:v>
       </s:c>
-      <s:c r="G52" s="15"/>
+      <s:c r="G52" s="15" t="n">
+        <s:v>6647.74</s:v>
+      </s:c>
       <s:c r="J52"/>
       <s:c r="K52"/>
       <s:c r="L52"/>
@@ -2508,12 +2814,18 @@
       <s:c r="C53" s="11" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D53" s="12"/>
-      <s:c r="E53" s="13"/>
+      <s:c r="D53" s="12" t="n">
+        <s:v>39442</s:v>
+      </s:c>
+      <s:c r="E53" s="13" t="n">
+        <s:v>8476.73</s:v>
+      </s:c>
       <s:c r="F53" s="14" t="n">
         <s:v>8916.6</s:v>
       </s:c>
-      <s:c r="G53" s="15"/>
+      <s:c r="G53" s="15" t="n">
+        <s:v>7027.79</s:v>
+      </s:c>
       <s:c r="J53"/>
       <s:c r="K53"/>
       <s:c r="L53"/>
@@ -2530,12 +2842,18 @@
       <s:c r="C54" s="11" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D54" s="12"/>
-      <s:c r="E54" s="13"/>
+      <s:c r="D54" s="12" t="n">
+        <s:v>39390.3</s:v>
+      </s:c>
+      <s:c r="E54" s="13" t="n">
+        <s:v>9170.77</s:v>
+      </s:c>
       <s:c r="F54" s="14" t="n">
         <s:v>8617.9</s:v>
       </s:c>
-      <s:c r="G54" s="15"/>
+      <s:c r="G54" s="15" t="n">
+        <s:v>6900.79</s:v>
+      </s:c>
       <s:c r="J54"/>
       <s:c r="K54"/>
       <s:c r="L54"/>
@@ -2552,12 +2870,18 @@
       <s:c r="C55" s="11" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D55" s="12"/>
-      <s:c r="E55" s="13"/>
+      <s:c r="D55" s="12" t="n">
+        <s:v>39052.1</s:v>
+      </s:c>
+      <s:c r="E55" s="13" t="n">
+        <s:v>9868.27</s:v>
+      </s:c>
       <s:c r="F55" s="14" t="n">
         <s:v>8524.2</s:v>
       </s:c>
-      <s:c r="G55" s="15"/>
+      <s:c r="G55" s="15" t="n">
+        <s:v>7337.19</s:v>
+      </s:c>
       <s:c r="J55"/>
       <s:c r="K55"/>
       <s:c r="L55"/>
@@ -2574,12 +2898,18 @@
       <s:c r="C56" s="11" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D56" s="12"/>
-      <s:c r="E56" s="13"/>
+      <s:c r="D56" s="12" t="n">
+        <s:v>39247.7</s:v>
+      </s:c>
+      <s:c r="E56" s="13" t="n">
+        <s:v>10733.13</s:v>
+      </s:c>
       <s:c r="F56" s="14" t="n">
         <s:v>8352.2</s:v>
       </s:c>
-      <s:c r="G56" s="15"/>
+      <s:c r="G56" s="15" t="n">
+        <s:v>7239.22</s:v>
+      </s:c>
       <s:c r="J56"/>
       <s:c r="K56"/>
       <s:c r="L56"/>
@@ -2596,12 +2926,18 @@
       <s:c r="C57" s="11" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D57" s="12"/>
-      <s:c r="E57" s="13"/>
+      <s:c r="D57" s="12" t="n">
+        <s:v>38527.2</s:v>
+      </s:c>
+      <s:c r="E57" s="13" t="n">
+        <s:v>11079.45</s:v>
+      </s:c>
       <s:c r="F57" s="14" t="n">
         <s:v>7959.3</s:v>
       </s:c>
-      <s:c r="G57" s="15"/>
+      <s:c r="G57" s="15" t="n">
+        <s:v>7908.82</s:v>
+      </s:c>
       <s:c r="J57"/>
       <s:c r="K57"/>
       <s:c r="L57"/>
@@ -2618,12 +2954,18 @@
       <s:c r="C58" s="11" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D58" s="12"/>
-      <s:c r="E58" s="13"/>
+      <s:c r="D58" s="12" t="n">
+        <s:v>38263</s:v>
+      </s:c>
+      <s:c r="E58" s="13" t="n">
+        <s:v>11316.1</s:v>
+      </s:c>
       <s:c r="F58" s="14" t="n">
         <s:v>7565.2</s:v>
       </s:c>
-      <s:c r="G58" s="15"/>
+      <s:c r="G58" s="15" t="n">
+        <s:v>8151.77</s:v>
+      </s:c>
       <s:c r="J58"/>
       <s:c r="K58"/>
       <s:c r="L58"/>
@@ -2640,12 +2982,18 @@
       <s:c r="C59" s="11" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D59" s="12"/>
-      <s:c r="E59" s="13"/>
+      <s:c r="D59" s="12" t="n">
+        <s:v>38959.4</s:v>
+      </s:c>
+      <s:c r="E59" s="13" t="n">
+        <s:v>11558.72</s:v>
+      </s:c>
       <s:c r="F59" s="14" t="n">
         <s:v>7378.9</s:v>
       </s:c>
-      <s:c r="G59" s="15"/>
+      <s:c r="G59" s="15" t="n">
+        <s:v>8850.45</s:v>
+      </s:c>
       <s:c r="J59"/>
       <s:c r="K59"/>
       <s:c r="L59"/>
@@ -2662,12 +3010,18 @@
       <s:c r="C60" s="11" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D60" s="12"/>
-      <s:c r="E60" s="13"/>
+      <s:c r="D60" s="12" t="n">
+        <s:v>39190.7</s:v>
+      </s:c>
+      <s:c r="E60" s="13" t="n">
+        <s:v>11554.01</s:v>
+      </s:c>
       <s:c r="F60" s="14" t="n">
         <s:v>7311.1</s:v>
       </s:c>
-      <s:c r="G60" s="15"/>
+      <s:c r="G60" s="15" t="n">
+        <s:v>8586.32</s:v>
+      </s:c>
       <s:c r="J60"/>
       <s:c r="K60"/>
       <s:c r="L60"/>
@@ -2684,12 +3038,18 @@
       <s:c r="C61" s="11" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D61" s="12"/>
-      <s:c r="E61" s="13"/>
+      <s:c r="D61" s="12" t="n">
+        <s:v>39456.3</s:v>
+      </s:c>
+      <s:c r="E61" s="13" t="n">
+        <s:v>11735.08</s:v>
+      </s:c>
       <s:c r="F61" s="14" t="n">
         <s:v>7199.3</s:v>
       </s:c>
-      <s:c r="G61" s="15"/>
+      <s:c r="G61" s="15" t="n">
+        <s:v>8308.32</s:v>
+      </s:c>
       <s:c r="J61"/>
       <s:c r="K61"/>
       <s:c r="L61"/>
@@ -2706,12 +3066,18 @@
       <s:c r="C62" s="11" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D62" s="12"/>
-      <s:c r="E62" s="13"/>
+      <s:c r="D62" s="12" t="n">
+        <s:v>39867.1</s:v>
+      </s:c>
+      <s:c r="E62" s="13" t="n">
+        <s:v>12284.95</s:v>
+      </s:c>
       <s:c r="F62" s="14" t="n">
         <s:v>6772.6</s:v>
       </s:c>
-      <s:c r="G62" s="15"/>
+      <s:c r="G62" s="15" t="n">
+        <s:v>8264.8</s:v>
+      </s:c>
       <s:c r="J62"/>
       <s:c r="K62"/>
       <s:c r="L62"/>
@@ -2728,12 +3094,18 @@
       <s:c r="C63" s="11" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D63" s="12"/>
-      <s:c r="E63" s="13"/>
+      <s:c r="D63" s="12" t="n">
+        <s:v>40469.4</s:v>
+      </s:c>
+      <s:c r="E63" s="13" t="n">
+        <s:v>12768.8</s:v>
+      </s:c>
       <s:c r="F63" s="14" t="n">
         <s:v>6437.2</s:v>
       </s:c>
-      <s:c r="G63" s="15"/>
+      <s:c r="G63" s="15" t="n">
+        <s:v>8649.28</s:v>
+      </s:c>
       <s:c r="J63"/>
       <s:c r="K63"/>
       <s:c r="L63"/>
@@ -2750,12 +3122,18 @@
       <s:c r="C64" s="11" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D64" s="12"/>
-      <s:c r="E64" s="13"/>
+      <s:c r="D64" s="12" t="n">
+        <s:v>40813.6</s:v>
+      </s:c>
+      <s:c r="E64" s="13" t="n">
+        <s:v>12945.4</s:v>
+      </s:c>
       <s:c r="F64" s="14" t="n">
         <s:v>6406.7</s:v>
       </s:c>
-      <s:c r="G64" s="15"/>
+      <s:c r="G64" s="15" t="n">
+        <s:v>8439.18</s:v>
+      </s:c>
       <s:c r="J64"/>
       <s:c r="K64"/>
       <s:c r="L64"/>
@@ -2772,12 +3150,18 @@
       <s:c r="C65" s="11" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D65" s="12"/>
-      <s:c r="E65" s="13"/>
+      <s:c r="D65" s="12" t="n">
+        <s:v>41211</s:v>
+      </s:c>
+      <s:c r="E65" s="13" t="n">
+        <s:v>13019.33</s:v>
+      </s:c>
       <s:c r="F65" s="14" t="n">
         <s:v>6322.9</s:v>
       </s:c>
-      <s:c r="G65" s="15"/>
+      <s:c r="G65" s="15" t="n">
+        <s:v>8556.46</s:v>
+      </s:c>
       <s:c r="J65"/>
       <s:c r="K65"/>
       <s:c r="L65"/>
@@ -2794,12 +3178,18 @@
       <s:c r="C66" s="11" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D66" s="12"/>
-      <s:c r="E66" s="13"/>
+      <s:c r="D66" s="12" t="n">
+        <s:v>41862.4</s:v>
+      </s:c>
+      <s:c r="E66" s="13" t="n">
+        <s:v>12980.24</s:v>
+      </s:c>
       <s:c r="F66" s="14" t="n">
         <s:v>6288</s:v>
       </s:c>
-      <s:c r="G66" s="15"/>
+      <s:c r="G66" s="15" t="n">
+        <s:v>8368.94</s:v>
+      </s:c>
       <s:c r="J66"/>
       <s:c r="K66"/>
       <s:c r="L66"/>
@@ -2816,12 +3206,18 @@
       <s:c r="C67" s="11" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D67" s="12"/>
-      <s:c r="E67" s="13"/>
+      <s:c r="D67" s="12" t="n">
+        <s:v>42615.9</s:v>
+      </s:c>
+      <s:c r="E67" s="13" t="n">
+        <s:v>13086.36</s:v>
+      </s:c>
       <s:c r="F67" s="14" t="n">
         <s:v>6068.7</s:v>
       </s:c>
-      <s:c r="G67" s="15"/>
+      <s:c r="G67" s="15" t="n">
+        <s:v>8401.96</s:v>
+      </s:c>
       <s:c r="J67"/>
       <s:c r="K67"/>
       <s:c r="L67"/>
@@ -2838,12 +3234,18 @@
       <s:c r="C68" s="11" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D68" s="12"/>
-      <s:c r="E68" s="13"/>
+      <s:c r="D68" s="12" t="n">
+        <s:v>43000.8</s:v>
+      </s:c>
+      <s:c r="E68" s="13" t="n">
+        <s:v>13196.67</s:v>
+      </s:c>
       <s:c r="F68" s="14" t="n">
         <s:v>5722.7</s:v>
       </s:c>
-      <s:c r="G68" s="15"/>
+      <s:c r="G68" s="15" t="n">
+        <s:v>8330.35</s:v>
+      </s:c>
       <s:c r="J68"/>
       <s:c r="K68"/>
       <s:c r="L68"/>
@@ -2860,12 +3262,18 @@
       <s:c r="C69" s="11" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D69" s="12"/>
-      <s:c r="E69" s="13"/>
+      <s:c r="D69" s="12" t="n">
+        <s:v>43605.9</s:v>
+      </s:c>
+      <s:c r="E69" s="13" t="n">
+        <s:v>13253.6</s:v>
+      </s:c>
       <s:c r="F69" s="14" t="n">
         <s:v>5248.6</s:v>
       </s:c>
-      <s:c r="G69" s="15"/>
+      <s:c r="G69" s="15" t="n">
+        <s:v>8327.28</s:v>
+      </s:c>
       <s:c r="J69"/>
       <s:c r="K69"/>
       <s:c r="L69"/>
@@ -2882,12 +3290,18 @@
       <s:c r="C70" s="11" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D70" s="12"/>
-      <s:c r="E70" s="13"/>
+      <s:c r="D70" s="12" t="n">
+        <s:v>43844.1</s:v>
+      </s:c>
+      <s:c r="E70" s="13" t="n">
+        <s:v>13208.35</s:v>
+      </s:c>
       <s:c r="F70" s="14" t="n">
         <s:v>5238.6</s:v>
       </s:c>
-      <s:c r="G70" s="15"/>
+      <s:c r="G70" s="15" t="n">
+        <s:v>8646.31</s:v>
+      </s:c>
       <s:c r="J70"/>
       <s:c r="K70"/>
       <s:c r="L70"/>
@@ -2904,12 +3318,18 @@
       <s:c r="C71" s="11" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D71" s="12"/>
-      <s:c r="E71" s="13"/>
+      <s:c r="D71" s="12" t="n">
+        <s:v>43737.7</s:v>
+      </s:c>
+      <s:c r="E71" s="13" t="n">
+        <s:v>13170.91</s:v>
+      </s:c>
       <s:c r="F71" s="14" t="n">
         <s:v>5246.1</s:v>
       </s:c>
-      <s:c r="G71" s="15"/>
+      <s:c r="G71" s="15" t="n">
+        <s:v>9176.74</s:v>
+      </s:c>
       <s:c r="J71"/>
       <s:c r="K71"/>
       <s:c r="L71"/>
@@ -2926,12 +3346,18 @@
       <s:c r="C72" s="11" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D72" s="12"/>
-      <s:c r="E72" s="13"/>
+      <s:c r="D72" s="12" t="n">
+        <s:v>43703.6</s:v>
+      </s:c>
+      <s:c r="E72" s="13" t="n">
+        <s:v>13279.56</s:v>
+      </s:c>
       <s:c r="F72" s="14" t="n">
         <s:v>5403.3</s:v>
       </s:c>
-      <s:c r="G72" s="15"/>
+      <s:c r="G72" s="15" t="n">
+        <s:v>10054.34</s:v>
+      </s:c>
       <s:c r="J72"/>
       <s:c r="K72"/>
       <s:c r="L72"/>
@@ -2948,12 +3374,18 @@
       <s:c r="C73" s="11" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D73" s="12"/>
-      <s:c r="E73" s="13"/>
+      <s:c r="D73" s="12" t="n">
+        <s:v>43670.5</s:v>
+      </s:c>
+      <s:c r="E73" s="13" t="n">
+        <s:v>13554.25</s:v>
+      </s:c>
       <s:c r="F73" s="14" t="n">
         <s:v>5416</s:v>
       </s:c>
-      <s:c r="G73" s="15"/>
+      <s:c r="G73" s="15" t="n">
+        <s:v>10756.3</s:v>
+      </s:c>
       <s:c r="J73"/>
       <s:c r="K73"/>
       <s:c r="L73"/>
@@ -2970,12 +3402,18 @@
       <s:c r="C74" s="11" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D74" s="12"/>
-      <s:c r="E74" s="13"/>
+      <s:c r="D74" s="12" t="n">
+        <s:v>43208.8</s:v>
+      </s:c>
+      <s:c r="E74" s="13" t="n">
+        <s:v>13780.53</s:v>
+      </s:c>
       <s:c r="F74" s="14" t="n">
         <s:v>5092.4</s:v>
       </s:c>
-      <s:c r="G74" s="15"/>
+      <s:c r="G74" s="15" t="n">
+        <s:v>11284.59</s:v>
+      </s:c>
       <s:c r="J74"/>
       <s:c r="K74"/>
       <s:c r="L74"/>
@@ -2992,12 +3430,18 @@
       <s:c r="C75" s="11" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D75" s="12"/>
-      <s:c r="E75" s="13"/>
+      <s:c r="D75" s="12" t="n">
+        <s:v>43153.7</s:v>
+      </s:c>
+      <s:c r="E75" s="13" t="n">
+        <s:v>14008.63</s:v>
+      </s:c>
       <s:c r="F75" s="14" t="n">
         <s:v>4773.4</s:v>
       </s:c>
-      <s:c r="G75" s="15"/>
+      <s:c r="G75" s="15" t="n">
+        <s:v>11228.44</s:v>
+      </s:c>
       <s:c r="J75"/>
       <s:c r="K75"/>
       <s:c r="L75"/>
@@ -3014,12 +3458,18 @@
       <s:c r="C76" s="11" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D76" s="12"/>
-      <s:c r="E76" s="13"/>
+      <s:c r="D76" s="12" t="n">
+        <s:v>43027.6</s:v>
+      </s:c>
+      <s:c r="E76" s="13" t="n">
+        <s:v>14093.96</s:v>
+      </s:c>
       <s:c r="F76" s="14" t="n">
         <s:v>4585.2</s:v>
       </s:c>
-      <s:c r="G76" s="15"/>
+      <s:c r="G76" s="15" t="n">
+        <s:v>11336.77</s:v>
+      </s:c>
       <s:c r="J76"/>
       <s:c r="K76"/>
       <s:c r="L76"/>
@@ -3036,12 +3486,18 @@
       <s:c r="C77" s="11" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D77" s="12"/>
-      <s:c r="E77" s="13"/>
+      <s:c r="D77" s="12" t="n">
+        <s:v>42839.3</s:v>
+      </s:c>
+      <s:c r="E77" s="13" t="n">
+        <s:v>14086.49</s:v>
+      </s:c>
       <s:c r="F77" s="14" t="n">
         <s:v>4609</s:v>
       </s:c>
-      <s:c r="G77" s="15"/>
+      <s:c r="G77" s="15" t="n">
+        <s:v>11283.36</s:v>
+      </s:c>
       <s:c r="J77"/>
       <s:c r="K77"/>
       <s:c r="L77"/>
@@ -3058,12 +3514,18 @@
       <s:c r="C78" s="11" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D78" s="12"/>
-      <s:c r="E78" s="13"/>
+      <s:c r="D78" s="12" t="n">
+        <s:v>42581.6</s:v>
+      </s:c>
+      <s:c r="E78" s="13" t="n">
+        <s:v>14090.03</s:v>
+      </s:c>
       <s:c r="F78" s="14" t="n">
         <s:v>4534.3</s:v>
       </s:c>
-      <s:c r="G78" s="15"/>
+      <s:c r="G78" s="15" t="n">
+        <s:v>11514.27</s:v>
+      </s:c>
       <s:c r="J78"/>
       <s:c r="K78"/>
       <s:c r="L78"/>
@@ -3080,12 +3542,18 @@
       <s:c r="C79" s="11" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D79" s="12"/>
-      <s:c r="E79" s="13"/>
+      <s:c r="D79" s="12" t="n">
+        <s:v>43080.6</s:v>
+      </s:c>
+      <s:c r="E79" s="13" t="n">
+        <s:v>14099.59</s:v>
+      </s:c>
       <s:c r="F79" s="14" t="n">
         <s:v>4198.5</s:v>
       </s:c>
-      <s:c r="G79" s="15"/>
+      <s:c r="G79" s="15" t="n">
+        <s:v>11904.52</s:v>
+      </s:c>
       <s:c r="J79"/>
       <s:c r="K79"/>
       <s:c r="L79"/>
@@ -3102,12 +3570,18 @@
       <s:c r="C80" s="11" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D80" s="12"/>
-      <s:c r="E80" s="13"/>
+      <s:c r="D80" s="12" t="n">
+        <s:v>42908.5</s:v>
+      </s:c>
+      <s:c r="E80" s="13" t="n">
+        <s:v>14110.86</s:v>
+      </s:c>
       <s:c r="F80" s="14" t="n">
         <s:v>4484.9</s:v>
       </s:c>
-      <s:c r="G80" s="15"/>
+      <s:c r="G80" s="15" t="n">
+        <s:v>11704</s:v>
+      </s:c>
       <s:c r="J80"/>
       <s:c r="K80"/>
       <s:c r="L80"/>
@@ -3124,12 +3598,18 @@
       <s:c r="C81" s="11" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D81" s="12"/>
-      <s:c r="E81" s="13"/>
+      <s:c r="D81" s="12" t="n">
+        <s:v>42588</s:v>
+      </s:c>
+      <s:c r="E81" s="13" t="n">
+        <s:v>14124.33</s:v>
+      </s:c>
       <s:c r="F81" s="14" t="n">
         <s:v>4366.5</s:v>
       </s:c>
-      <s:c r="G81" s="15"/>
+      <s:c r="G81" s="15" t="n">
+        <s:v>11613.39</s:v>
+      </s:c>
       <s:c r="J81"/>
       <s:c r="K81"/>
       <s:c r="L81"/>
@@ -3146,12 +3626,18 @@
       <s:c r="C82" s="11" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D82" s="12"/>
-      <s:c r="E82" s="13"/>
+      <s:c r="D82" s="12" t="n">
+        <s:v>42593.8</s:v>
+      </s:c>
+      <s:c r="E82" s="13" t="n">
+        <s:v>14127.3</s:v>
+      </s:c>
       <s:c r="F82" s="14" t="n">
         <s:v>4039.4</s:v>
       </s:c>
-      <s:c r="G82" s="15"/>
+      <s:c r="G82" s="15" t="n">
+        <s:v>11726.49</s:v>
+      </s:c>
       <s:c r="J82"/>
       <s:c r="K82"/>
       <s:c r="L82"/>
@@ -3168,12 +3654,18 @@
       <s:c r="C83" s="11" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D83" s="12"/>
-      <s:c r="E83" s="13"/>
+      <s:c r="D83" s="12" t="n">
+        <s:v>42326.2</s:v>
+      </s:c>
+      <s:c r="E83" s="13" t="n">
+        <s:v>14084.03</s:v>
+      </s:c>
       <s:c r="F83" s="14" t="n">
         <s:v>3763.7</s:v>
       </s:c>
-      <s:c r="G83" s="15"/>
+      <s:c r="G83" s="15" t="n">
+        <s:v>11561.38</s:v>
+      </s:c>
       <s:c r="J83"/>
       <s:c r="K83"/>
       <s:c r="L83"/>
@@ -3190,12 +3682,18 @@
       <s:c r="C84" s="11" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D84" s="12"/>
-      <s:c r="E84" s="13"/>
+      <s:c r="D84" s="12" t="n">
+        <s:v>41997.3</s:v>
+      </s:c>
+      <s:c r="E84" s="13" t="n">
+        <s:v>14038.62</s:v>
+      </s:c>
       <s:c r="F84" s="14" t="n">
         <s:v>3713.4</s:v>
       </s:c>
-      <s:c r="G84" s="15"/>
+      <s:c r="G84" s="15" t="n">
+        <s:v>11544.92</s:v>
+      </s:c>
       <s:c r="J84"/>
       <s:c r="K84"/>
       <s:c r="L84"/>
@@ -3212,12 +3710,18 @@
       <s:c r="C85" s="11" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D85" s="12"/>
-      <s:c r="E85" s="13"/>
+      <s:c r="D85" s="12" t="n">
+        <s:v>41522.9</s:v>
+      </s:c>
+      <s:c r="E85" s="13" t="n">
+        <s:v>13988.63</s:v>
+      </s:c>
       <s:c r="F85" s="14" t="n">
         <s:v>3857.4</s:v>
       </s:c>
-      <s:c r="G85" s="15"/>
+      <s:c r="G85" s="15" t="n">
+        <s:v>11501.36</s:v>
+      </s:c>
       <s:c r="J85"/>
       <s:c r="K85"/>
       <s:c r="L85"/>
@@ -3234,12 +3738,18 @@
       <s:c r="C86" s="11" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D86" s="12"/>
-      <s:c r="E86" s="13"/>
+      <s:c r="D86" s="12" t="n">
+        <s:v>41114</s:v>
+      </s:c>
+      <s:c r="E86" s="13" t="n">
+        <s:v>13951.51</s:v>
+      </s:c>
       <s:c r="F86" s="14" t="n">
         <s:v>3753.8</s:v>
       </s:c>
-      <s:c r="G86" s="15"/>
+      <s:c r="G86" s="15" t="n">
+        <s:v>11276.5</s:v>
+      </s:c>
       <s:c r="J86"/>
       <s:c r="K86"/>
       <s:c r="L86"/>
@@ -3256,12 +3766,18 @@
       <s:c r="C87" s="11" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D87" s="12"/>
-      <s:c r="E87" s="13"/>
+      <s:c r="D87" s="12" t="n">
+        <s:v>41056.4</s:v>
+      </s:c>
+      <s:c r="E87" s="13" t="n">
+        <s:v>13954.41</s:v>
+      </s:c>
       <s:c r="F87" s="14" t="n">
         <s:v>3763.1</s:v>
       </s:c>
-      <s:c r="G87" s="15"/>
+      <s:c r="G87" s="15" t="n">
+        <s:v>10741.23</s:v>
+      </s:c>
       <s:c r="J87"/>
       <s:c r="K87"/>
       <s:c r="L87"/>
@@ -3278,12 +3794,18 @@
       <s:c r="C88" s="11" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D88" s="12"/>
-      <s:c r="E88" s="13"/>
+      <s:c r="D88" s="12" t="n">
+        <s:v>40351</s:v>
+      </s:c>
+      <s:c r="E88" s="13" t="n">
+        <s:v>13858.06</s:v>
+      </s:c>
       <s:c r="F88" s="14" t="n">
         <s:v>3915.7</s:v>
       </s:c>
-      <s:c r="G88" s="15"/>
+      <s:c r="G88" s="15" t="n">
+        <s:v>10118.53</s:v>
+      </s:c>
       <s:c r="J88"/>
       <s:c r="K88"/>
       <s:c r="L88"/>
@@ -3300,12 +3822,18 @@
       <s:c r="C89" s="11" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D89" s="12"/>
-      <s:c r="E89" s="13"/>
+      <s:c r="D89" s="12" t="n">
+        <s:v>39982.3</s:v>
+      </s:c>
+      <s:c r="E89" s="13" t="n">
+        <s:v>13609.17</s:v>
+      </s:c>
       <s:c r="F89" s="14" t="n">
         <s:v>3871.5</s:v>
       </s:c>
-      <s:c r="G89" s="15"/>
+      <s:c r="G89" s="15" t="n">
+        <s:v>9838.66</s:v>
+      </s:c>
       <s:c r="J89"/>
       <s:c r="K89"/>
       <s:c r="L89"/>
@@ -3322,12 +3850,18 @@
       <s:c r="C90" s="11" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D90" s="12"/>
-      <s:c r="E90" s="13"/>
+      <s:c r="D90" s="12" t="n">
+        <s:v>39379.3</s:v>
+      </s:c>
+      <s:c r="E90" s="13" t="n">
+        <s:v>12639.15</s:v>
+      </s:c>
       <s:c r="F90" s="14" t="n">
         <s:v>3602.4</s:v>
       </s:c>
-      <s:c r="G90" s="15"/>
+      <s:c r="G90" s="15" t="n">
+        <s:v>9013.66</s:v>
+      </s:c>
       <s:c r="J90"/>
       <s:c r="K90"/>
       <s:c r="L90"/>
@@ -3344,12 +3878,18 @@
       <s:c r="C91" s="11" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D91" s="12"/>
-      <s:c r="E91" s="13"/>
+      <s:c r="D91" s="12" t="n">
+        <s:v>38945.6</s:v>
+      </s:c>
+      <s:c r="E91" s="13" t="n">
+        <s:v>12245.62</s:v>
+      </s:c>
       <s:c r="F91" s="14" t="n">
         <s:v>3371.6</s:v>
       </s:c>
-      <s:c r="G91" s="15"/>
+      <s:c r="G91" s="15" t="n">
+        <s:v>8329.48</s:v>
+      </s:c>
       <s:c r="J91"/>
       <s:c r="K91"/>
       <s:c r="L91"/>
@@ -3366,12 +3906,18 @@
       <s:c r="C92" s="11" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D92" s="12"/>
-      <s:c r="E92" s="13"/>
+      <s:c r="D92" s="12" t="n">
+        <s:v>37979.9</s:v>
+      </s:c>
+      <s:c r="E92" s="13" t="n">
+        <s:v>11953.43</s:v>
+      </s:c>
       <s:c r="F92" s="14" t="n">
         <s:v>3112.6</s:v>
       </s:c>
-      <s:c r="G92" s="15"/>
+      <s:c r="G92" s="15" t="n">
+        <s:v>7364.94</s:v>
+      </s:c>
       <s:c r="J92"/>
       <s:c r="K92"/>
       <s:c r="L92"/>
@@ -3388,12 +3934,18 @@
       <s:c r="C93" s="11" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D93" s="12"/>
-      <s:c r="E93" s="13"/>
+      <s:c r="D93" s="12" t="n">
+        <s:v>37319.6</s:v>
+      </s:c>
+      <s:c r="E93" s="13" t="n">
+        <s:v>11765.31</s:v>
+      </s:c>
       <s:c r="F93" s="14" t="n">
         <s:v>2951.2</s:v>
       </s:c>
-      <s:c r="G93" s="15"/>
+      <s:c r="G93" s="15" t="n">
+        <s:v>6831.04</s:v>
+      </s:c>
       <s:c r="J93"/>
       <s:c r="K93"/>
       <s:c r="L93"/>
@@ -3410,12 +3962,18 @@
       <s:c r="C94" s="11" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D94" s="12"/>
-      <s:c r="E94" s="13"/>
+      <s:c r="D94" s="12" t="n">
+        <s:v>36477.1</s:v>
+      </s:c>
+      <s:c r="E94" s="13" t="n">
+        <s:v>11569.57</s:v>
+      </s:c>
       <s:c r="F94" s="14" t="n">
         <s:v>2976</s:v>
       </s:c>
-      <s:c r="G94" s="15"/>
+      <s:c r="G94" s="15" t="n">
+        <s:v>6223.79</s:v>
+      </s:c>
       <s:c r="J94"/>
       <s:c r="K94"/>
       <s:c r="L94"/>
@@ -3432,12 +3990,18 @@
       <s:c r="C95" s="11" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D95" s="12"/>
-      <s:c r="E95" s="13"/>
+      <s:c r="D95" s="12" t="n">
+        <s:v>35971.8</s:v>
+      </s:c>
+      <s:c r="E95" s="13" t="n">
+        <s:v>11371.62</s:v>
+      </s:c>
       <s:c r="F95" s="14" t="n">
         <s:v>2942</s:v>
       </s:c>
-      <s:c r="G95" s="15"/>
+      <s:c r="G95" s="15" t="n">
+        <s:v>6222.08</s:v>
+      </s:c>
       <s:c r="J95"/>
       <s:c r="K95"/>
       <s:c r="L95"/>
@@ -3454,12 +4018,18 @@
       <s:c r="C96" s="11" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D96" s="12"/>
-      <s:c r="E96" s="13"/>
+      <s:c r="D96" s="12" t="n">
+        <s:v>35377.4</s:v>
+      </s:c>
+      <s:c r="E96" s="13" t="n">
+        <s:v>11174.36</s:v>
+      </s:c>
       <s:c r="F96" s="14" t="n">
         <s:v>2910.3</s:v>
       </s:c>
-      <s:c r="G96" s="15"/>
+      <s:c r="G96" s="15" t="n">
+        <s:v>6097.34</s:v>
+      </s:c>
       <s:c r="J96"/>
       <s:c r="K96"/>
       <s:c r="L96"/>
@@ -3478,12 +4048,18 @@
       <s:c r="C97" s="11" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D97" s="12"/>
-      <s:c r="E97" s="13"/>
+      <s:c r="D97" s="12" t="n">
+        <s:v>34971</s:v>
+      </s:c>
+      <s:c r="E97" s="13" t="n">
+        <s:v>11001.5</s:v>
+      </s:c>
       <s:c r="F97" s="14" t="n">
         <s:v>2872.9</s:v>
       </s:c>
-      <s:c r="G97" s="15"/>
+      <s:c r="G97" s="15" t="n">
+        <s:v>5928.24</s:v>
+      </s:c>
       <s:c r="J97"/>
       <s:c r="K97"/>
       <s:c r="L97"/>
